--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07D06D61-E368-4B7F-ABAE-2B8067D06B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90F29B45-0E38-44DA-8A2B-E3368F674CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{88375829-F622-4FE1-8296-3204C4AC81B5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{577248E1-FC9B-4553-9436-7C0CCDF58D34}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3383,7 +3383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E72743F-1421-4673-A120-3D6418892A39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBAFC497-87B8-450C-AD73-B9EAFFD14139}">
   <dimension ref="B9:T466"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24562,7 +24562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87672045-D7D5-4C83-AEF6-AB7A18D5F89A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27ADCB8-FB0A-48D6-BFF2-40C8B0F9428E}">
   <dimension ref="B9:T623"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49099,7 +49099,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L555">
-        <v>0.55977485635294111</v>
+        <v>0.55977485635294122</v>
       </c>
     </row>
     <row r="556" spans="2:12" x14ac:dyDescent="0.45">
@@ -49904,7 +49904,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L590">
-        <v>0.33802250703984932</v>
+        <v>0.33802250703984926</v>
       </c>
     </row>
     <row r="591" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90F29B45-0E38-44DA-8A2B-E3368F674CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC4B93EC-0B20-4920-942F-C5B9837F2416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{577248E1-FC9B-4553-9436-7C0CCDF58D34}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C7B9D3CE-1739-4726-8687-322A540E8B38}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3383,7 +3383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBAFC497-87B8-450C-AD73-B9EAFFD14139}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55FED866-F1F4-4C8C-8C22-6EA5460923A9}">
   <dimension ref="B9:T466"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24562,7 +24562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27ADCB8-FB0A-48D6-BFF2-40C8B0F9428E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EFDACB6-7701-4FD5-B777-FC2ADE169747}">
   <dimension ref="B9:T623"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -48061,7 +48061,7 @@
         <v>33</v>
       </c>
       <c r="L525">
-        <v>0.14220084641443553</v>
+        <v>0.14220084641443556</v>
       </c>
     </row>
     <row r="526" spans="2:12" x14ac:dyDescent="0.45">
@@ -49099,7 +49099,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L555">
-        <v>0.55977485635294122</v>
+        <v>0.55977485635294111</v>
       </c>
     </row>
     <row r="556" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC4B93EC-0B20-4920-942F-C5B9837F2416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DC8E476-7935-4CDA-827D-872CB9961034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C7B9D3CE-1739-4726-8687-322A540E8B38}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A8EB2609-9AC4-4BD4-AE2F-1C425EEC7624}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3383,7 +3383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55FED866-F1F4-4C8C-8C22-6EA5460923A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC731AE5-A508-4BAF-BAEC-D585689EFB98}">
   <dimension ref="B9:T466"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24562,7 +24562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EFDACB6-7701-4FD5-B777-FC2ADE169747}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5900890F-FD68-4F15-8C10-80F07B936B91}">
   <dimension ref="B9:T623"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -48061,7 +48061,7 @@
         <v>33</v>
       </c>
       <c r="L525">
-        <v>0.14220084641443556</v>
+        <v>0.14220084641443553</v>
       </c>
     </row>
     <row r="526" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DC8E476-7935-4CDA-827D-872CB9961034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C21BB684-28A5-4F37-BC41-72961474FB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A8EB2609-9AC4-4BD4-AE2F-1C425EEC7624}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{64CADF40-7A13-4854-BC94-E2DF6449C32F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3383,7 +3383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC731AE5-A508-4BAF-BAEC-D585689EFB98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{357DCDFA-D6A3-4475-8BA8-0F98ACFE06B2}">
   <dimension ref="B9:T466"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24562,7 +24562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5900890F-FD68-4F15-8C10-80F07B936B91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F89970F-613B-4C4C-8212-44A8ED6C2C75}">
   <dimension ref="B9:T623"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49099,7 +49099,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L555">
-        <v>0.55977485635294111</v>
+        <v>0.55977485635294122</v>
       </c>
     </row>
     <row r="556" spans="2:12" x14ac:dyDescent="0.45">
@@ -49904,7 +49904,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L590">
-        <v>0.33802250703984926</v>
+        <v>0.33802250703984932</v>
       </c>
     </row>
     <row r="591" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C21BB684-28A5-4F37-BC41-72961474FB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A957EA0-CF49-4847-8193-E9024166254A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{64CADF40-7A13-4854-BC94-E2DF6449C32F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D9AFB254-76DD-4FE8-9BBA-873249A1E5DC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3383,7 +3383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{357DCDFA-D6A3-4475-8BA8-0F98ACFE06B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C480F22B-82CA-4284-93AA-741BC3DC45D4}">
   <dimension ref="B9:T466"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24562,7 +24562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F89970F-613B-4C4C-8212-44A8ED6C2C75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B06FC1-3584-4686-9F87-70523F8F2438}">
   <dimension ref="B9:T623"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49099,7 +49099,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L555">
-        <v>0.55977485635294122</v>
+        <v>0.55977485635294111</v>
       </c>
     </row>
     <row r="556" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A957EA0-CF49-4847-8193-E9024166254A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20B47A81-89D4-4382-8783-11208E52D0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D9AFB254-76DD-4FE8-9BBA-873249A1E5DC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{18235DD2-FDF6-4DA8-88E5-9CD988D043E0}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3383,7 +3383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C480F22B-82CA-4284-93AA-741BC3DC45D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C54B378-0594-4043-A524-9AAEB2474149}">
   <dimension ref="B9:T466"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24562,7 +24562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B06FC1-3584-4686-9F87-70523F8F2438}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{082A2DDA-0616-4B81-AB21-3C5570626FEB}">
   <dimension ref="B9:T623"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -48061,7 +48061,7 @@
         <v>33</v>
       </c>
       <c r="L525">
-        <v>0.14220084641443553</v>
+        <v>0.14220084641443556</v>
       </c>
     </row>
     <row r="526" spans="2:12" x14ac:dyDescent="0.45">
@@ -49099,7 +49099,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L555">
-        <v>0.55977485635294111</v>
+        <v>0.55977485635294122</v>
       </c>
     </row>
     <row r="556" spans="2:12" x14ac:dyDescent="0.45">
@@ -49904,7 +49904,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L590">
-        <v>0.33802250703984932</v>
+        <v>0.33802250703984926</v>
       </c>
     </row>
     <row r="591" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20B47A81-89D4-4382-8783-11208E52D0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D353704-AFFD-4C6E-88A4-E4486373B822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{18235DD2-FDF6-4DA8-88E5-9CD988D043E0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A5CAFA1C-E992-466F-AC23-D24AAB532E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -996,7 +996,7 @@
     <t>ep_solar_pv_G100001005219</t>
   </si>
   <si>
-    <t>ep_windoff_c_wof-DEU</t>
+    <t>ep_windoff_DEU</t>
   </si>
   <si>
     <t>windoff</t>
@@ -1005,6 +1005,9 @@
     <t>elc_wof-DEU</t>
   </si>
   <si>
+    <t>ep_windoff_wind_DEU</t>
+  </si>
+  <si>
     <t>ep_windoff_wind_G100000919751</t>
   </si>
   <si>
@@ -1092,9 +1095,6 @@
     <t>ep_windoff_wind_G100000920008</t>
   </si>
   <si>
-    <t>ep_windoff_wind_c_wof-DEU</t>
-  </si>
-  <si>
     <t>ep_windon_wind_</t>
   </si>
   <si>
@@ -1104,7 +1104,7 @@
     <t>elc_won-DEU</t>
   </si>
   <si>
-    <t>ep_windon_wind_c_won-DEU</t>
+    <t>ep_windon_wind_DEU</t>
   </si>
   <si>
     <t>~fi_process</t>
@@ -3383,7 +3383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C54B378-0594-4043-A524-9AAEB2474149}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B18255-E7D9-4034-836C-C8E089E41BDD}">
   <dimension ref="B9:T466"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24562,7 +24562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{082A2DDA-0616-4B81-AB21-3C5570626FEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C71A075F-F0A2-4FE7-91C4-0AE4F067E64B}">
   <dimension ref="B9:T623"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40515,7 +40515,7 @@
         <v>322</v>
       </c>
       <c r="P310" t="s">
-        <v>567</v>
+        <v>364</v>
       </c>
       <c r="Q310" t="s">
         <v>365</v>
@@ -40527,7 +40527,7 @@
         <v>563</v>
       </c>
       <c r="T310" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="311" spans="2:20" x14ac:dyDescent="0.45">
@@ -40568,7 +40568,7 @@
         <v>323</v>
       </c>
       <c r="P311" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="Q311" t="s">
         <v>365</v>
@@ -40621,7 +40621,7 @@
         <v>324</v>
       </c>
       <c r="P312" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="Q312" t="s">
         <v>365</v>
@@ -40674,7 +40674,7 @@
         <v>325</v>
       </c>
       <c r="P313" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="Q313" t="s">
         <v>365</v>
@@ -40727,7 +40727,7 @@
         <v>326</v>
       </c>
       <c r="P314" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="Q314" t="s">
         <v>365</v>
@@ -40780,7 +40780,7 @@
         <v>327</v>
       </c>
       <c r="P315" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="Q315" t="s">
         <v>365</v>
@@ -40833,7 +40833,7 @@
         <v>328</v>
       </c>
       <c r="P316" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="Q316" t="s">
         <v>365</v>
@@ -40886,7 +40886,7 @@
         <v>329</v>
       </c>
       <c r="P317" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="Q317" t="s">
         <v>365</v>
@@ -40939,7 +40939,7 @@
         <v>330</v>
       </c>
       <c r="P318" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="Q318" t="s">
         <v>365</v>
@@ -40992,7 +40992,7 @@
         <v>331</v>
       </c>
       <c r="P319" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="Q319" t="s">
         <v>365</v>
@@ -41045,7 +41045,7 @@
         <v>332</v>
       </c>
       <c r="P320" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="Q320" t="s">
         <v>365</v>
@@ -41098,7 +41098,7 @@
         <v>333</v>
       </c>
       <c r="P321" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="Q321" t="s">
         <v>365</v>
@@ -41151,7 +41151,7 @@
         <v>334</v>
       </c>
       <c r="P322" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Q322" t="s">
         <v>365</v>
@@ -41204,7 +41204,7 @@
         <v>335</v>
       </c>
       <c r="P323" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="Q323" t="s">
         <v>365</v>
@@ -41257,7 +41257,7 @@
         <v>336</v>
       </c>
       <c r="P324" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Q324" t="s">
         <v>365</v>
@@ -41310,7 +41310,7 @@
         <v>337</v>
       </c>
       <c r="P325" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q325" t="s">
         <v>365</v>
@@ -41363,7 +41363,7 @@
         <v>338</v>
       </c>
       <c r="P326" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q326" t="s">
         <v>365</v>
@@ -41416,7 +41416,7 @@
         <v>339</v>
       </c>
       <c r="P327" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="Q327" t="s">
         <v>365</v>
@@ -41469,7 +41469,7 @@
         <v>340</v>
       </c>
       <c r="P328" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="Q328" t="s">
         <v>365</v>
@@ -41522,7 +41522,7 @@
         <v>341</v>
       </c>
       <c r="P329" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="Q329" t="s">
         <v>365</v>
@@ -41575,7 +41575,7 @@
         <v>342</v>
       </c>
       <c r="P330" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="Q330" t="s">
         <v>365</v>
@@ -41628,7 +41628,7 @@
         <v>343</v>
       </c>
       <c r="P331" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="Q331" t="s">
         <v>365</v>
@@ -41681,7 +41681,7 @@
         <v>344</v>
       </c>
       <c r="P332" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="Q332" t="s">
         <v>365</v>
@@ -41734,7 +41734,7 @@
         <v>345</v>
       </c>
       <c r="P333" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="Q333" t="s">
         <v>365</v>
@@ -41787,7 +41787,7 @@
         <v>346</v>
       </c>
       <c r="P334" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="Q334" t="s">
         <v>365</v>
@@ -41840,7 +41840,7 @@
         <v>347</v>
       </c>
       <c r="P335" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Q335" t="s">
         <v>365</v>
@@ -41893,7 +41893,7 @@
         <v>348</v>
       </c>
       <c r="P336" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q336" t="s">
         <v>365</v>
@@ -41946,7 +41946,7 @@
         <v>349</v>
       </c>
       <c r="P337" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="Q337" t="s">
         <v>365</v>
@@ -41999,7 +41999,7 @@
         <v>350</v>
       </c>
       <c r="P338" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="Q338" t="s">
         <v>365</v>
@@ -42052,7 +42052,7 @@
         <v>351</v>
       </c>
       <c r="P339" t="s">
-        <v>364</v>
+        <v>595</v>
       </c>
       <c r="Q339" t="s">
         <v>365</v>
@@ -42064,7 +42064,7 @@
         <v>563</v>
       </c>
       <c r="T339" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="340" spans="2:20" x14ac:dyDescent="0.45">
@@ -48061,7 +48061,7 @@
         <v>33</v>
       </c>
       <c r="L525">
-        <v>0.14220084641443556</v>
+        <v>0.14414942289270033</v>
       </c>
     </row>
     <row r="526" spans="2:12" x14ac:dyDescent="0.45">
@@ -48096,7 +48096,7 @@
         <v>58</v>
       </c>
       <c r="L526">
-        <v>0.154796817</v>
+        <v>0.15479681717407709</v>
       </c>
     </row>
     <row r="527" spans="2:12" x14ac:dyDescent="0.45">
@@ -48131,7 +48131,7 @@
         <v>52</v>
       </c>
       <c r="L527">
-        <v>0.14239484199999999</v>
+        <v>0.14269970471336499</v>
       </c>
     </row>
     <row r="528" spans="2:12" x14ac:dyDescent="0.45">
@@ -48166,7 +48166,7 @@
         <v>51</v>
       </c>
       <c r="L528">
-        <v>0.14272310271904762</v>
+        <v>0.14530909379690005</v>
       </c>
     </row>
     <row r="529" spans="2:12" x14ac:dyDescent="0.45">
@@ -48201,7 +48201,7 @@
         <v>50</v>
       </c>
       <c r="L529">
-        <v>0.14889358660568383</v>
+        <v>0.15110343458075226</v>
       </c>
     </row>
     <row r="530" spans="2:12" x14ac:dyDescent="0.45">
@@ -48236,7 +48236,7 @@
         <v>49</v>
       </c>
       <c r="L530">
-        <v>0.14617942234629633</v>
+        <v>0.1484646113737709</v>
       </c>
     </row>
     <row r="531" spans="2:12" x14ac:dyDescent="0.45">
@@ -48271,7 +48271,7 @@
         <v>48</v>
       </c>
       <c r="L531">
-        <v>0.14632010246675289</v>
+        <v>0.1478125168922467</v>
       </c>
     </row>
     <row r="532" spans="2:12" x14ac:dyDescent="0.45">
@@ -48306,7 +48306,7 @@
         <v>47</v>
       </c>
       <c r="L532">
-        <v>0.14195861092253534</v>
+        <v>0.14318892495764401</v>
       </c>
     </row>
     <row r="533" spans="2:12" x14ac:dyDescent="0.45">
@@ -48341,7 +48341,7 @@
         <v>46</v>
       </c>
       <c r="L533">
-        <v>0.14203431021460089</v>
+        <v>0.14374602832673186</v>
       </c>
     </row>
     <row r="534" spans="2:12" x14ac:dyDescent="0.45">
@@ -48376,7 +48376,7 @@
         <v>45</v>
       </c>
       <c r="L534">
-        <v>0.14052119535026128</v>
+        <v>0.14236302397229519</v>
       </c>
     </row>
     <row r="535" spans="2:12" x14ac:dyDescent="0.45">
@@ -48411,7 +48411,7 @@
         <v>44</v>
       </c>
       <c r="L535">
-        <v>0.13766433831664407</v>
+        <v>0.13910548113503837</v>
       </c>
     </row>
     <row r="536" spans="2:12" x14ac:dyDescent="0.45">
@@ -48446,7 +48446,7 @@
         <v>43</v>
       </c>
       <c r="L536">
-        <v>0.13801197826830153</v>
+        <v>0.13976035684171115</v>
       </c>
     </row>
     <row r="537" spans="2:12" x14ac:dyDescent="0.45">
@@ -48481,7 +48481,7 @@
         <v>42</v>
       </c>
       <c r="L537">
-        <v>0.14079377215870786</v>
+        <v>0.14278654204113042</v>
       </c>
     </row>
     <row r="538" spans="2:12" x14ac:dyDescent="0.45">
@@ -48516,7 +48516,7 @@
         <v>41</v>
       </c>
       <c r="L538">
-        <v>0.13951973454105707</v>
+        <v>0.14164320877837852</v>
       </c>
     </row>
     <row r="539" spans="2:12" x14ac:dyDescent="0.45">
@@ -48551,7 +48551,7 @@
         <v>40</v>
       </c>
       <c r="L539">
-        <v>0.13798938637994149</v>
+        <v>0.13947097497492156</v>
       </c>
     </row>
     <row r="540" spans="2:12" x14ac:dyDescent="0.45">
@@ -48586,7 +48586,7 @@
         <v>39</v>
       </c>
       <c r="L540">
-        <v>0.13798332827978627</v>
+        <v>0.13916256554785422</v>
       </c>
     </row>
     <row r="541" spans="2:12" x14ac:dyDescent="0.45">
@@ -48621,7 +48621,7 @@
         <v>38</v>
       </c>
       <c r="L541">
-        <v>0.14063260512172071</v>
+        <v>0.14226203382933417</v>
       </c>
     </row>
     <row r="542" spans="2:12" x14ac:dyDescent="0.45">
@@ -48656,7 +48656,7 @@
         <v>37</v>
       </c>
       <c r="L542">
-        <v>0.14035028189024384</v>
+        <v>0.14224126879395918</v>
       </c>
     </row>
     <row r="543" spans="2:12" x14ac:dyDescent="0.45">
@@ -48691,7 +48691,7 @@
         <v>36</v>
       </c>
       <c r="L543">
-        <v>0.14142181364417927</v>
+        <v>0.14358227326029918</v>
       </c>
     </row>
     <row r="544" spans="2:12" x14ac:dyDescent="0.45">
@@ -48726,7 +48726,7 @@
         <v>35</v>
       </c>
       <c r="L544">
-        <v>0.13985110901356679</v>
+        <v>0.14183629438879436</v>
       </c>
     </row>
     <row r="545" spans="2:12" x14ac:dyDescent="0.45">
@@ -48761,7 +48761,7 @@
         <v>34</v>
       </c>
       <c r="L545">
-        <v>0.14097107730078495</v>
+        <v>0.14267964250835558</v>
       </c>
     </row>
     <row r="546" spans="2:12" x14ac:dyDescent="0.45">
@@ -48796,7 +48796,7 @@
         <v>33</v>
       </c>
       <c r="L546">
-        <v>0.14046810543254867</v>
+        <v>0.14276086713284047</v>
       </c>
     </row>
     <row r="547" spans="2:12" x14ac:dyDescent="0.45">
@@ -48831,7 +48831,7 @@
         <v>32</v>
       </c>
       <c r="L547">
-        <v>0.14124074719487253</v>
+        <v>0.14312627568554598</v>
       </c>
     </row>
     <row r="548" spans="2:12" x14ac:dyDescent="0.45">
@@ -48866,7 +48866,7 @@
         <v>31</v>
       </c>
       <c r="L548">
-        <v>0.14081681645948885</v>
+        <v>0.14266939187885863</v>
       </c>
     </row>
     <row r="549" spans="2:12" x14ac:dyDescent="0.45">
@@ -48901,7 +48901,7 @@
         <v>30</v>
       </c>
       <c r="L549">
-        <v>0.13216799300000001</v>
+        <v>0.13560478025114331</v>
       </c>
     </row>
     <row r="550" spans="2:12" x14ac:dyDescent="0.45">
@@ -48936,7 +48936,7 @@
         <v>30</v>
       </c>
       <c r="L550">
-        <v>0.14349987439160838</v>
+        <v>0.14402577506745184</v>
       </c>
     </row>
     <row r="551" spans="2:12" x14ac:dyDescent="0.45">
@@ -48971,7 +48971,7 @@
         <v>51</v>
       </c>
       <c r="L551">
-        <v>0.15572482300000001</v>
+        <v>0.1662904323543602</v>
       </c>
     </row>
     <row r="552" spans="2:12" x14ac:dyDescent="0.45">
@@ -49006,7 +49006,7 @@
         <v>30</v>
       </c>
       <c r="L552">
-        <v>0.14730061699999999</v>
+        <v>0.14947329818381069</v>
       </c>
     </row>
     <row r="553" spans="2:12" x14ac:dyDescent="0.45">
@@ -49041,7 +49041,7 @@
         <v>31</v>
       </c>
       <c r="L553">
-        <v>0.13506702800000001</v>
+        <v>0.13506702809050411</v>
       </c>
     </row>
     <row r="554" spans="2:12" x14ac:dyDescent="0.45">
@@ -49076,7 +49076,7 @@
         <v>30</v>
       </c>
       <c r="L554">
-        <v>0.14652712700000001</v>
+        <v>0.1473006173562347</v>
       </c>
     </row>
     <row r="555" spans="2:12" x14ac:dyDescent="0.45">
@@ -49099,7 +49099,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L555">
-        <v>0.55977485635294122</v>
+        <v>0.5494511547454104</v>
       </c>
     </row>
     <row r="556" spans="2:12" x14ac:dyDescent="0.45">
@@ -49113,21 +49113,21 @@
         <v>321</v>
       </c>
       <c r="E556">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="F556">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="G556">
         <v>0.33123000000000002</v>
       </c>
       <c r="L556">
-        <v>0.57868857299999998</v>
+        <v>0.56070484516620278</v>
       </c>
     </row>
     <row r="557" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B557" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C557" t="s">
         <v>320</v>
@@ -49136,21 +49136,21 @@
         <v>321</v>
       </c>
       <c r="E557">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="F557">
-        <v>0.20300000000000001</v>
+        <v>7.8E-2</v>
       </c>
       <c r="G557">
         <v>0.33123000000000002</v>
       </c>
       <c r="L557">
-        <v>0.57868857299999998</v>
+        <v>0.49739244453118475</v>
       </c>
     </row>
     <row r="558" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B558" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C558" t="s">
         <v>320</v>
@@ -49159,21 +49159,21 @@
         <v>321</v>
       </c>
       <c r="E558">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="F558">
-        <v>0.24</v>
+        <v>0.113</v>
       </c>
       <c r="G558">
-        <v>0.33123000000000002</v>
+        <v>0.33123000000000008</v>
       </c>
       <c r="L558">
-        <v>0.553779154</v>
+        <v>0.52772313454747122</v>
       </c>
     </row>
     <row r="559" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B559" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C559" t="s">
         <v>320</v>
@@ -49182,21 +49182,21 @@
         <v>321</v>
       </c>
       <c r="E559">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="F559">
-        <v>0.24</v>
+        <v>0.111</v>
       </c>
       <c r="G559">
         <v>0.33123000000000002</v>
       </c>
       <c r="L559">
-        <v>0.57868857299999987</v>
+        <v>0.45399681816583826</v>
       </c>
     </row>
     <row r="560" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B560" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C560" t="s">
         <v>320</v>
@@ -49205,21 +49205,21 @@
         <v>321</v>
       </c>
       <c r="E560">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="F560">
-        <v>0.26500000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="G560">
         <v>0.33123000000000002</v>
       </c>
       <c r="L560">
-        <v>0.57442702300000004</v>
+        <v>0.57259317315365765</v>
       </c>
     </row>
     <row r="561" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B561" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C561" t="s">
         <v>320</v>
@@ -49228,21 +49228,21 @@
         <v>321</v>
       </c>
       <c r="E561">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="F561">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="G561">
         <v>0.33123000000000002</v>
       </c>
       <c r="L561">
-        <v>0.57868857299999998</v>
+        <v>0.56070484516620278</v>
       </c>
     </row>
     <row r="562" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B562" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C562" t="s">
         <v>320</v>
@@ -49251,21 +49251,21 @@
         <v>321</v>
       </c>
       <c r="E562">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="F562">
-        <v>0.252</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="G562">
         <v>0.33123000000000002</v>
       </c>
       <c r="L562">
-        <v>0.57442702300000004</v>
+        <v>0.56070484516620278</v>
       </c>
     </row>
     <row r="563" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B563" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C563" t="s">
         <v>320</v>
@@ -49274,21 +49274,21 @@
         <v>321</v>
       </c>
       <c r="E563">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F563">
-        <v>0.25700000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="G563">
         <v>0.33123000000000002</v>
       </c>
       <c r="L563">
-        <v>0.51877992900000003</v>
+        <v>0.56070484516620278</v>
       </c>
     </row>
     <row r="564" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B564" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C564" t="s">
         <v>320</v>
@@ -49297,21 +49297,21 @@
         <v>321</v>
       </c>
       <c r="E564">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="F564">
-        <v>0.28799999999999998</v>
+        <v>0.24</v>
       </c>
       <c r="G564">
         <v>0.33123000000000002</v>
       </c>
       <c r="L564">
-        <v>0.57695094899999999</v>
+        <v>0.56070484516620278</v>
       </c>
     </row>
     <row r="565" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B565" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C565" t="s">
         <v>320</v>
@@ -49320,21 +49320,21 @@
         <v>321</v>
       </c>
       <c r="E565">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="F565">
-        <v>0.28799999999999998</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="G565">
         <v>0.33123000000000002</v>
       </c>
       <c r="L565">
-        <v>0.58773672300000002</v>
+        <v>0.55664824028154647</v>
       </c>
     </row>
     <row r="566" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B566" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C566" t="s">
         <v>320</v>
@@ -49343,21 +49343,21 @@
         <v>321</v>
       </c>
       <c r="E566">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="F566">
-        <v>0.28799999999999998</v>
+        <v>0.26</v>
       </c>
       <c r="G566">
         <v>0.33123000000000002</v>
       </c>
       <c r="L566">
-        <v>0.49296379099999998</v>
+        <v>0.57259317315365765</v>
       </c>
     </row>
     <row r="567" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B567" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C567" t="s">
         <v>320</v>
@@ -49366,21 +49366,21 @@
         <v>321</v>
       </c>
       <c r="E567">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="F567">
-        <v>0.28799999999999998</v>
+        <v>0.252</v>
       </c>
       <c r="G567">
         <v>0.33123000000000002</v>
       </c>
       <c r="L567">
-        <v>0.56071739600000003</v>
+        <v>0.56070484516620278</v>
       </c>
     </row>
     <row r="568" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B568" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C568" t="s">
         <v>320</v>
@@ -49389,21 +49389,21 @@
         <v>321</v>
       </c>
       <c r="E568">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="F568">
-        <v>0.28799999999999998</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="G568">
         <v>0.33123000000000002</v>
       </c>
       <c r="L568">
-        <v>0.58773672300000002</v>
+        <v>0.51308140128455437</v>
       </c>
     </row>
     <row r="569" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B569" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C569" t="s">
         <v>320</v>
@@ -49412,21 +49412,21 @@
         <v>321</v>
       </c>
       <c r="E569">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="F569">
-        <v>0.33200000000000002</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="G569">
         <v>0.33123000000000002</v>
       </c>
       <c r="L569">
-        <v>0.56071739600000003</v>
+        <v>0.55878495565143582</v>
       </c>
     </row>
     <row r="570" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B570" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C570" t="s">
         <v>320</v>
@@ -49435,21 +49435,21 @@
         <v>321</v>
       </c>
       <c r="E570">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="F570">
-        <v>0.30199999999999999</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="G570">
         <v>0.33123000000000002</v>
       </c>
       <c r="L570">
-        <v>0.57279671099999996</v>
+        <v>0.56989438640319556</v>
       </c>
     </row>
     <row r="571" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B571" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C571" t="s">
         <v>320</v>
@@ -49461,18 +49461,18 @@
         <v>2015</v>
       </c>
       <c r="F571">
-        <v>0.312</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="G571">
         <v>0.33123000000000002</v>
       </c>
       <c r="L571">
-        <v>0.553779154</v>
+        <v>0.4984996459547133</v>
       </c>
     </row>
     <row r="572" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B572" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C572" t="s">
         <v>320</v>
@@ -49481,21 +49481,21 @@
         <v>321</v>
       </c>
       <c r="E572">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="F572">
-        <v>0.33</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="G572">
         <v>0.33123000000000002</v>
       </c>
       <c r="L572">
-        <v>0.57442702300000004</v>
+        <v>0.55664824028154647</v>
       </c>
     </row>
     <row r="573" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B573" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C573" t="s">
         <v>320</v>
@@ -49504,21 +49504,21 @@
         <v>321</v>
       </c>
       <c r="E573">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F573">
-        <v>0.33200000000000002</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="G573">
         <v>0.33123000000000002</v>
       </c>
       <c r="L573">
-        <v>0.56071739600000003</v>
+        <v>0.57477504140417834</v>
       </c>
     </row>
     <row r="574" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B574" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C574" t="s">
         <v>320</v>
@@ -49527,21 +49527,21 @@
         <v>321</v>
       </c>
       <c r="E574">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="F574">
-        <v>0.34200000000000003</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="G574">
         <v>0.33123000000000002</v>
       </c>
       <c r="L574">
-        <v>0.57279671099999996</v>
+        <v>0.55664824028154647</v>
       </c>
     </row>
     <row r="575" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B575" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C575" t="s">
         <v>320</v>
@@ -49550,21 +49550,21 @@
         <v>321</v>
       </c>
       <c r="E575">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="F575">
-        <v>0.35</v>
+        <v>0.30199999999999999</v>
       </c>
       <c r="G575">
         <v>0.33123000000000002</v>
       </c>
       <c r="L575">
-        <v>0.53262292899999997</v>
+        <v>0.5657270300232291</v>
       </c>
     </row>
     <row r="576" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B576" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C576" t="s">
         <v>320</v>
@@ -49573,21 +49573,21 @@
         <v>321</v>
       </c>
       <c r="E576">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="F576">
-        <v>0.38400000000000001</v>
+        <v>0.312</v>
       </c>
       <c r="G576">
         <v>0.33123000000000002</v>
       </c>
       <c r="L576">
-        <v>0.53262292899999997</v>
+        <v>0.56070484516620278</v>
       </c>
     </row>
     <row r="577" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B577" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C577" t="s">
         <v>320</v>
@@ -49596,21 +49596,21 @@
         <v>321</v>
       </c>
       <c r="E577">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="F577">
-        <v>0.39600000000000002</v>
+        <v>0.33</v>
       </c>
       <c r="G577">
-        <v>0.33122999999999997</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L577">
-        <v>0.57868857299999998</v>
+        <v>0.56070484516620278</v>
       </c>
     </row>
     <row r="578" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B578" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C578" t="s">
         <v>320</v>
@@ -49619,21 +49619,21 @@
         <v>321</v>
       </c>
       <c r="E578">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="F578">
-        <v>0.4</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="G578">
         <v>0.33123000000000002</v>
       </c>
       <c r="L578">
-        <v>0.57868857299999998</v>
+        <v>0.55664824028154647</v>
       </c>
     </row>
     <row r="579" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B579" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C579" t="s">
         <v>320</v>
@@ -49642,21 +49642,21 @@
         <v>321</v>
       </c>
       <c r="E579">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F579">
-        <v>0.4</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="G579">
         <v>0.33123000000000002</v>
       </c>
       <c r="L579">
-        <v>0.58738256700000002</v>
+        <v>0.55479310155183892</v>
       </c>
     </row>
     <row r="580" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B580" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C580" t="s">
         <v>320</v>
@@ -49665,21 +49665,21 @@
         <v>321</v>
       </c>
       <c r="E580">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="F580">
-        <v>0.40200000000000002</v>
+        <v>0.35</v>
       </c>
       <c r="G580">
         <v>0.33123000000000002</v>
       </c>
       <c r="L580">
-        <v>0.57868857299999998</v>
+        <v>0.51308140128455437</v>
       </c>
     </row>
     <row r="581" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B581" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C581" t="s">
         <v>320</v>
@@ -49688,21 +49688,21 @@
         <v>321</v>
       </c>
       <c r="E581">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="F581">
-        <v>0.42</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="G581">
         <v>0.33123000000000002</v>
       </c>
       <c r="L581">
-        <v>0.553779154</v>
+        <v>0.51308140128455437</v>
       </c>
     </row>
     <row r="582" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B582" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C582" t="s">
         <v>320</v>
@@ -49714,18 +49714,18 @@
         <v>2019</v>
       </c>
       <c r="F582">
-        <v>0.45</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="G582">
-        <v>0.33123000000000002</v>
+        <v>0.33122999999999997</v>
       </c>
       <c r="L582">
-        <v>0.553779154</v>
+        <v>0.56070484516620278</v>
       </c>
     </row>
     <row r="583" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B583" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C583" t="s">
         <v>320</v>
@@ -49734,21 +49734,21 @@
         <v>321</v>
       </c>
       <c r="E583">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="F583">
-        <v>0.47599999999999998</v>
+        <v>0.4</v>
       </c>
       <c r="G583">
         <v>0.33123000000000002</v>
       </c>
       <c r="L583">
-        <v>0.51877992900000003</v>
+        <v>0.57259317315365765</v>
       </c>
     </row>
     <row r="584" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B584" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C584" t="s">
         <v>320</v>
@@ -49757,21 +49757,21 @@
         <v>321</v>
       </c>
       <c r="E584">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="F584">
-        <v>0.497</v>
+        <v>0.4</v>
       </c>
       <c r="G584">
         <v>0.33123000000000002</v>
       </c>
       <c r="L584">
-        <v>0.57868857299999998</v>
+        <v>0.57259317315365765</v>
       </c>
     </row>
     <row r="585" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B585" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C585" t="s">
         <v>320</v>
@@ -49780,21 +49780,21 @@
         <v>321</v>
       </c>
       <c r="E585">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="F585">
-        <v>0.03</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="G585">
         <v>0.33123000000000002</v>
       </c>
       <c r="L585">
-        <v>0.57868857299999987</v>
+        <v>0.57259317315365765</v>
       </c>
     </row>
     <row r="586" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B586" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C586" t="s">
         <v>320</v>
@@ -49803,21 +49803,21 @@
         <v>321</v>
       </c>
       <c r="E586">
-        <v>2010</v>
+        <v>2025</v>
       </c>
       <c r="F586">
-        <v>7.8E-2</v>
+        <v>0.42</v>
       </c>
       <c r="G586">
         <v>0.33123000000000002</v>
       </c>
       <c r="L586">
-        <v>0.52593486099999986</v>
+        <v>0.56070484516620278</v>
       </c>
     </row>
     <row r="587" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B587" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C587" t="s">
         <v>320</v>
@@ -49826,21 +49826,21 @@
         <v>321</v>
       </c>
       <c r="E587">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="F587">
-        <v>0.113</v>
+        <v>0.45</v>
       </c>
       <c r="G587">
-        <v>0.33123000000000008</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L587">
-        <v>0.553779154</v>
+        <v>0.56070484516620278</v>
       </c>
     </row>
     <row r="588" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B588" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C588" t="s">
         <v>320</v>
@@ -49849,16 +49849,16 @@
         <v>321</v>
       </c>
       <c r="E588">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="F588">
-        <v>0.111</v>
+        <v>0.47599999999999998</v>
       </c>
       <c r="G588">
         <v>0.33123000000000002</v>
       </c>
       <c r="L588">
-        <v>0.45533161300000002</v>
+        <v>0.51308140128455437</v>
       </c>
     </row>
     <row r="589" spans="2:12" x14ac:dyDescent="0.45">
@@ -49872,16 +49872,16 @@
         <v>321</v>
       </c>
       <c r="E589">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F589">
-        <v>0.112</v>
+        <v>0.497</v>
       </c>
       <c r="G589">
         <v>0.33123000000000002</v>
       </c>
       <c r="L589">
-        <v>0.58738256700000002</v>
+        <v>0.57011497424994284</v>
       </c>
     </row>
     <row r="590" spans="2:12" x14ac:dyDescent="0.45">
@@ -49904,7 +49904,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L590">
-        <v>0.33802250703984926</v>
+        <v>0.36687700880096002</v>
       </c>
     </row>
     <row r="591" spans="2:12" x14ac:dyDescent="0.45">
@@ -49927,7 +49927,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L591">
-        <v>0.47927322999999994</v>
+        <v>0.57960586277235726</v>
       </c>
     </row>
     <row r="592" spans="2:12" x14ac:dyDescent="0.45">
@@ -49950,7 +49950,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L592">
-        <v>0.27891074700000001</v>
+        <v>0.29345412456770209</v>
       </c>
     </row>
     <row r="593" spans="2:12" x14ac:dyDescent="0.45">
@@ -49973,7 +49973,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L593">
-        <v>0.556460866</v>
+        <v>0.57960586277235726</v>
       </c>
     </row>
     <row r="594" spans="2:12" x14ac:dyDescent="0.45">
@@ -49996,7 +49996,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L594">
-        <v>0.3782632267039473</v>
+        <v>0.40716942844871029</v>
       </c>
     </row>
     <row r="595" spans="2:12" x14ac:dyDescent="0.45">
@@ -50019,7 +50019,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L595">
-        <v>0.39424212022058819</v>
+        <v>0.44553220249489695</v>
       </c>
     </row>
     <row r="596" spans="2:12" x14ac:dyDescent="0.45">
@@ -50042,7 +50042,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L596">
-        <v>0.34978559211858978</v>
+        <v>0.39029394340867146</v>
       </c>
     </row>
     <row r="597" spans="2:12" x14ac:dyDescent="0.45">
@@ -50065,7 +50065,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L597">
-        <v>0.3706354114628253</v>
+        <v>0.40951176344477497</v>
       </c>
     </row>
     <row r="598" spans="2:12" x14ac:dyDescent="0.45">
@@ -50088,7 +50088,7 @@
         <v>0.33122999999999991</v>
       </c>
       <c r="L598">
-        <v>0.33803193122610925</v>
+        <v>0.36385657007974331</v>
       </c>
     </row>
     <row r="599" spans="2:12" x14ac:dyDescent="0.45">
@@ -50111,7 +50111,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L599">
-        <v>0.30941858547899836</v>
+        <v>0.33194161857526489</v>
       </c>
     </row>
     <row r="600" spans="2:12" x14ac:dyDescent="0.45">
@@ -50134,7 +50134,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L600">
-        <v>0.31823450098576522</v>
+        <v>0.33795595597789496</v>
       </c>
     </row>
     <row r="601" spans="2:12" x14ac:dyDescent="0.45">
@@ -50157,7 +50157,7 @@
         <v>0.33123000000000019</v>
       </c>
       <c r="L601">
-        <v>0.31696840105730129</v>
+        <v>0.33419644957508021</v>
       </c>
     </row>
     <row r="602" spans="2:12" x14ac:dyDescent="0.45">
@@ -50180,7 +50180,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L602">
-        <v>0.3037725052661564</v>
+        <v>0.31606196577783485</v>
       </c>
     </row>
     <row r="603" spans="2:12" x14ac:dyDescent="0.45">
@@ -50203,7 +50203,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L603">
-        <v>0.30731123640614783</v>
+        <v>0.32541181281028336</v>
       </c>
     </row>
     <row r="604" spans="2:12" x14ac:dyDescent="0.45">
@@ -50226,7 +50226,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L604">
-        <v>0.32862943673974088</v>
+        <v>0.35538857121279305</v>
       </c>
     </row>
     <row r="605" spans="2:12" x14ac:dyDescent="0.45">
@@ -50249,7 +50249,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L605">
-        <v>0.31900415108041241</v>
+        <v>0.34142238717273093</v>
       </c>
     </row>
     <row r="606" spans="2:12" x14ac:dyDescent="0.45">
@@ -50272,7 +50272,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L606">
-        <v>0.31958613712183537</v>
+        <v>0.3479140280040306</v>
       </c>
     </row>
     <row r="607" spans="2:12" x14ac:dyDescent="0.45">
@@ -50295,7 +50295,7 @@
         <v>0.33123000000000014</v>
       </c>
       <c r="L607">
-        <v>0.33165445322399995</v>
+        <v>0.36922972657268188</v>
       </c>
     </row>
     <row r="608" spans="2:12" x14ac:dyDescent="0.45">
@@ -50318,7 +50318,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L608">
-        <v>0.34142924835544419</v>
+        <v>0.36518333402274966</v>
       </c>
     </row>
     <row r="609" spans="2:12" x14ac:dyDescent="0.45">
@@ -50341,7 +50341,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L609">
-        <v>0.29599825899237614</v>
+        <v>0.32011608892000692</v>
       </c>
     </row>
     <row r="610" spans="2:12" x14ac:dyDescent="0.45">
@@ -50364,7 +50364,7 @@
         <v>0.33122999999999991</v>
       </c>
       <c r="L610">
-        <v>0.31916375905830718</v>
+        <v>0.3582768951118746</v>
       </c>
     </row>
     <row r="611" spans="2:12" x14ac:dyDescent="0.45">
@@ -50387,7 +50387,7 @@
         <v>0.33123000000000014</v>
       </c>
       <c r="L611">
-        <v>0.35677404768302162</v>
+        <v>0.39853219391201034</v>
       </c>
     </row>
     <row r="612" spans="2:12" x14ac:dyDescent="0.45">
@@ -50410,7 +50410,7 @@
         <v>0.33122999999999947</v>
       </c>
       <c r="L612">
-        <v>0.32756666922523542</v>
+        <v>0.36024764561507033</v>
       </c>
     </row>
     <row r="613" spans="2:12" x14ac:dyDescent="0.45">
@@ -50433,7 +50433,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L613">
-        <v>0.31701195220728284</v>
+        <v>0.34679697176819568</v>
       </c>
     </row>
     <row r="614" spans="2:12" x14ac:dyDescent="0.45">
@@ -50456,7 +50456,7 @@
         <v>0.33123000000000019</v>
       </c>
       <c r="L614">
-        <v>0.32504681279221576</v>
+        <v>0.35588338090206756</v>
       </c>
     </row>
     <row r="615" spans="2:12" x14ac:dyDescent="0.45">
@@ -50479,7 +50479,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L615">
-        <v>0.31722156359927373</v>
+        <v>0.33827571167071746</v>
       </c>
     </row>
     <row r="616" spans="2:12" x14ac:dyDescent="0.45">
@@ -50502,7 +50502,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L616">
-        <v>0.3049193016895162</v>
+        <v>0.32365249813066049</v>
       </c>
     </row>
     <row r="617" spans="2:12" x14ac:dyDescent="0.45">
@@ -50525,7 +50525,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L617">
-        <v>0.31586642105830909</v>
+        <v>0.33024606820967578</v>
       </c>
     </row>
     <row r="618" spans="2:12" x14ac:dyDescent="0.45">
@@ -50548,7 +50548,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L618">
-        <v>0.32067161331905369</v>
+        <v>0.33611265186546579</v>
       </c>
     </row>
     <row r="619" spans="2:12" x14ac:dyDescent="0.45">
@@ -50571,7 +50571,7 @@
         <v>0.33122999999999991</v>
       </c>
       <c r="L619">
-        <v>0.33597491714748196</v>
+        <v>0.36760833613165234</v>
       </c>
     </row>
     <row r="620" spans="2:12" x14ac:dyDescent="0.45">
@@ -50594,7 +50594,7 @@
         <v>0.33123000000000014</v>
       </c>
       <c r="L620">
-        <v>0.34363872932090916</v>
+        <v>0.38042509665852708</v>
       </c>
     </row>
     <row r="621" spans="2:12" x14ac:dyDescent="0.45">
@@ -50617,7 +50617,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L621">
-        <v>0.30971206985156258</v>
+        <v>0.33799693932688096</v>
       </c>
     </row>
     <row r="622" spans="2:12" x14ac:dyDescent="0.45">
@@ -50640,7 +50640,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L622">
-        <v>0.32539136420833337</v>
+        <v>0.35093753070228756</v>
       </c>
     </row>
     <row r="623" spans="2:12" x14ac:dyDescent="0.45">
@@ -50663,7 +50663,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L623">
-        <v>0.29817347171428571</v>
+        <v>0.30809767381603087</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D353704-AFFD-4C6E-88A4-E4486373B822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54381F5A-272B-49DB-82B1-5EA582A6CAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A5CAFA1C-E992-466F-AC23-D24AAB532E6C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BA9CF9B8-C9EC-41C9-8FBD-8632401E90D8}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3383,7 +3383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B18255-E7D9-4034-836C-C8E089E41BDD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74C255D7-4AB2-4AB4-BF37-03C22A3D4581}">
   <dimension ref="B9:T466"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24562,7 +24562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C71A075F-F0A2-4FE7-91C4-0AE4F067E64B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA72EA67-880A-4A68-829F-692F30D57056}">
   <dimension ref="B9:T623"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49099,7 +49099,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L555">
-        <v>0.5494511547454104</v>
+        <v>0.54945115474541029</v>
       </c>
     </row>
     <row r="556" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08EF5133-A130-4C0C-A786-AE6CE9258C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D070A169-980B-42D6-9D8E-35E3DB08C8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3A6D5BD9-4A80-44A1-847F-20D1B0DD523D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{043C9971-4161-4665-8CDA-8FE4993E3913}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2867,7 +2867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{310FE5CE-E1C7-421F-A3EC-DE2AE19C40DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEC9B473-78E2-4ACD-962B-421058620D44}">
   <dimension ref="B9:T281"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15744,7 +15744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6756F45-4896-42F9-895D-9C12CD88C2AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD8C76A-31BE-4C94-A7A4-29A6D438E996}">
   <dimension ref="B9:T438"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31496,7 +31496,7 @@
         <v>33</v>
       </c>
       <c r="L340">
-        <v>0.14414942289270036</v>
+        <v>0.14414942289270033</v>
       </c>
     </row>
     <row r="341" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D070A169-980B-42D6-9D8E-35E3DB08C8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{474305DA-899B-4501-9C0B-456FDE90F366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{043C9971-4161-4665-8CDA-8FE4993E3913}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EA8DCD04-FEAF-4876-9EE8-6BA5E9BCEF73}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2867,7 +2867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEC9B473-78E2-4ACD-962B-421058620D44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{951E6388-2381-4EE7-8A77-3B018DB399A1}">
   <dimension ref="B9:T281"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2946,19 +2946,19 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.27506149999999996</v>
+        <v>0.23684850000000002</v>
       </c>
       <c r="F11">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G11">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H11">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I11">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J11" t="s">
         <v>30</v>
@@ -3002,19 +3002,19 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.30462249999999996</v>
+        <v>0.26767125000000003</v>
       </c>
       <c r="F12">
-        <v>1726</v>
+        <v>1923</v>
       </c>
       <c r="G12">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="H12">
-        <v>2.5499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="I12">
-        <v>0.82269999999999999</v>
+        <v>0.80844999999999989</v>
       </c>
       <c r="J12" t="s">
         <v>31</v>
@@ -3058,19 +3058,19 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.13765950000000002</v>
+        <v>9.2996640000000019E-2</v>
       </c>
       <c r="F13">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G13">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H13">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I13">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J13" t="s">
         <v>32</v>
@@ -3114,19 +3114,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.13765950000000002</v>
+        <v>9.2996640000000019E-2</v>
       </c>
       <c r="F14">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G14">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H14">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I14">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J14" t="s">
         <v>33</v>
@@ -3170,19 +3170,19 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.30462249999999996</v>
+        <v>0.26767125000000003</v>
       </c>
       <c r="F15">
-        <v>1726</v>
+        <v>1923</v>
       </c>
       <c r="G15">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="H15">
-        <v>2.5499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="I15">
-        <v>0.82269999999999999</v>
+        <v>0.80844999999999989</v>
       </c>
       <c r="J15" t="s">
         <v>34</v>
@@ -3226,19 +3226,19 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.26720260000000001</v>
+        <v>0.23008140000000002</v>
       </c>
       <c r="F16">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G16">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H16">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I16">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J16" t="s">
         <v>35</v>
@@ -3282,19 +3282,19 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.26720260000000001</v>
+        <v>0.23008140000000002</v>
       </c>
       <c r="F17">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G17">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H17">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I17">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J17" t="s">
         <v>36</v>
@@ -3338,7 +3338,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>9.3936000000000006E-2</v>
+        <v>8.4542400000000018E-2</v>
       </c>
       <c r="F18">
         <v>3583</v>
@@ -3394,19 +3394,19 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.13765950000000002</v>
+        <v>9.2996640000000019E-2</v>
       </c>
       <c r="F19">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G19">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H19">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I19">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J19" t="s">
         <v>38</v>
@@ -3450,19 +3450,19 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.13765950000000002</v>
+        <v>9.2996640000000019E-2</v>
       </c>
       <c r="F20">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G20">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H20">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I20">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J20" t="s">
         <v>39</v>
@@ -3506,19 +3506,19 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.133488</v>
+        <v>9.0178560000000019E-2</v>
       </c>
       <c r="F21">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G21">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H21">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I21">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J21" t="s">
         <v>40</v>
@@ -3562,19 +3562,19 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.28292040000000002</v>
+        <v>0.24361560000000004</v>
       </c>
       <c r="F22">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G22">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H22">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I22">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J22" t="s">
         <v>41</v>
@@ -3618,7 +3618,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>9.3936000000000006E-2</v>
+        <v>8.4542400000000018E-2</v>
       </c>
       <c r="F23">
         <v>3583</v>
@@ -3674,7 +3674,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>9.3936000000000006E-2</v>
+        <v>8.4542400000000018E-2</v>
       </c>
       <c r="F24">
         <v>3583</v>
@@ -3730,19 +3730,19 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.30462249999999996</v>
+        <v>0.26767125000000008</v>
       </c>
       <c r="F25">
-        <v>1726</v>
+        <v>1923</v>
       </c>
       <c r="G25">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="H25">
-        <v>2.5499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="I25">
-        <v>0.82269999999999999</v>
+        <v>0.80844999999999989</v>
       </c>
       <c r="J25" t="s">
         <v>44</v>
@@ -3786,19 +3786,19 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.27506149999999996</v>
+        <v>0.23684850000000002</v>
       </c>
       <c r="F26">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G26">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H26">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I26">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J26" t="s">
         <v>45</v>
@@ -3842,19 +3842,19 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.27506149999999996</v>
+        <v>0.23684850000000002</v>
       </c>
       <c r="F27">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G27">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H27">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I27">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J27" t="s">
         <v>46</v>
@@ -3898,19 +3898,19 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.27506149999999996</v>
+        <v>0.23684850000000002</v>
       </c>
       <c r="F28">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G28">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H28">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I28">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J28" t="s">
         <v>47</v>
@@ -3954,19 +3954,19 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.27506149999999996</v>
+        <v>0.23684850000000002</v>
       </c>
       <c r="F29">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G29">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H29">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I29">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J29" t="s">
         <v>48</v>
@@ -4010,19 +4010,19 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.133488</v>
+        <v>9.0178560000000019E-2</v>
       </c>
       <c r="F30">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G30">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H30">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I30">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J30" t="s">
         <v>49</v>
@@ -4066,19 +4066,19 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.26720260000000001</v>
+        <v>0.23008140000000002</v>
       </c>
       <c r="F31">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G31">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H31">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I31">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J31" t="s">
         <v>50</v>
@@ -4122,19 +4122,19 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.26720260000000001</v>
+        <v>0.23008140000000002</v>
       </c>
       <c r="F32">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G32">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H32">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I32">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J32" t="s">
         <v>51</v>
@@ -4178,19 +4178,19 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.27506149999999996</v>
+        <v>0.23684850000000002</v>
       </c>
       <c r="F33">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G33">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H33">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I33">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J33" t="s">
         <v>52</v>
@@ -4234,19 +4234,19 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.28292040000000002</v>
+        <v>0.24361560000000002</v>
       </c>
       <c r="F34">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G34">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H34">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I34">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J34" t="s">
         <v>53</v>
@@ -4290,19 +4290,19 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.28292040000000002</v>
+        <v>0.24361560000000002</v>
       </c>
       <c r="F35">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G35">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H35">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I35">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J35" t="s">
         <v>54</v>
@@ -4346,19 +4346,19 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.133488</v>
+        <v>9.0178560000000019E-2</v>
       </c>
       <c r="F36">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G36">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H36">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I36">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J36" t="s">
         <v>55</v>
@@ -4402,19 +4402,19 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.133488</v>
+        <v>9.0178560000000019E-2</v>
       </c>
       <c r="F37">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G37">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H37">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I37">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J37" t="s">
         <v>56</v>
@@ -4458,19 +4458,19 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.17299880000000001</v>
+        <v>0.12764790000000001</v>
       </c>
       <c r="F38">
-        <v>2757</v>
+        <v>3144</v>
       </c>
       <c r="G38">
-        <v>39.200000000000003</v>
+        <v>43.8</v>
       </c>
       <c r="H38">
-        <v>3.35</v>
+        <v>3.94</v>
       </c>
       <c r="I38">
-        <v>0.63080000000000003</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J38" t="s">
         <v>57</v>
@@ -4514,19 +4514,19 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.13765950000000002</v>
+        <v>9.2996640000000033E-2</v>
       </c>
       <c r="F39">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G39">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H39">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I39">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J39" t="s">
         <v>58</v>
@@ -4570,19 +4570,19 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.13765950000000002</v>
+        <v>9.2996640000000033E-2</v>
       </c>
       <c r="F40">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G40">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H40">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I40">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J40" t="s">
         <v>59</v>
@@ -4626,7 +4626,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>9.3936000000000006E-2</v>
+        <v>8.4542400000000018E-2</v>
       </c>
       <c r="F41">
         <v>3583</v>
@@ -4682,7 +4682,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>9.3936000000000006E-2</v>
+        <v>8.4542400000000018E-2</v>
       </c>
       <c r="F42">
         <v>3583</v>
@@ -4738,7 +4738,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>9.3936000000000006E-2</v>
+        <v>8.4542400000000018E-2</v>
       </c>
       <c r="F43">
         <v>3583</v>
@@ -4794,19 +4794,19 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.29591900000000004</v>
+        <v>0.26002350000000002</v>
       </c>
       <c r="F44">
-        <v>1726</v>
+        <v>1923</v>
       </c>
       <c r="G44">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="H44">
-        <v>2.5499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="I44">
-        <v>0.82269999999999999</v>
+        <v>0.80844999999999989</v>
       </c>
       <c r="J44" t="s">
         <v>63</v>
@@ -4850,19 +4850,19 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.133488</v>
+        <v>9.0178560000000019E-2</v>
       </c>
       <c r="F45">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G45">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H45">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I45">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J45" t="s">
         <v>64</v>
@@ -4906,19 +4906,19 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.26720260000000001</v>
+        <v>0.23008140000000002</v>
       </c>
       <c r="F46">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G46">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H46">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I46">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J46" t="s">
         <v>65</v>
@@ -4962,19 +4962,19 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.26720260000000001</v>
+        <v>0.23008140000000002</v>
       </c>
       <c r="F47">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G47">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H47">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I47">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J47" t="s">
         <v>66</v>
@@ -5018,7 +5018,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.11272320000000002</v>
+        <v>0.10145088000000003</v>
       </c>
       <c r="F48">
         <v>3583</v>
@@ -5074,7 +5074,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.10332960000000004</v>
+        <v>9.2996640000000019E-2</v>
       </c>
       <c r="F49">
         <v>3583</v>
@@ -5130,7 +5130,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.10646080000000004</v>
+        <v>9.581472000000002E-2</v>
       </c>
       <c r="F50">
         <v>3583</v>
@@ -5186,7 +5186,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.10646080000000004</v>
+        <v>9.581472000000002E-2</v>
       </c>
       <c r="F51">
         <v>3583</v>
@@ -5242,7 +5242,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.10646080000000004</v>
+        <v>9.581472000000002E-2</v>
       </c>
       <c r="F52">
         <v>3583</v>
@@ -5298,7 +5298,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.10646080000000004</v>
+        <v>9.581472000000002E-2</v>
       </c>
       <c r="F53">
         <v>3583</v>
@@ -5354,7 +5354,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.10646080000000004</v>
+        <v>9.581472000000002E-2</v>
       </c>
       <c r="F54">
         <v>3583</v>
@@ -5410,7 +5410,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>0.10646080000000004</v>
+        <v>9.581472000000002E-2</v>
       </c>
       <c r="F55">
         <v>3583</v>
@@ -5466,7 +5466,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>0.10646080000000004</v>
+        <v>9.581472000000002E-2</v>
       </c>
       <c r="F56">
         <v>3583</v>
@@ -5522,7 +5522,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>0.10646080000000004</v>
+        <v>9.581472000000002E-2</v>
       </c>
       <c r="F57">
         <v>3583</v>
@@ -5578,7 +5578,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.19843979999999997</v>
+        <v>0.17859581999999999</v>
       </c>
       <c r="F58">
         <v>2757</v>
@@ -5634,7 +5634,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.33943649999999997</v>
+        <v>0.30549285000000004</v>
       </c>
       <c r="F59">
         <v>1726</v>
@@ -5690,7 +5690,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.29077929999999996</v>
+        <v>0.26170136999999999</v>
       </c>
       <c r="F60">
         <v>1967</v>
@@ -5746,7 +5746,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.29077930000000002</v>
+        <v>0.26170136999999999</v>
       </c>
       <c r="F61">
         <v>1967</v>
@@ -5802,7 +5802,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.33943649999999997</v>
+        <v>0.30549285000000004</v>
       </c>
       <c r="F62">
         <v>1726</v>
@@ -5858,7 +5858,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>0.33943649999999997</v>
+        <v>0.30549285000000004</v>
       </c>
       <c r="F63">
         <v>1726</v>
@@ -5914,7 +5914,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>0.30649709999999997</v>
+        <v>0.27584738999999997</v>
       </c>
       <c r="F64">
         <v>1967</v>
@@ -5970,7 +5970,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>0.33943649999999997</v>
+        <v>0.30549284999999998</v>
       </c>
       <c r="F65">
         <v>1726</v>
@@ -6026,7 +6026,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>0.33943649999999997</v>
+        <v>0.30549284999999998</v>
       </c>
       <c r="F66">
         <v>1726</v>
@@ -6082,7 +6082,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>0.30649709999999997</v>
+        <v>0.27584738999999997</v>
       </c>
       <c r="F67">
         <v>1967</v>
@@ -6138,7 +6138,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>0.29077929999999996</v>
+        <v>0.26170136999999999</v>
       </c>
       <c r="F68">
         <v>1967</v>
@@ -6194,7 +6194,7 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>0.34186214999999998</v>
+        <v>0.30767593500000001</v>
       </c>
       <c r="F69">
         <v>1967</v>
@@ -6250,7 +6250,7 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>0.37860224999999997</v>
+        <v>0.340742025</v>
       </c>
       <c r="F70">
         <v>1726</v>
@@ -6306,7 +6306,7 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>0.37860224999999997</v>
+        <v>0.340742025</v>
       </c>
       <c r="F71">
         <v>1726</v>
@@ -6362,7 +6362,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.37860224999999997</v>
+        <v>0.34074202500000006</v>
       </c>
       <c r="F72">
         <v>1726</v>
@@ -6418,7 +6418,7 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>0.37860224999999997</v>
+        <v>0.340742025</v>
       </c>
       <c r="F73">
         <v>1726</v>
@@ -6474,7 +6474,7 @@
         <v>14</v>
       </c>
       <c r="E74">
-        <v>0.37860224999999997</v>
+        <v>0.340742025</v>
       </c>
       <c r="F74">
         <v>1726</v>
@@ -6530,7 +6530,7 @@
         <v>14</v>
       </c>
       <c r="E75">
-        <v>0.36554699999999996</v>
+        <v>0.32899230000000002</v>
       </c>
       <c r="F75">
         <v>1726</v>
@@ -6586,7 +6586,7 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>0.37860224999999997</v>
+        <v>0.34074202500000006</v>
       </c>
       <c r="F76">
         <v>1726</v>
@@ -6642,7 +6642,7 @@
         <v>14</v>
       </c>
       <c r="E77">
-        <v>0.37860224999999997</v>
+        <v>0.340742025</v>
       </c>
       <c r="F77">
         <v>1726</v>
@@ -6698,7 +6698,7 @@
         <v>14</v>
       </c>
       <c r="E78">
-        <v>0.37860224999999997</v>
+        <v>0.340742025</v>
       </c>
       <c r="F78">
         <v>1726</v>
@@ -6754,7 +6754,7 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>0.450625</v>
+        <v>0.40556249999999999</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -6810,7 +6810,7 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>0.450625</v>
+        <v>0.40556250000000005</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -6866,7 +6866,7 @@
         <v>14</v>
       </c>
       <c r="E81">
-        <v>0.47315625000000006</v>
+        <v>0.42584062500000008</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -6922,7 +6922,7 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>0.450625</v>
+        <v>0.40556249999999999</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -6978,7 +6978,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0.450625</v>
+        <v>0.40556250000000005</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -7034,7 +7034,7 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <v>0.46865000000000007</v>
+        <v>0.42178500000000013</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -7090,7 +7090,7 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>0.49118125000000001</v>
+        <v>0.44206312500000011</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -7146,7 +7146,7 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>0.47315625000000006</v>
+        <v>0.42584062500000008</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -7202,7 +7202,7 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <v>0.46865000000000007</v>
+        <v>0.42178500000000002</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -7258,7 +7258,7 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.36050000000000004</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -7314,7 +7314,7 @@
         <v>14</v>
       </c>
       <c r="E89">
-        <v>0.36050000000000004</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -7370,7 +7370,7 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.49118125000000001</v>
+        <v>0.44206312500000011</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -7426,7 +7426,7 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.36050000000000004</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -7482,7 +7482,7 @@
         <v>14</v>
       </c>
       <c r="E92">
-        <v>0.36049999999999999</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -7538,7 +7538,7 @@
         <v>14</v>
       </c>
       <c r="E93">
-        <v>0.36050000000000004</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -7594,7 +7594,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.50470000000000004</v>
+        <v>0.45423000000000008</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -7650,7 +7650,7 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -7706,7 +7706,7 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.49118125000000001</v>
+        <v>0.44206312500000011</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -7762,7 +7762,7 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0.450625</v>
+        <v>0.40556249999999999</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -7818,7 +7818,7 @@
         <v>14</v>
       </c>
       <c r="E98">
-        <v>0.50470000000000004</v>
+        <v>0.45423000000000008</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -7874,7 +7874,7 @@
         <v>14</v>
       </c>
       <c r="E99">
-        <v>0.450625</v>
+        <v>0.40556249999999999</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -7930,7 +7930,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.49118125000000001</v>
+        <v>0.44206312500000011</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -7986,7 +7986,7 @@
         <v>14</v>
       </c>
       <c r="E101">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -8042,7 +8042,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -8098,7 +8098,7 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.450625</v>
+        <v>0.40556249999999999</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -8154,7 +8154,7 @@
         <v>14</v>
       </c>
       <c r="E104">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -8210,7 +8210,7 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.49118125000000001</v>
+        <v>0.44206312500000011</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -8266,7 +8266,7 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>0.47315625000000006</v>
+        <v>0.42584062500000008</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -8322,7 +8322,7 @@
         <v>14</v>
       </c>
       <c r="E107">
-        <v>0.36050000000000004</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -8378,7 +8378,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.47315625000000006</v>
+        <v>0.42584062500000008</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -8434,7 +8434,7 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>0.46865000000000007</v>
+        <v>0.42178500000000008</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -8490,7 +8490,7 @@
         <v>14</v>
       </c>
       <c r="E110">
-        <v>0.49118125000000001</v>
+        <v>0.44206312500000011</v>
       </c>
       <c r="F110">
         <v>1365</v>
@@ -8546,7 +8546,7 @@
         <v>14</v>
       </c>
       <c r="E111">
-        <v>0.34247500000000003</v>
+        <v>0.30822750000000004</v>
       </c>
       <c r="F111">
         <v>1365</v>
@@ -8602,7 +8602,7 @@
         <v>14</v>
       </c>
       <c r="E112">
-        <v>0.49118125000000001</v>
+        <v>0.44206312500000011</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -8658,7 +8658,7 @@
         <v>14</v>
       </c>
       <c r="E113">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -8714,7 +8714,7 @@
         <v>14</v>
       </c>
       <c r="E114">
-        <v>0.47315625000000006</v>
+        <v>0.42584062500000008</v>
       </c>
       <c r="F114">
         <v>1365</v>
@@ -8770,7 +8770,7 @@
         <v>14</v>
       </c>
       <c r="E115">
-        <v>0.50470000000000004</v>
+        <v>0.45423000000000008</v>
       </c>
       <c r="F115">
         <v>1365</v>
@@ -8826,7 +8826,7 @@
         <v>14</v>
       </c>
       <c r="E116">
-        <v>0.50470000000000004</v>
+        <v>0.45423000000000008</v>
       </c>
       <c r="F116">
         <v>1365</v>
@@ -8882,7 +8882,7 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>0.46865000000000007</v>
+        <v>0.42178500000000008</v>
       </c>
       <c r="F117">
         <v>1365</v>
@@ -8938,7 +8938,7 @@
         <v>14</v>
       </c>
       <c r="E118">
-        <v>0.49118125000000001</v>
+        <v>0.44206312500000011</v>
       </c>
       <c r="F118">
         <v>1365</v>
@@ -8994,7 +8994,7 @@
         <v>14</v>
       </c>
       <c r="E119">
-        <v>0.49118125000000001</v>
+        <v>0.44206312500000011</v>
       </c>
       <c r="F119">
         <v>1365</v>
@@ -9050,7 +9050,7 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>0.46865000000000007</v>
+        <v>0.42178500000000008</v>
       </c>
       <c r="F120">
         <v>1365</v>
@@ -9106,7 +9106,7 @@
         <v>14</v>
       </c>
       <c r="E121">
-        <v>0.50470000000000004</v>
+        <v>0.45423000000000008</v>
       </c>
       <c r="F121">
         <v>1365</v>
@@ -9162,7 +9162,7 @@
         <v>14</v>
       </c>
       <c r="E122">
-        <v>0.54075000000000006</v>
+        <v>0.48667500000000002</v>
       </c>
       <c r="F122">
         <v>1365</v>
@@ -9218,7 +9218,7 @@
         <v>14</v>
       </c>
       <c r="E123">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F123">
         <v>1365</v>
@@ -9274,7 +9274,7 @@
         <v>14</v>
       </c>
       <c r="E124">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F124">
         <v>1365</v>
@@ -9330,7 +9330,7 @@
         <v>14</v>
       </c>
       <c r="E125">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F125">
         <v>1365</v>
@@ -9386,7 +9386,7 @@
         <v>14</v>
       </c>
       <c r="E126">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F126">
         <v>1365</v>
@@ -9442,7 +9442,7 @@
         <v>14</v>
       </c>
       <c r="E127">
-        <v>0.36050000000000004</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="F127">
         <v>1365</v>
@@ -9498,7 +9498,7 @@
         <v>14</v>
       </c>
       <c r="E128">
-        <v>0.38753750000000003</v>
+        <v>0.34878375</v>
       </c>
       <c r="F128">
         <v>1365</v>
@@ -9554,7 +9554,7 @@
         <v>14</v>
       </c>
       <c r="E129">
-        <v>0.54075000000000006</v>
+        <v>0.48667500000000002</v>
       </c>
       <c r="F129">
         <v>1365</v>
@@ -9610,7 +9610,7 @@
         <v>14</v>
       </c>
       <c r="E130">
-        <v>0.36050000000000004</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="F130">
         <v>1365</v>
@@ -9666,7 +9666,7 @@
         <v>14</v>
       </c>
       <c r="E131">
-        <v>0.38753750000000003</v>
+        <v>0.34878375</v>
       </c>
       <c r="F131">
         <v>1365</v>
@@ -9722,7 +9722,7 @@
         <v>14</v>
       </c>
       <c r="E132">
-        <v>0.34247500000000003</v>
+        <v>0.30822750000000004</v>
       </c>
       <c r="F132">
         <v>1365</v>
@@ -9778,7 +9778,7 @@
         <v>14</v>
       </c>
       <c r="E133">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F133">
         <v>1365</v>
@@ -9834,7 +9834,7 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>0.54075000000000006</v>
+        <v>0.48667500000000002</v>
       </c>
       <c r="F134">
         <v>1365</v>
@@ -9890,7 +9890,7 @@
         <v>14</v>
       </c>
       <c r="E135">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F135">
         <v>1365</v>
@@ -9946,7 +9946,7 @@
         <v>14</v>
       </c>
       <c r="E136">
-        <v>0.34247500000000003</v>
+        <v>0.30822750000000004</v>
       </c>
       <c r="F136">
         <v>1365</v>
@@ -10002,7 +10002,7 @@
         <v>14</v>
       </c>
       <c r="E137">
-        <v>0.46865000000000007</v>
+        <v>0.42178500000000008</v>
       </c>
       <c r="F137">
         <v>1365</v>
@@ -10058,7 +10058,7 @@
         <v>14</v>
       </c>
       <c r="E138">
-        <v>0.54075000000000006</v>
+        <v>0.48667500000000002</v>
       </c>
       <c r="F138">
         <v>1365</v>
@@ -10114,7 +10114,7 @@
         <v>14</v>
       </c>
       <c r="E139">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F139">
         <v>1365</v>
@@ -10170,7 +10170,7 @@
         <v>14</v>
       </c>
       <c r="E140">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F140">
         <v>1365</v>
@@ -10226,7 +10226,7 @@
         <v>14</v>
       </c>
       <c r="E141">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F141">
         <v>1365</v>
@@ -10282,7 +10282,7 @@
         <v>14</v>
       </c>
       <c r="E142">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F142">
         <v>1365</v>
@@ -10338,7 +10338,7 @@
         <v>14</v>
       </c>
       <c r="E143">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F143">
         <v>1365</v>
@@ -10394,7 +10394,7 @@
         <v>14</v>
       </c>
       <c r="E144">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F144">
         <v>1365</v>
@@ -10450,7 +10450,7 @@
         <v>14</v>
       </c>
       <c r="E145">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F145">
         <v>1365</v>
@@ -10506,7 +10506,7 @@
         <v>14</v>
       </c>
       <c r="E146">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F146">
         <v>1365</v>
@@ -10562,7 +10562,7 @@
         <v>14</v>
       </c>
       <c r="E147">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F147">
         <v>1365</v>
@@ -10618,7 +10618,7 @@
         <v>14</v>
       </c>
       <c r="E148">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F148">
         <v>1365</v>
@@ -10674,7 +10674,7 @@
         <v>14</v>
       </c>
       <c r="E149">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F149">
         <v>1365</v>
@@ -10730,7 +10730,7 @@
         <v>14</v>
       </c>
       <c r="E150">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F150">
         <v>1365</v>
@@ -10786,7 +10786,7 @@
         <v>14</v>
       </c>
       <c r="E151">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F151">
         <v>1365</v>
@@ -10842,7 +10842,7 @@
         <v>14</v>
       </c>
       <c r="E152">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F152">
         <v>1365</v>
@@ -10898,7 +10898,7 @@
         <v>14</v>
       </c>
       <c r="E153">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F153">
         <v>1365</v>
@@ -10954,7 +10954,7 @@
         <v>14</v>
       </c>
       <c r="E154">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F154">
         <v>1365</v>
@@ -11010,7 +11010,7 @@
         <v>14</v>
       </c>
       <c r="E155">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F155">
         <v>1365</v>
@@ -11066,7 +11066,7 @@
         <v>14</v>
       </c>
       <c r="E156">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F156">
         <v>1365</v>
@@ -11122,7 +11122,7 @@
         <v>14</v>
       </c>
       <c r="E157">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F157">
         <v>1365</v>
@@ -11178,7 +11178,7 @@
         <v>14</v>
       </c>
       <c r="E158">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F158">
         <v>1365</v>
@@ -11234,7 +11234,7 @@
         <v>14</v>
       </c>
       <c r="E159">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F159">
         <v>1365</v>
@@ -11290,7 +11290,7 @@
         <v>14</v>
       </c>
       <c r="E160">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F160">
         <v>1365</v>
@@ -11346,7 +11346,7 @@
         <v>14</v>
       </c>
       <c r="E161">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F161">
         <v>1365</v>
@@ -11402,7 +11402,7 @@
         <v>14</v>
       </c>
       <c r="E162">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F162">
         <v>1365</v>
@@ -11458,7 +11458,7 @@
         <v>14</v>
       </c>
       <c r="E163">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F163">
         <v>1365</v>
@@ -11514,7 +11514,7 @@
         <v>14</v>
       </c>
       <c r="E164">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F164">
         <v>1365</v>
@@ -11570,7 +11570,7 @@
         <v>14</v>
       </c>
       <c r="E165">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F165">
         <v>1365</v>
@@ -11626,7 +11626,7 @@
         <v>14</v>
       </c>
       <c r="E166">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F166">
         <v>1365</v>
@@ -11682,7 +11682,7 @@
         <v>14</v>
       </c>
       <c r="E167">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F167">
         <v>1365</v>
@@ -11738,7 +11738,7 @@
         <v>14</v>
       </c>
       <c r="E168">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F168">
         <v>1365</v>
@@ -11794,7 +11794,7 @@
         <v>14</v>
       </c>
       <c r="E169">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F169">
         <v>1365</v>
@@ -11829,7 +11829,7 @@
         <v>14</v>
       </c>
       <c r="E170">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F170">
         <v>1365</v>
@@ -11864,7 +11864,7 @@
         <v>14</v>
       </c>
       <c r="E171">
-        <v>0.52272499999999988</v>
+        <v>0.47045249999999994</v>
       </c>
       <c r="F171">
         <v>1365</v>
@@ -11899,7 +11899,7 @@
         <v>14</v>
       </c>
       <c r="E172">
-        <v>0.2253125</v>
+        <v>0.20278125000000002</v>
       </c>
       <c r="F172">
         <v>1365</v>
@@ -11934,7 +11934,7 @@
         <v>14</v>
       </c>
       <c r="E173">
-        <v>0.21630000000000002</v>
+        <v>0.19467000000000001</v>
       </c>
       <c r="F173">
         <v>1365</v>
@@ -11969,7 +11969,7 @@
         <v>14</v>
       </c>
       <c r="E174">
-        <v>0.26136249999999994</v>
+        <v>0.23522624999999997</v>
       </c>
       <c r="F174">
         <v>1365</v>
@@ -12004,7 +12004,7 @@
         <v>14</v>
       </c>
       <c r="E175">
-        <v>0.26136249999999994</v>
+        <v>0.23522624999999997</v>
       </c>
       <c r="F175">
         <v>1365</v>
@@ -12039,7 +12039,7 @@
         <v>14</v>
       </c>
       <c r="E176">
-        <v>0.29741250000000002</v>
+        <v>0.26767125000000003</v>
       </c>
       <c r="F176">
         <v>1365</v>
@@ -12074,7 +12074,7 @@
         <v>14</v>
       </c>
       <c r="E177">
-        <v>0.29741250000000002</v>
+        <v>0.26767125000000003</v>
       </c>
       <c r="F177">
         <v>1365</v>
@@ -12109,7 +12109,7 @@
         <v>14</v>
       </c>
       <c r="E178">
-        <v>0.21629999999999999</v>
+        <v>0.19467000000000001</v>
       </c>
       <c r="F178">
         <v>1365</v>
@@ -12144,7 +12144,7 @@
         <v>14</v>
       </c>
       <c r="E179">
-        <v>0.28839999999999999</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="F179">
         <v>1365</v>
@@ -12179,7 +12179,7 @@
         <v>14</v>
       </c>
       <c r="E180">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F180">
         <v>1365</v>
@@ -12214,7 +12214,7 @@
         <v>14</v>
       </c>
       <c r="E181">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F181">
         <v>1365</v>
@@ -12249,7 +12249,7 @@
         <v>14</v>
       </c>
       <c r="E182">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F182">
         <v>1365</v>
@@ -12284,7 +12284,7 @@
         <v>14</v>
       </c>
       <c r="E183">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F183">
         <v>1365</v>
@@ -12319,7 +12319,7 @@
         <v>14</v>
       </c>
       <c r="E184">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F184">
         <v>1365</v>
@@ -12354,7 +12354,7 @@
         <v>14</v>
       </c>
       <c r="E185">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F185">
         <v>1365</v>
@@ -12389,7 +12389,7 @@
         <v>14</v>
       </c>
       <c r="E186">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F186">
         <v>1365</v>
@@ -12424,7 +12424,7 @@
         <v>14</v>
       </c>
       <c r="E187">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F187">
         <v>1365</v>
@@ -12459,7 +12459,7 @@
         <v>14</v>
       </c>
       <c r="E188">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F188">
         <v>1365</v>
@@ -12494,7 +12494,7 @@
         <v>14</v>
       </c>
       <c r="E189">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F189">
         <v>1365</v>
@@ -12529,7 +12529,7 @@
         <v>14</v>
       </c>
       <c r="E190">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F190">
         <v>1365</v>
@@ -12564,7 +12564,7 @@
         <v>14</v>
       </c>
       <c r="E191">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F191">
         <v>1365</v>
@@ -12599,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="E192">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F192">
         <v>1365</v>
@@ -12634,7 +12634,7 @@
         <v>14</v>
       </c>
       <c r="E193">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F193">
         <v>1365</v>
@@ -12669,7 +12669,7 @@
         <v>14</v>
       </c>
       <c r="E194">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F194">
         <v>1365</v>
@@ -12704,7 +12704,7 @@
         <v>14</v>
       </c>
       <c r="E195">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F195">
         <v>1365</v>
@@ -12739,7 +12739,7 @@
         <v>14</v>
       </c>
       <c r="E196">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F196">
         <v>1365</v>
@@ -12774,7 +12774,7 @@
         <v>14</v>
       </c>
       <c r="E197">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F197">
         <v>1365</v>
@@ -12809,7 +12809,7 @@
         <v>14</v>
       </c>
       <c r="E198">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F198">
         <v>1365</v>
@@ -12844,7 +12844,7 @@
         <v>14</v>
       </c>
       <c r="E199">
-        <v>0.28222392131979701</v>
+        <v>0.25400152918781727</v>
       </c>
       <c r="F199">
         <v>1365</v>
@@ -12879,7 +12879,7 @@
         <v>14</v>
       </c>
       <c r="E200">
-        <v>0.31994374999999997</v>
+        <v>0.28794937499999995</v>
       </c>
       <c r="F200">
         <v>1365</v>
@@ -12914,7 +12914,7 @@
         <v>14</v>
       </c>
       <c r="E201">
-        <v>0.32445000000000007</v>
+        <v>0.29200500000000007</v>
       </c>
       <c r="F201">
         <v>1365</v>
@@ -12949,7 +12949,7 @@
         <v>14</v>
       </c>
       <c r="E202">
-        <v>0.32445000000000007</v>
+        <v>0.29200500000000007</v>
       </c>
       <c r="F202">
         <v>1365</v>
@@ -12984,7 +12984,7 @@
         <v>14</v>
       </c>
       <c r="E203">
-        <v>0.32445000000000007</v>
+        <v>0.29200500000000007</v>
       </c>
       <c r="F203">
         <v>1365</v>
@@ -13019,7 +13019,7 @@
         <v>14</v>
       </c>
       <c r="E204">
-        <v>0.32445000000000007</v>
+        <v>0.29200500000000007</v>
       </c>
       <c r="F204">
         <v>1365</v>
@@ -13054,7 +13054,7 @@
         <v>14</v>
       </c>
       <c r="E205">
-        <v>0.32445000000000007</v>
+        <v>0.29200500000000007</v>
       </c>
       <c r="F205">
         <v>1365</v>
@@ -13089,7 +13089,7 @@
         <v>14</v>
       </c>
       <c r="E206">
-        <v>0.32445000000000007</v>
+        <v>0.29200500000000007</v>
       </c>
       <c r="F206">
         <v>1365</v>
@@ -13124,7 +13124,7 @@
         <v>14</v>
       </c>
       <c r="E207">
-        <v>0.32445000000000007</v>
+        <v>0.29200500000000007</v>
       </c>
       <c r="F207">
         <v>1365</v>
@@ -13159,7 +13159,7 @@
         <v>14</v>
       </c>
       <c r="E208">
-        <v>0.32445000000000007</v>
+        <v>0.29200500000000007</v>
       </c>
       <c r="F208">
         <v>1365</v>
@@ -13194,7 +13194,7 @@
         <v>14</v>
       </c>
       <c r="E209">
-        <v>0.32445000000000007</v>
+        <v>0.29200500000000007</v>
       </c>
       <c r="F209">
         <v>1365</v>
@@ -13229,7 +13229,7 @@
         <v>14</v>
       </c>
       <c r="E210">
-        <v>0.32445000000000007</v>
+        <v>0.29200500000000007</v>
       </c>
       <c r="F210">
         <v>1365</v>
@@ -13264,7 +13264,7 @@
         <v>14</v>
       </c>
       <c r="E211">
-        <v>0.32445000000000007</v>
+        <v>0.29200500000000007</v>
       </c>
       <c r="F211">
         <v>1365</v>
@@ -13299,7 +13299,7 @@
         <v>14</v>
       </c>
       <c r="E212">
-        <v>0.32445000000000007</v>
+        <v>0.29200500000000007</v>
       </c>
       <c r="F212">
         <v>1365</v>
@@ -13334,7 +13334,7 @@
         <v>14</v>
       </c>
       <c r="E213">
-        <v>0.31093124999999999</v>
+        <v>0.27983812500000005</v>
       </c>
       <c r="F213">
         <v>1365</v>
@@ -13369,7 +13369,7 @@
         <v>14</v>
       </c>
       <c r="E214">
-        <v>0.32895625000000001</v>
+        <v>0.29606062500000002</v>
       </c>
       <c r="F214">
         <v>1365</v>
@@ -13404,7 +13404,7 @@
         <v>14</v>
       </c>
       <c r="E215">
-        <v>0.29741250000000002</v>
+        <v>0.26767125000000003</v>
       </c>
       <c r="F215">
         <v>1365</v>
@@ -13439,7 +13439,7 @@
         <v>14</v>
       </c>
       <c r="E216">
-        <v>0.29741250000000002</v>
+        <v>0.26767125000000008</v>
       </c>
       <c r="F216">
         <v>1365</v>
@@ -13474,7 +13474,7 @@
         <v>14</v>
       </c>
       <c r="E217">
-        <v>0.29741250000000002</v>
+        <v>0.26767125000000003</v>
       </c>
       <c r="F217">
         <v>1365</v>
@@ -13509,7 +13509,7 @@
         <v>14</v>
       </c>
       <c r="E218">
-        <v>0.306425</v>
+        <v>0.27578249999999999</v>
       </c>
       <c r="F218">
         <v>1365</v>
@@ -13544,7 +13544,7 @@
         <v>14</v>
       </c>
       <c r="E219">
-        <v>0.306425</v>
+        <v>0.27578249999999999</v>
       </c>
       <c r="F219">
         <v>1365</v>
@@ -13579,7 +13579,7 @@
         <v>14</v>
       </c>
       <c r="E220">
-        <v>0.29741250000000002</v>
+        <v>0.26767125000000003</v>
       </c>
       <c r="F220">
         <v>1365</v>
@@ -13614,7 +13614,7 @@
         <v>14</v>
       </c>
       <c r="E221">
-        <v>0.29741250000000002</v>
+        <v>0.26767125000000003</v>
       </c>
       <c r="F221">
         <v>1365</v>
@@ -13649,7 +13649,7 @@
         <v>14</v>
       </c>
       <c r="E222">
-        <v>0.27037500000000003</v>
+        <v>0.24333750000000001</v>
       </c>
       <c r="F222">
         <v>1365</v>
@@ -13684,7 +13684,7 @@
         <v>14</v>
       </c>
       <c r="E223">
-        <v>0.306425</v>
+        <v>0.27578249999999999</v>
       </c>
       <c r="F223">
         <v>1365</v>
@@ -13719,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="E224">
-        <v>0.29741250000000002</v>
+        <v>0.26767125000000003</v>
       </c>
       <c r="F224">
         <v>1365</v>
@@ -13754,7 +13754,7 @@
         <v>14</v>
       </c>
       <c r="E225">
-        <v>0.31093124999999999</v>
+        <v>0.27983812500000005</v>
       </c>
       <c r="F225">
         <v>1365</v>
@@ -13789,7 +13789,7 @@
         <v>14</v>
       </c>
       <c r="E226">
-        <v>0.26136249999999994</v>
+        <v>0.23522624999999997</v>
       </c>
       <c r="F226">
         <v>1365</v>
@@ -13824,7 +13824,7 @@
         <v>14</v>
       </c>
       <c r="E227">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F227">
         <v>1365</v>
@@ -13859,7 +13859,7 @@
         <v>14</v>
       </c>
       <c r="E228">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F228">
         <v>1365</v>
@@ -13894,7 +13894,7 @@
         <v>14</v>
       </c>
       <c r="E229">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F229">
         <v>1365</v>
@@ -13929,7 +13929,7 @@
         <v>14</v>
       </c>
       <c r="E230">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F230">
         <v>1365</v>
@@ -13964,7 +13964,7 @@
         <v>14</v>
       </c>
       <c r="E231">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F231">
         <v>1365</v>
@@ -13999,7 +13999,7 @@
         <v>14</v>
       </c>
       <c r="E232">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F232">
         <v>1365</v>
@@ -14034,7 +14034,7 @@
         <v>14</v>
       </c>
       <c r="E233">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F233">
         <v>1365</v>
@@ -14069,7 +14069,7 @@
         <v>14</v>
       </c>
       <c r="E234">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F234">
         <v>1365</v>
@@ -14104,7 +14104,7 @@
         <v>14</v>
       </c>
       <c r="E235">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F235">
         <v>1365</v>
@@ -14139,7 +14139,7 @@
         <v>14</v>
       </c>
       <c r="E236">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F236">
         <v>1365</v>
@@ -14174,7 +14174,7 @@
         <v>14</v>
       </c>
       <c r="E237">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F237">
         <v>1365</v>
@@ -14209,7 +14209,7 @@
         <v>14</v>
       </c>
       <c r="E238">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F238">
         <v>1365</v>
@@ -14244,7 +14244,7 @@
         <v>14</v>
       </c>
       <c r="E239">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F239">
         <v>1365</v>
@@ -14279,7 +14279,7 @@
         <v>14</v>
       </c>
       <c r="E240">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F240">
         <v>1365</v>
@@ -14314,7 +14314,7 @@
         <v>14</v>
       </c>
       <c r="E241">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F241">
         <v>1365</v>
@@ -14349,7 +14349,7 @@
         <v>14</v>
       </c>
       <c r="E242">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F242">
         <v>1365</v>
@@ -14384,7 +14384,7 @@
         <v>14</v>
       </c>
       <c r="E243">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F243">
         <v>1365</v>
@@ -14419,7 +14419,7 @@
         <v>14</v>
       </c>
       <c r="E244">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F244">
         <v>1365</v>
@@ -14454,7 +14454,7 @@
         <v>14</v>
       </c>
       <c r="E245">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F245">
         <v>1365</v>
@@ -14489,7 +14489,7 @@
         <v>14</v>
       </c>
       <c r="E246">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F246">
         <v>1365</v>
@@ -14524,7 +14524,7 @@
         <v>14</v>
       </c>
       <c r="E247">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F247">
         <v>1365</v>
@@ -14559,7 +14559,7 @@
         <v>14</v>
       </c>
       <c r="E248">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F248">
         <v>1365</v>
@@ -14594,7 +14594,7 @@
         <v>14</v>
       </c>
       <c r="E249">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F249">
         <v>1365</v>
@@ -14629,7 +14629,7 @@
         <v>14</v>
       </c>
       <c r="E250">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F250">
         <v>1365</v>
@@ -14664,7 +14664,7 @@
         <v>14</v>
       </c>
       <c r="E251">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F251">
         <v>1365</v>
@@ -14699,7 +14699,7 @@
         <v>14</v>
       </c>
       <c r="E252">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F252">
         <v>1365</v>
@@ -14734,7 +14734,7 @@
         <v>14</v>
       </c>
       <c r="E253">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F253">
         <v>1365</v>
@@ -14769,7 +14769,7 @@
         <v>14</v>
       </c>
       <c r="E254">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F254">
         <v>1365</v>
@@ -14804,7 +14804,7 @@
         <v>14</v>
       </c>
       <c r="E255">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F255">
         <v>1365</v>
@@ -14839,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="E256">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F256">
         <v>1365</v>
@@ -14874,7 +14874,7 @@
         <v>14</v>
       </c>
       <c r="E257">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F257">
         <v>1365</v>
@@ -14909,7 +14909,7 @@
         <v>14</v>
       </c>
       <c r="E258">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F258">
         <v>1365</v>
@@ -14944,7 +14944,7 @@
         <v>14</v>
       </c>
       <c r="E259">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F259">
         <v>1365</v>
@@ -14979,7 +14979,7 @@
         <v>14</v>
       </c>
       <c r="E260">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F260">
         <v>1365</v>
@@ -15014,7 +15014,7 @@
         <v>14</v>
       </c>
       <c r="E261">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F261">
         <v>1365</v>
@@ -15049,7 +15049,7 @@
         <v>14</v>
       </c>
       <c r="E262">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F262">
         <v>1365</v>
@@ -15084,7 +15084,7 @@
         <v>14</v>
       </c>
       <c r="E263">
-        <v>0.30846207191780817</v>
+        <v>0.27761586472602745</v>
       </c>
       <c r="F263">
         <v>1365</v>
@@ -15119,7 +15119,7 @@
         <v>14</v>
       </c>
       <c r="E264">
-        <v>0.32445000000000002</v>
+        <v>0.29200500000000001</v>
       </c>
       <c r="F264">
         <v>1365</v>
@@ -15154,7 +15154,7 @@
         <v>14</v>
       </c>
       <c r="E265">
-        <v>0.43259999999999998</v>
+        <v>0.38934000000000002</v>
       </c>
       <c r="F265">
         <v>1365</v>
@@ -15189,7 +15189,7 @@
         <v>14</v>
       </c>
       <c r="E266">
-        <v>0.48667500000000002</v>
+        <v>0.43800749999999999</v>
       </c>
       <c r="F266">
         <v>1365</v>
@@ -15224,7 +15224,7 @@
         <v>14</v>
       </c>
       <c r="E267">
-        <v>0.43260000000000004</v>
+        <v>0.38934000000000002</v>
       </c>
       <c r="F267">
         <v>1365</v>
@@ -15259,7 +15259,7 @@
         <v>14</v>
       </c>
       <c r="E268">
-        <v>0.43260000000000004</v>
+        <v>0.38934000000000002</v>
       </c>
       <c r="F268">
         <v>1365</v>
@@ -15294,7 +15294,7 @@
         <v>14</v>
       </c>
       <c r="E269">
-        <v>0.43260000000000004</v>
+        <v>0.38934000000000002</v>
       </c>
       <c r="F269">
         <v>1365</v>
@@ -15329,7 +15329,7 @@
         <v>14</v>
       </c>
       <c r="E270">
-        <v>0.21629999999999999</v>
+        <v>0.19467000000000001</v>
       </c>
       <c r="F270">
         <v>1365</v>
@@ -15364,7 +15364,7 @@
         <v>14</v>
       </c>
       <c r="E271">
-        <v>0.18025000000000002</v>
+        <v>0.16222500000000001</v>
       </c>
       <c r="F271">
         <v>1365</v>
@@ -15399,7 +15399,7 @@
         <v>14</v>
       </c>
       <c r="E272">
-        <v>0.26136249999999994</v>
+        <v>0.23522624999999997</v>
       </c>
       <c r="F272">
         <v>1365</v>
@@ -15434,7 +15434,7 @@
         <v>14</v>
       </c>
       <c r="E273">
-        <v>0.26136249999999994</v>
+        <v>0.23522624999999997</v>
       </c>
       <c r="F273">
         <v>1365</v>
@@ -15469,7 +15469,7 @@
         <v>14</v>
       </c>
       <c r="E274">
-        <v>0.26136249999999994</v>
+        <v>0.23522624999999997</v>
       </c>
       <c r="F274">
         <v>1365</v>
@@ -15504,7 +15504,7 @@
         <v>14</v>
       </c>
       <c r="E275">
-        <v>0.26136249999999994</v>
+        <v>0.23522624999999997</v>
       </c>
       <c r="F275">
         <v>1365</v>
@@ -15539,7 +15539,7 @@
         <v>14</v>
       </c>
       <c r="E276">
-        <v>0.27488125000000002</v>
+        <v>0.24739312499999999</v>
       </c>
       <c r="F276">
         <v>1365</v>
@@ -15574,7 +15574,7 @@
         <v>14</v>
       </c>
       <c r="E277">
-        <v>0.31994374999999997</v>
+        <v>0.28794937499999995</v>
       </c>
       <c r="F277">
         <v>1365</v>
@@ -15609,7 +15609,7 @@
         <v>14</v>
       </c>
       <c r="E278">
-        <v>0.30191875000000001</v>
+        <v>0.27172687500000003</v>
       </c>
       <c r="F278">
         <v>1365</v>
@@ -15644,7 +15644,7 @@
         <v>14</v>
       </c>
       <c r="E279">
-        <v>0.30191875000000001</v>
+        <v>0.27172687500000003</v>
       </c>
       <c r="F279">
         <v>1365</v>
@@ -15679,7 +15679,7 @@
         <v>14</v>
       </c>
       <c r="E280">
-        <v>0.30191875000000001</v>
+        <v>0.27172687500000003</v>
       </c>
       <c r="F280">
         <v>1365</v>
@@ -15714,7 +15714,7 @@
         <v>14</v>
       </c>
       <c r="E281">
-        <v>0.30191875000000001</v>
+        <v>0.27172687500000003</v>
       </c>
       <c r="F281">
         <v>1365</v>
@@ -15744,7 +15744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD8C76A-31BE-4C94-A7A4-29A6D438E996}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97889FDA-DA1A-4AF5-9FCA-9B16D13B4126}">
   <dimension ref="B9:T438"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15829,7 +15829,7 @@
         <v>0.04</v>
       </c>
       <c r="G11">
-        <v>0.25235000000000002</v>
+        <v>0.22711500000000001</v>
       </c>
       <c r="H11">
         <v>5197.5</v>
@@ -15882,7 +15882,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G12">
-        <v>0.25235000000000002</v>
+        <v>0.22711500000000004</v>
       </c>
       <c r="H12">
         <v>5197.5</v>
@@ -15935,7 +15935,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="G13">
-        <v>0.28840000000000005</v>
+        <v>0.25956000000000007</v>
       </c>
       <c r="H13">
         <v>5197.5</v>
@@ -15988,7 +15988,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G14">
-        <v>0.28840000000000005</v>
+        <v>0.25956000000000007</v>
       </c>
       <c r="H14">
         <v>5197.5</v>
@@ -16041,7 +16041,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="G15">
-        <v>0.28840000000000005</v>
+        <v>0.25956000000000007</v>
       </c>
       <c r="H15">
         <v>5197.5</v>
@@ -16094,7 +16094,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="G16">
-        <v>0.28840000000000005</v>
+        <v>0.25956000000000007</v>
       </c>
       <c r="H16">
         <v>5197.5</v>
@@ -16147,7 +16147,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="G17">
-        <v>0.28840000000000005</v>
+        <v>0.25956000000000007</v>
       </c>
       <c r="H17">
         <v>5197.5</v>
@@ -16200,7 +16200,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G18">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H18">
         <v>5197.5</v>
@@ -16253,7 +16253,7 @@
         <v>0.04</v>
       </c>
       <c r="G19">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H19">
         <v>5197.5</v>
@@ -16306,7 +16306,7 @@
         <v>8.777000000000001</v>
       </c>
       <c r="G20">
-        <v>0.36049999999999999</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="H20">
         <v>3850</v>
@@ -16359,7 +16359,7 @@
         <v>0.05</v>
       </c>
       <c r="G21">
-        <v>0.18539999999999998</v>
+        <v>0.16686000000000001</v>
       </c>
       <c r="H21">
         <v>5197.5</v>
@@ -16412,7 +16412,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G22">
-        <v>0.27295000000000003</v>
+        <v>0.24565500000000004</v>
       </c>
       <c r="H22">
         <v>4427.5</v>
@@ -16465,7 +16465,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G23">
-        <v>0.27295000000000003</v>
+        <v>0.24565500000000004</v>
       </c>
       <c r="H23">
         <v>4427.5</v>
@@ -16518,7 +16518,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="G24">
-        <v>0.27295000000000003</v>
+        <v>0.24565500000000004</v>
       </c>
       <c r="H24">
         <v>4427.5</v>
@@ -16571,7 +16571,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G25">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H25">
         <v>4427.5</v>
@@ -16624,7 +16624,7 @@
         <v>0.05</v>
       </c>
       <c r="G26">
-        <v>0.2369</v>
+        <v>0.21321000000000004</v>
       </c>
       <c r="H26">
         <v>5197.5</v>
@@ -16677,7 +16677,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G27">
-        <v>0.23690000000000005</v>
+        <v>0.21321000000000004</v>
       </c>
       <c r="H27">
         <v>4427.5</v>
@@ -16730,7 +16730,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G28">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H28">
         <v>4427.5</v>
@@ -16783,7 +16783,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G29">
-        <v>0.27295000000000003</v>
+        <v>0.24565500000000004</v>
       </c>
       <c r="H29">
         <v>4427.5</v>
@@ -16836,7 +16836,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="G30">
-        <v>0.31930000000000003</v>
+        <v>0.28737000000000001</v>
       </c>
       <c r="H30">
         <v>4427.5</v>
@@ -16889,7 +16889,7 @@
         <v>0.1</v>
       </c>
       <c r="G31">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H31">
         <v>4427.5</v>
@@ -16942,7 +16942,7 @@
         <v>4.82E-2</v>
       </c>
       <c r="G32">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H32">
         <v>2970.0000000000005</v>
@@ -16995,7 +16995,7 @@
         <v>4.82E-2</v>
       </c>
       <c r="G33">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H33">
         <v>2970.0000000000005</v>
@@ -17048,7 +17048,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="G34">
-        <v>0.33559890109890111</v>
+        <v>0.30203901098901098</v>
       </c>
       <c r="H34">
         <v>2713.7362637362639</v>
@@ -17101,7 +17101,7 @@
         <v>0.14399999999999999</v>
       </c>
       <c r="G35">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H35">
         <v>2530</v>
@@ -17154,7 +17154,7 @@
         <v>0.16</v>
       </c>
       <c r="G36">
-        <v>0.33989999999999998</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H36">
         <v>2530</v>
@@ -17207,7 +17207,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G37">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H37">
         <v>2530</v>
@@ -17260,7 +17260,7 @@
         <v>0.107</v>
       </c>
       <c r="G38">
-        <v>0.34721588785046731</v>
+        <v>0.31249429906542059</v>
       </c>
       <c r="H38">
         <v>2657.4766355140187</v>
@@ -17313,7 +17313,7 @@
         <v>3.7399999999999996E-2</v>
       </c>
       <c r="G39">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H39">
         <v>2970.0000000000005</v>
@@ -17366,7 +17366,7 @@
         <v>8.0874999999999986</v>
       </c>
       <c r="G40">
-        <v>0.37080000000000002</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H40">
         <v>2200</v>
@@ -17419,7 +17419,7 @@
         <v>0.433</v>
       </c>
       <c r="G41">
-        <v>0.36049999999999999</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="H41">
         <v>2200</v>
@@ -17472,7 +17472,7 @@
         <v>0.78</v>
       </c>
       <c r="G42">
-        <v>0.36049999999999999</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="H42">
         <v>2200</v>
@@ -17525,7 +17525,7 @@
         <v>0.3</v>
       </c>
       <c r="G43">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H43">
         <v>2530</v>
@@ -17578,7 +17578,7 @@
         <v>0.3</v>
       </c>
       <c r="G44">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H44">
         <v>2530</v>
@@ -17631,7 +17631,7 @@
         <v>0.78</v>
       </c>
       <c r="G45">
-        <v>0.36049999999999999</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="H45">
         <v>2200</v>
@@ -17684,7 +17684,7 @@
         <v>0.5</v>
       </c>
       <c r="G46">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H46">
         <v>2200</v>
@@ -17737,7 +17737,7 @@
         <v>0.5</v>
       </c>
       <c r="G47">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H47">
         <v>2200</v>
@@ -17790,7 +17790,7 @@
         <v>0.112</v>
       </c>
       <c r="G48">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H48">
         <v>2530</v>
@@ -17843,7 +17843,7 @@
         <v>0.15</v>
       </c>
       <c r="G49">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H49">
         <v>2530</v>
@@ -17896,7 +17896,7 @@
         <v>0.15</v>
       </c>
       <c r="G50">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H50">
         <v>2530</v>
@@ -17949,7 +17949,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G51">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H51">
         <v>2530</v>
@@ -18002,7 +18002,7 @@
         <v>0.48</v>
       </c>
       <c r="G52">
-        <v>0.37080000000000002</v>
+        <v>0.33372000000000007</v>
       </c>
       <c r="H52">
         <v>2200</v>
@@ -18055,7 +18055,7 @@
         <v>0.125</v>
       </c>
       <c r="G53">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H53">
         <v>2530</v>
@@ -18108,7 +18108,7 @@
         <v>0.125</v>
       </c>
       <c r="G54">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H54">
         <v>2530</v>
@@ -18161,7 +18161,7 @@
         <v>0.81599999999999995</v>
       </c>
       <c r="G55">
-        <v>0.36049999999999999</v>
+        <v>0.32445000000000007</v>
       </c>
       <c r="H55">
         <v>2200</v>
@@ -18214,7 +18214,7 @@
         <v>0.53500000000000003</v>
       </c>
       <c r="G56">
-        <v>0.36049999999999999</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="H56">
         <v>2200</v>
@@ -18267,7 +18267,7 @@
         <v>0.53500000000000003</v>
       </c>
       <c r="G57">
-        <v>0.36049999999999999</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="H57">
         <v>2200</v>
@@ -18320,7 +18320,7 @@
         <v>0.53500000000000003</v>
       </c>
       <c r="G58">
-        <v>0.36049999999999999</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="H58">
         <v>2200</v>
@@ -18373,7 +18373,7 @@
         <v>0.53500000000000003</v>
       </c>
       <c r="G59">
-        <v>0.36049999999999999</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="H59">
         <v>2200</v>
@@ -18426,7 +18426,7 @@
         <v>0.12</v>
       </c>
       <c r="G60">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H60">
         <v>2530</v>
@@ -18479,7 +18479,7 @@
         <v>0.63</v>
       </c>
       <c r="G61">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H61">
         <v>2200</v>
@@ -18532,7 +18532,7 @@
         <v>0.63600000000000001</v>
       </c>
       <c r="G62">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H62">
         <v>2200</v>
@@ -18585,7 +18585,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G63">
-        <v>0.36049999999999999</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="H63">
         <v>2200</v>
@@ -18638,7 +18638,7 @@
         <v>0.49</v>
       </c>
       <c r="G64">
-        <v>0.37080000000000002</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H64">
         <v>2200</v>
@@ -18691,7 +18691,7 @@
         <v>0.49</v>
       </c>
       <c r="G65">
-        <v>0.37080000000000002</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H65">
         <v>2200</v>
@@ -18744,7 +18744,7 @@
         <v>0.37</v>
       </c>
       <c r="G66">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H66">
         <v>2200</v>
@@ -18797,7 +18797,7 @@
         <v>0.37</v>
       </c>
       <c r="G67">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H67">
         <v>2200</v>
@@ -18850,7 +18850,7 @@
         <v>0.20499999999999999</v>
       </c>
       <c r="G68">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H68">
         <v>2530</v>
@@ -18903,7 +18903,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="G69">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000007</v>
       </c>
       <c r="H69">
         <v>2530</v>
@@ -18956,7 +18956,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="G70">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000007</v>
       </c>
       <c r="H70">
         <v>2530</v>
@@ -19009,7 +19009,7 @@
         <v>0.16</v>
       </c>
       <c r="G71">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H71">
         <v>2530</v>
@@ -19062,7 +19062,7 @@
         <v>0.151</v>
       </c>
       <c r="G72">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H72">
         <v>2530</v>
@@ -19115,7 +19115,7 @@
         <v>0.13869999999999999</v>
       </c>
       <c r="G73">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H73">
         <v>2530</v>
@@ -19168,7 +19168,7 @@
         <v>0.72399999999999998</v>
       </c>
       <c r="G74">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H74">
         <v>2200</v>
@@ -19221,7 +19221,7 @@
         <v>0.34</v>
       </c>
       <c r="G75">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H75">
         <v>2200</v>
@@ -19274,7 +19274,7 @@
         <v>0.63</v>
       </c>
       <c r="G76">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H76">
         <v>2200</v>
@@ -19327,7 +19327,7 @@
         <v>0.625</v>
       </c>
       <c r="G77">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H77">
         <v>2200</v>
@@ -19380,7 +19380,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G78">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H78">
         <v>2530</v>
@@ -19433,7 +19433,7 @@
         <v>0.35</v>
       </c>
       <c r="G79">
-        <v>0.4017</v>
+        <v>0.36153000000000002</v>
       </c>
       <c r="H79">
         <v>2420</v>
@@ -19486,7 +19486,7 @@
         <v>0.90700000000000003</v>
       </c>
       <c r="G80">
-        <v>0.4017</v>
+        <v>0.36153000000000002</v>
       </c>
       <c r="H80">
         <v>2420</v>
@@ -19539,7 +19539,7 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="G81">
-        <v>0.38109999999999999</v>
+        <v>0.34299000000000002</v>
       </c>
       <c r="H81">
         <v>2420</v>
@@ -19592,7 +19592,7 @@
         <v>0.5</v>
       </c>
       <c r="G82">
-        <v>0.38110000000000005</v>
+        <v>0.34299000000000002</v>
       </c>
       <c r="H82">
         <v>2420</v>
@@ -19645,7 +19645,7 @@
         <v>0.93300000000000005</v>
       </c>
       <c r="G83">
-        <v>0.4017</v>
+        <v>0.36153000000000002</v>
       </c>
       <c r="H83">
         <v>2420</v>
@@ -19698,7 +19698,7 @@
         <v>0.93300000000000005</v>
       </c>
       <c r="G84">
-        <v>0.4017</v>
+        <v>0.36153000000000002</v>
       </c>
       <c r="H84">
         <v>2420</v>
@@ -19751,7 +19751,7 @@
         <v>0.55300000000000005</v>
       </c>
       <c r="G85">
-        <v>0.4017</v>
+        <v>0.36153000000000002</v>
       </c>
       <c r="H85">
         <v>2420</v>
@@ -19804,7 +19804,7 @@
         <v>0.8</v>
       </c>
       <c r="G86">
-        <v>0.4017</v>
+        <v>0.36152999999999996</v>
       </c>
       <c r="H86">
         <v>2420</v>
@@ -19857,7 +19857,7 @@
         <v>0.8</v>
       </c>
       <c r="G87">
-        <v>0.4017</v>
+        <v>0.36152999999999996</v>
       </c>
       <c r="H87">
         <v>2420</v>
@@ -19910,7 +19910,7 @@
         <v>0.55300000000000005</v>
       </c>
       <c r="G88">
-        <v>0.4017</v>
+        <v>0.36153000000000002</v>
       </c>
       <c r="H88">
         <v>2420</v>
@@ -19963,7 +19963,7 @@
         <v>0.47399999999999998</v>
       </c>
       <c r="G89">
-        <v>0.38109999999999999</v>
+        <v>0.34299000000000002</v>
       </c>
       <c r="H89">
         <v>2420</v>
@@ -20016,7 +20016,7 @@
         <v>0.67500000000000004</v>
       </c>
       <c r="G90">
-        <v>0.44804999999999995</v>
+        <v>0.40324500000000002</v>
       </c>
       <c r="H90">
         <v>2640</v>
@@ -20069,7 +20069,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G91">
-        <v>0.44805</v>
+        <v>0.40324500000000002</v>
       </c>
       <c r="H91">
         <v>2640</v>
@@ -20122,7 +20122,7 @@
         <v>0.91200000000000003</v>
       </c>
       <c r="G92">
-        <v>0.44805</v>
+        <v>0.40324500000000002</v>
       </c>
       <c r="H92">
         <v>2640</v>
@@ -20175,7 +20175,7 @@
         <v>0.81</v>
       </c>
       <c r="G93">
-        <v>0.44805</v>
+        <v>0.40324500000000008</v>
       </c>
       <c r="H93">
         <v>2640</v>
@@ -20228,7 +20228,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G94">
-        <v>0.44805</v>
+        <v>0.40324500000000002</v>
       </c>
       <c r="H94">
         <v>2640</v>
@@ -20281,7 +20281,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G95">
-        <v>0.44805</v>
+        <v>0.40324500000000002</v>
       </c>
       <c r="H95">
         <v>2640</v>
@@ -20334,7 +20334,7 @@
         <v>1.012</v>
       </c>
       <c r="G96">
-        <v>0.43259999999999998</v>
+        <v>0.38934000000000002</v>
       </c>
       <c r="H96">
         <v>2640</v>
@@ -20387,7 +20387,7 @@
         <v>0.91</v>
       </c>
       <c r="G97">
-        <v>0.44805</v>
+        <v>0.40324500000000008</v>
       </c>
       <c r="H97">
         <v>2640</v>
@@ -20440,7 +20440,7 @@
         <v>0.79</v>
       </c>
       <c r="G98">
-        <v>0.44805</v>
+        <v>0.40324500000000002</v>
       </c>
       <c r="H98">
         <v>2640</v>
@@ -20493,7 +20493,7 @@
         <v>0.83</v>
       </c>
       <c r="G99">
-        <v>0.44805</v>
+        <v>0.40324500000000002</v>
       </c>
       <c r="H99">
         <v>2640</v>
@@ -20546,7 +20546,7 @@
         <v>2.6499999999999999E-2</v>
       </c>
       <c r="G100">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H100">
         <v>1485.0000000000002</v>
@@ -20599,7 +20599,7 @@
         <v>0.108</v>
       </c>
       <c r="G101">
-        <v>0.3635518518518519</v>
+        <v>0.32719666666666669</v>
       </c>
       <c r="H101">
         <v>1342.4074074074074</v>
@@ -20652,7 +20652,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G102">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H102">
         <v>1485.0000000000002</v>
@@ -20705,7 +20705,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="G103">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H103">
         <v>1485.0000000000002</v>
@@ -20758,7 +20758,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G104">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H104">
         <v>1485.0000000000002</v>
@@ -20811,7 +20811,7 @@
         <v>0.02</v>
       </c>
       <c r="G105">
-        <v>0.37080000000000002</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H105">
         <v>1485.0000000000002</v>
@@ -20864,7 +20864,7 @@
         <v>0.17299999999999999</v>
       </c>
       <c r="G106">
-        <v>0.39139999999999997</v>
+        <v>0.35226000000000007</v>
       </c>
       <c r="H106">
         <v>1265</v>
@@ -20917,7 +20917,7 @@
         <v>0.08</v>
       </c>
       <c r="G107">
-        <v>0.39140000000000003</v>
+        <v>0.35226000000000002</v>
       </c>
       <c r="H107">
         <v>1265</v>
@@ -20970,7 +20970,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G108">
-        <v>0.37080000000000002</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H108">
         <v>1485.0000000000002</v>
@@ -21023,7 +21023,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G109">
-        <v>0.37080000000000002</v>
+        <v>0.33371999999999996</v>
       </c>
       <c r="H109">
         <v>1485.0000000000002</v>
@@ -21076,7 +21076,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="G110">
-        <v>0.44290000000000002</v>
+        <v>0.39861000000000002</v>
       </c>
       <c r="H110">
         <v>1265</v>
@@ -21129,7 +21129,7 @@
         <v>0.23799999999999999</v>
       </c>
       <c r="G111">
-        <v>0.50547899159663867</v>
+        <v>0.45493109243697472</v>
       </c>
       <c r="H111">
         <v>1366.6806722689075</v>
@@ -21182,7 +21182,7 @@
         <v>0.26900000000000002</v>
       </c>
       <c r="G112">
-        <v>0.51500000000000012</v>
+        <v>0.46350000000000002</v>
       </c>
       <c r="H112">
         <v>1265</v>
@@ -21235,7 +21235,7 @@
         <v>0.16</v>
       </c>
       <c r="G113">
-        <v>0.51500000000000001</v>
+        <v>0.46349999999999997</v>
       </c>
       <c r="H113">
         <v>1265</v>
@@ -21288,7 +21288,7 @@
         <v>0.14199999999999999</v>
       </c>
       <c r="G114">
-        <v>0.51500000000000001</v>
+        <v>0.46350000000000008</v>
       </c>
       <c r="H114">
         <v>1265</v>
@@ -21341,7 +21341,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="G115">
-        <v>0.50680204081632652</v>
+        <v>0.45612183673469386</v>
       </c>
       <c r="H115">
         <v>1352.5510204081634</v>
@@ -21394,7 +21394,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="G116">
-        <v>0.51500000000000001</v>
+        <v>0.46350000000000008</v>
       </c>
       <c r="H116">
         <v>1265</v>
@@ -21447,7 +21447,7 @@
         <v>0.1</v>
       </c>
       <c r="G117">
-        <v>0.51500000000000001</v>
+        <v>0.46350000000000002</v>
       </c>
       <c r="H117">
         <v>1265</v>
@@ -21500,7 +21500,7 @@
         <v>0.62879999999999991</v>
       </c>
       <c r="G118">
-        <v>0.53279239821882962</v>
+        <v>0.47951315839694664</v>
       </c>
       <c r="H118">
         <v>1294.984096692112</v>
@@ -21553,7 +21553,7 @@
         <v>7.8E-2</v>
       </c>
       <c r="G119">
-        <v>0.53560000000000008</v>
+        <v>0.48204000000000008</v>
       </c>
       <c r="H119">
         <v>1265</v>
@@ -21606,7 +21606,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G120">
-        <v>0.53560000000000008</v>
+        <v>0.48204000000000002</v>
       </c>
       <c r="H120">
         <v>1265</v>
@@ -21659,7 +21659,7 @@
         <v>0.19600000000000001</v>
       </c>
       <c r="G121">
-        <v>0.53139591836734701</v>
+        <v>0.47825632653061234</v>
       </c>
       <c r="H121">
         <v>1309.8979591836735</v>
@@ -21712,7 +21712,7 @@
         <v>0.13100000000000001</v>
       </c>
       <c r="G122">
-        <v>0.56893740458015263</v>
+        <v>0.51204366412213753</v>
       </c>
       <c r="H122">
         <v>1348.969465648855</v>
@@ -21765,7 +21765,7 @@
         <v>0.126</v>
       </c>
       <c r="G123">
-        <v>0.55619999999999992</v>
+        <v>0.50058000000000002</v>
       </c>
       <c r="H123">
         <v>1485.0000000000002</v>
@@ -21818,7 +21818,7 @@
         <v>0.1661</v>
       </c>
       <c r="G124">
-        <v>0.57097098133654434</v>
+        <v>0.51387388320288985</v>
       </c>
       <c r="H124">
         <v>1327.2516556291391</v>
@@ -21871,7 +21871,7 @@
         <v>0.18659999999999999</v>
       </c>
       <c r="G125">
-        <v>0.56591489817792084</v>
+        <v>0.50932340836012868</v>
       </c>
       <c r="H125">
         <v>1381.2486602357988</v>
@@ -21924,7 +21924,7 @@
         <v>0.24580000000000002</v>
       </c>
       <c r="G126">
-        <v>0.57679999999999998</v>
+        <v>0.51912000000000003</v>
       </c>
       <c r="H126">
         <v>1265</v>
@@ -21977,7 +21977,7 @@
         <v>3.9E-2</v>
       </c>
       <c r="G127">
-        <v>0.55620000000000003</v>
+        <v>0.50058000000000002</v>
       </c>
       <c r="H127">
         <v>1485.0000000000002</v>
@@ -22030,7 +22030,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G128">
-        <v>0.57680000000000009</v>
+        <v>0.51912000000000014</v>
       </c>
       <c r="H128">
         <v>1265</v>
@@ -22083,7 +22083,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="G129">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H129">
         <v>1265</v>
@@ -22136,7 +22136,7 @@
         <v>0.50900000000000001</v>
       </c>
       <c r="G130">
-        <v>0.59739999999999993</v>
+        <v>0.5376599999999998</v>
       </c>
       <c r="H130">
         <v>1265</v>
@@ -22189,7 +22189,7 @@
         <v>0.155</v>
       </c>
       <c r="G131">
-        <v>0.59739999999999982</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H131">
         <v>1265</v>
@@ -22242,7 +22242,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G132">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H132">
         <v>1265</v>
@@ -22295,7 +22295,7 @@
         <v>0.44733999999999347</v>
       </c>
       <c r="G133">
-        <v>0.61799999999999999</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H133">
         <v>1100</v>
@@ -22348,7 +22348,7 @@
         <v>0.11600000000000001</v>
       </c>
       <c r="G134">
-        <v>0.51500000000000001</v>
+        <v>0.46350000000000002</v>
       </c>
       <c r="H134">
         <v>1265</v>
@@ -22401,7 +22401,7 @@
         <v>0.112</v>
       </c>
       <c r="G135">
-        <v>0.51500000000000001</v>
+        <v>0.46350000000000008</v>
       </c>
       <c r="H135">
         <v>1265</v>
@@ -22454,7 +22454,7 @@
         <v>0.46100000000000002</v>
       </c>
       <c r="G136">
-        <v>0.54075000000000006</v>
+        <v>0.48667500000000008</v>
       </c>
       <c r="H136">
         <v>1100</v>
@@ -22507,7 +22507,7 @@
         <v>0.23100000000000001</v>
       </c>
       <c r="G137">
-        <v>0.51500000000000001</v>
+        <v>0.46350000000000002</v>
       </c>
       <c r="H137">
         <v>1265</v>
@@ -22560,7 +22560,7 @@
         <v>0.112</v>
       </c>
       <c r="G138">
-        <v>0.51500000000000001</v>
+        <v>0.46350000000000008</v>
       </c>
       <c r="H138">
         <v>1265</v>
@@ -22613,7 +22613,7 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="G139">
-        <v>0.53560000000000008</v>
+        <v>0.48204000000000014</v>
       </c>
       <c r="H139">
         <v>1265</v>
@@ -22666,7 +22666,7 @@
         <v>0.41699999999999998</v>
       </c>
       <c r="G140">
-        <v>0.56135000000000002</v>
+        <v>0.50521500000000008</v>
       </c>
       <c r="H140">
         <v>1100</v>
@@ -22719,7 +22719,7 @@
         <v>0.58599999999999997</v>
       </c>
       <c r="G141">
-        <v>0.54075000000000006</v>
+        <v>0.48667500000000014</v>
       </c>
       <c r="H141">
         <v>1100</v>
@@ -22772,7 +22772,7 @@
         <v>0.23400000000000001</v>
       </c>
       <c r="G142">
-        <v>0.53560000000000008</v>
+        <v>0.48204000000000002</v>
       </c>
       <c r="H142">
         <v>1265</v>
@@ -22825,7 +22825,7 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="G143">
-        <v>0.41200000000000003</v>
+        <v>0.37079999999999996</v>
       </c>
       <c r="H143">
         <v>1100</v>
@@ -22878,7 +22878,7 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="G144">
-        <v>0.41200000000000003</v>
+        <v>0.37079999999999996</v>
       </c>
       <c r="H144">
         <v>1100</v>
@@ -22931,7 +22931,7 @@
         <v>0.88700000000000001</v>
       </c>
       <c r="G145">
-        <v>0.56135000000000002</v>
+        <v>0.50521500000000008</v>
       </c>
       <c r="H145">
         <v>1100</v>
@@ -22984,7 +22984,7 @@
         <v>0.39500000000000002</v>
       </c>
       <c r="G146">
-        <v>0.41200000000000003</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H146">
         <v>1100</v>
@@ -23037,7 +23037,7 @@
         <v>0.44</v>
       </c>
       <c r="G147">
-        <v>0.41199999999999998</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H147">
         <v>1100</v>
@@ -23090,7 +23090,7 @@
         <v>0.35499999999999998</v>
       </c>
       <c r="G148">
-        <v>0.41200000000000003</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H148">
         <v>1100</v>
@@ -23143,7 +23143,7 @@
         <v>0.23</v>
       </c>
       <c r="G149">
-        <v>0.57680000000000009</v>
+        <v>0.51912000000000014</v>
       </c>
       <c r="H149">
         <v>1265</v>
@@ -23196,7 +23196,7 @@
         <v>0.56100000000000005</v>
       </c>
       <c r="G150">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H150">
         <v>1100</v>
@@ -23249,7 +23249,7 @@
         <v>0.84599999999999997</v>
       </c>
       <c r="G151">
-        <v>0.56135000000000002</v>
+        <v>0.50521500000000008</v>
       </c>
       <c r="H151">
         <v>1100</v>
@@ -23302,7 +23302,7 @@
         <v>0.182</v>
       </c>
       <c r="G152">
-        <v>0.51500000000000001</v>
+        <v>0.46350000000000002</v>
       </c>
       <c r="H152">
         <v>1265</v>
@@ -23355,7 +23355,7 @@
         <v>0.1288</v>
       </c>
       <c r="G153">
-        <v>0.57680000000000009</v>
+        <v>0.51912000000000014</v>
       </c>
       <c r="H153">
         <v>1265</v>
@@ -23408,7 +23408,7 @@
         <v>0.16</v>
       </c>
       <c r="G154">
-        <v>0.51500000000000001</v>
+        <v>0.46349999999999997</v>
       </c>
       <c r="H154">
         <v>1265</v>
@@ -23461,7 +23461,7 @@
         <v>0.80200000000000005</v>
       </c>
       <c r="G155">
-        <v>0.56135000000000002</v>
+        <v>0.50521500000000008</v>
       </c>
       <c r="H155">
         <v>1100</v>
@@ -23514,7 +23514,7 @@
         <v>0.45</v>
       </c>
       <c r="G156">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H156">
         <v>1100</v>
@@ -23567,7 +23567,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="G157">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H157">
         <v>1100</v>
@@ -23620,7 +23620,7 @@
         <v>0.17199999999999999</v>
       </c>
       <c r="G158">
-        <v>0.51500000000000001</v>
+        <v>0.46350000000000002</v>
       </c>
       <c r="H158">
         <v>1265</v>
@@ -23673,7 +23673,7 @@
         <v>0.315</v>
       </c>
       <c r="G159">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H159">
         <v>1100</v>
@@ -23726,7 +23726,7 @@
         <v>0.503</v>
       </c>
       <c r="G160">
-        <v>0.56135000000000002</v>
+        <v>0.50521500000000008</v>
       </c>
       <c r="H160">
         <v>1100</v>
@@ -23779,7 +23779,7 @@
         <v>0.41499999999999998</v>
       </c>
       <c r="G161">
-        <v>0.54075000000000006</v>
+        <v>0.48667500000000008</v>
       </c>
       <c r="H161">
         <v>1100</v>
@@ -23832,7 +23832,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="G162">
-        <v>0.41200000000000003</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H162">
         <v>1100</v>
@@ -23885,7 +23885,7 @@
         <v>0.434</v>
       </c>
       <c r="G163">
-        <v>0.54075000000000006</v>
+        <v>0.48667500000000008</v>
       </c>
       <c r="H163">
         <v>1100</v>
@@ -23938,7 +23938,7 @@
         <v>0.128</v>
       </c>
       <c r="G164">
-        <v>0.53560000000000008</v>
+        <v>0.48204000000000008</v>
       </c>
       <c r="H164">
         <v>1265</v>
@@ -23991,7 +23991,7 @@
         <v>0.42899999999999999</v>
       </c>
       <c r="G165">
-        <v>0.56135000000000002</v>
+        <v>0.50521500000000008</v>
       </c>
       <c r="H165">
         <v>1100</v>
@@ -24044,7 +24044,7 @@
         <v>0.214</v>
       </c>
       <c r="G166">
-        <v>0.39140000000000003</v>
+        <v>0.35226000000000002</v>
       </c>
       <c r="H166">
         <v>1265</v>
@@ -24097,7 +24097,7 @@
         <v>0.41299999999999998</v>
       </c>
       <c r="G167">
-        <v>0.56135000000000002</v>
+        <v>0.50521500000000008</v>
       </c>
       <c r="H167">
         <v>1100</v>
@@ -24150,7 +24150,7 @@
         <v>0.46</v>
       </c>
       <c r="G168">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H168">
         <v>1100</v>
@@ -24203,7 +24203,7 @@
         <v>0.36299999999999999</v>
       </c>
       <c r="G169">
-        <v>0.54075000000000006</v>
+        <v>0.48667500000000008</v>
       </c>
       <c r="H169">
         <v>1100</v>
@@ -24256,7 +24256,7 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="G170">
-        <v>0.57680000000000009</v>
+        <v>0.51912000000000014</v>
       </c>
       <c r="H170">
         <v>1265</v>
@@ -24309,7 +24309,7 @@
         <v>0.13400000000000001</v>
       </c>
       <c r="G171">
-        <v>0.57680000000000009</v>
+        <v>0.51912000000000014</v>
       </c>
       <c r="H171">
         <v>1265</v>
@@ -24362,7 +24362,7 @@
         <v>0.127</v>
       </c>
       <c r="G172">
-        <v>0.53560000000000008</v>
+        <v>0.48204000000000008</v>
       </c>
       <c r="H172">
         <v>1265</v>
@@ -24415,7 +24415,7 @@
         <v>0.41699999999999998</v>
       </c>
       <c r="G173">
-        <v>0.56135000000000002</v>
+        <v>0.50521500000000008</v>
       </c>
       <c r="H173">
         <v>1100</v>
@@ -24468,7 +24468,7 @@
         <v>0.42099999999999999</v>
       </c>
       <c r="G174">
-        <v>0.56135000000000002</v>
+        <v>0.50521500000000008</v>
       </c>
       <c r="H174">
         <v>1100</v>
@@ -24521,7 +24521,7 @@
         <v>0.112</v>
       </c>
       <c r="G175">
-        <v>0.53560000000000008</v>
+        <v>0.48204000000000008</v>
       </c>
       <c r="H175">
         <v>1265</v>
@@ -24574,7 +24574,7 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="G176">
-        <v>0.57680000000000009</v>
+        <v>0.51912000000000014</v>
       </c>
       <c r="H176">
         <v>1265</v>
@@ -24627,7 +24627,7 @@
         <v>0.72499999999999998</v>
       </c>
       <c r="G177">
-        <v>0.61799999999999999</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H177">
         <v>1100</v>
@@ -24680,7 +24680,7 @@
         <v>0.13800000000000001</v>
       </c>
       <c r="G178">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H178">
         <v>1265</v>
@@ -24733,7 +24733,7 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="G179">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H179">
         <v>1265</v>
@@ -24786,7 +24786,7 @@
         <v>0.14399999999999999</v>
       </c>
       <c r="G180">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H180">
         <v>1265</v>
@@ -24839,7 +24839,7 @@
         <v>0.14399999999999999</v>
       </c>
       <c r="G181">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H181">
         <v>1265</v>
@@ -24892,7 +24892,7 @@
         <v>0.35499999999999998</v>
       </c>
       <c r="G182">
-        <v>0.41200000000000003</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H182">
         <v>1100</v>
@@ -24945,7 +24945,7 @@
         <v>0.13</v>
       </c>
       <c r="G183">
-        <v>0.44290000000000002</v>
+        <v>0.39861000000000002</v>
       </c>
       <c r="H183">
         <v>1265</v>
@@ -24998,7 +24998,7 @@
         <v>0.44</v>
       </c>
       <c r="G184">
-        <v>0.61799999999999999</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H184">
         <v>1100</v>
@@ -25051,7 +25051,7 @@
         <v>0.35499999999999998</v>
       </c>
       <c r="G185">
-        <v>0.41200000000000003</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H185">
         <v>1100</v>
@@ -25104,7 +25104,7 @@
         <v>0.125</v>
       </c>
       <c r="G186">
-        <v>0.44290000000000002</v>
+        <v>0.39861000000000002</v>
       </c>
       <c r="H186">
         <v>1265</v>
@@ -25157,7 +25157,7 @@
         <v>0.254</v>
       </c>
       <c r="G187">
-        <v>0.39140000000000003</v>
+        <v>0.35226000000000002</v>
       </c>
       <c r="H187">
         <v>1265</v>
@@ -25210,7 +25210,7 @@
         <v>0.114</v>
       </c>
       <c r="G188">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H188">
         <v>1265</v>
@@ -25263,7 +25263,7 @@
         <v>0.75</v>
       </c>
       <c r="G189">
-        <v>0.61799999999999999</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H189">
         <v>1100</v>
@@ -25316,7 +25316,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="G190">
-        <v>0.59739999999999993</v>
+        <v>0.53765999999999992</v>
       </c>
       <c r="H190">
         <v>1265</v>
@@ -25369,7 +25369,7 @@
         <v>0.23799999999999999</v>
       </c>
       <c r="G191">
-        <v>0.39140000000000003</v>
+        <v>0.35226000000000002</v>
       </c>
       <c r="H191">
         <v>1265</v>
@@ -25422,7 +25422,7 @@
         <v>0.115</v>
       </c>
       <c r="G192">
-        <v>0.53560000000000008</v>
+        <v>0.48204000000000008</v>
       </c>
       <c r="H192">
         <v>1265</v>
@@ -25475,7 +25475,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G193">
-        <v>0.20600000000000002</v>
+        <v>0.18539999999999998</v>
       </c>
       <c r="H193">
         <v>1188</v>
@@ -25528,7 +25528,7 @@
         <v>0.05</v>
       </c>
       <c r="G194">
-        <v>0.2266</v>
+        <v>0.20394000000000001</v>
       </c>
       <c r="H194">
         <v>1188</v>
@@ -25581,7 +25581,7 @@
         <v>0.22500000000000001</v>
       </c>
       <c r="G195">
-        <v>0.23690000000000003</v>
+        <v>0.21321000000000004</v>
       </c>
       <c r="H195">
         <v>1012</v>
@@ -25634,7 +25634,7 @@
         <v>6.6700000000000009E-2</v>
       </c>
       <c r="G196">
-        <v>0.23690000000000003</v>
+        <v>0.21321000000000004</v>
       </c>
       <c r="H196">
         <v>1012.0000000000001</v>
@@ -25687,7 +25687,7 @@
         <v>0.29569999999999996</v>
       </c>
       <c r="G197">
-        <v>0.23690000000000003</v>
+        <v>0.21321000000000007</v>
       </c>
       <c r="H197">
         <v>1012.0000000000001</v>
@@ -25740,7 +25740,7 @@
         <v>0.152</v>
       </c>
       <c r="G198">
-        <v>0.24719999999999998</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H198">
         <v>1188</v>
@@ -25793,7 +25793,7 @@
         <v>3.9E-2</v>
       </c>
       <c r="G199">
-        <v>0.2472</v>
+        <v>0.22247999999999998</v>
       </c>
       <c r="H199">
         <v>1188</v>
@@ -25846,7 +25846,7 @@
         <v>0.15</v>
       </c>
       <c r="G200">
-        <v>0.24719999999999998</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H200">
         <v>1188</v>
@@ -25899,7 +25899,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G201">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H201">
         <v>1012</v>
@@ -25952,7 +25952,7 @@
         <v>3.0699999999999998E-2</v>
       </c>
       <c r="G202">
-        <v>0.28840000000000005</v>
+        <v>0.25956000000000007</v>
       </c>
       <c r="H202">
         <v>1188</v>
@@ -26005,7 +26005,7 @@
         <v>4.4499999999999998E-2</v>
       </c>
       <c r="G203">
-        <v>0.28840000000000005</v>
+        <v>0.25956000000000007</v>
       </c>
       <c r="H203">
         <v>1188</v>
@@ -26058,7 +26058,7 @@
         <v>2.9499999999999998E-2</v>
       </c>
       <c r="G204">
-        <v>0.28840000000000005</v>
+        <v>0.25956000000000007</v>
       </c>
       <c r="H204">
         <v>1188</v>
@@ -26111,7 +26111,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G205">
-        <v>0.28840000000000005</v>
+        <v>0.25956000000000007</v>
       </c>
       <c r="H205">
         <v>1188</v>
@@ -26164,7 +26164,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="G206">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H206">
         <v>1188</v>
@@ -26217,7 +26217,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G207">
-        <v>0.31930000000000003</v>
+        <v>0.28737000000000001</v>
       </c>
       <c r="H207">
         <v>1012</v>
@@ -26270,7 +26270,7 @@
         <v>0.02</v>
       </c>
       <c r="G208">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H208">
         <v>1188</v>
@@ -26323,7 +26323,7 @@
         <v>0.02</v>
       </c>
       <c r="G209">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H209">
         <v>1188</v>
@@ -26376,7 +26376,7 @@
         <v>0.1</v>
       </c>
       <c r="G210">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H210">
         <v>1188</v>
@@ -26429,7 +26429,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G211">
-        <v>0.31930000000000003</v>
+        <v>0.28737000000000001</v>
       </c>
       <c r="H211">
         <v>1188</v>
@@ -26482,7 +26482,7 @@
         <v>0.59099999999999997</v>
       </c>
       <c r="G212">
-        <v>0.32254162436548234</v>
+        <v>0.29028746192893401</v>
       </c>
       <c r="H212">
         <v>1132.6091370558377</v>
@@ -26535,7 +26535,7 @@
         <v>0.112</v>
       </c>
       <c r="G213">
-        <v>0.25750000000000001</v>
+        <v>0.23175000000000004</v>
       </c>
       <c r="H213">
         <v>1012</v>
@@ -26588,7 +26588,7 @@
         <v>0.32100000000000001</v>
       </c>
       <c r="G214">
-        <v>0.24720000000000003</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H214">
         <v>880.00000000000023</v>
@@ -26641,7 +26641,7 @@
         <v>0.2</v>
       </c>
       <c r="G215">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H215">
         <v>1012</v>
@@ -26694,7 +26694,7 @@
         <v>0.2</v>
       </c>
       <c r="G216">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H216">
         <v>1012</v>
@@ -26747,7 +26747,7 @@
         <v>0.31900000000000001</v>
       </c>
       <c r="G217">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H217">
         <v>880.00000000000023</v>
@@ -26800,7 +26800,7 @@
         <v>0.32</v>
       </c>
       <c r="G218">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H218">
         <v>880.00000000000023</v>
@@ -26853,7 +26853,7 @@
         <v>0.45</v>
       </c>
       <c r="G219">
-        <v>0.24719999999999998</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H219">
         <v>880.00000000000011</v>
@@ -26906,7 +26906,7 @@
         <v>0.3</v>
       </c>
       <c r="G220">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H220">
         <v>1012</v>
@@ -26959,7 +26959,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="G221">
-        <v>0.31930000000000003</v>
+        <v>0.28737000000000001</v>
       </c>
       <c r="H221">
         <v>1633.5000000000002</v>
@@ -27012,7 +27012,7 @@
         <v>3.1199999999999999E-2</v>
       </c>
       <c r="G222">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H222">
         <v>1633.5000000000002</v>
@@ -27065,7 +27065,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="G223">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H223">
         <v>1633.5000000000005</v>
@@ -27118,7 +27118,7 @@
         <v>6.4200000000000007E-2</v>
       </c>
       <c r="G224">
-        <v>0.35535</v>
+        <v>0.31981499999999996</v>
       </c>
       <c r="H224">
         <v>1633.5</v>
@@ -27171,7 +27171,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G225">
-        <v>0.36564999999999998</v>
+        <v>0.32908499999999996</v>
       </c>
       <c r="H225">
         <v>1633.5000000000002</v>
@@ -27224,7 +27224,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G226">
-        <v>0.36564999999999998</v>
+        <v>0.32908499999999996</v>
       </c>
       <c r="H226">
         <v>1633.5000000000002</v>
@@ -27277,7 +27277,7 @@
         <v>3.0899999999999997E-2</v>
       </c>
       <c r="G227">
-        <v>0.36564999999999998</v>
+        <v>0.32908499999999996</v>
       </c>
       <c r="H227">
         <v>1633.5000000000002</v>
@@ -27330,7 +27330,7 @@
         <v>0.13150000000000001</v>
       </c>
       <c r="G228">
-        <v>0.36564999999999998</v>
+        <v>0.32908499999999996</v>
       </c>
       <c r="H228">
         <v>1449.4695817490494</v>
@@ -27383,7 +27383,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G229">
-        <v>0.37080000000000002</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H229">
         <v>1467.921052631579</v>
@@ -27436,7 +27436,7 @@
         <v>0.2515</v>
       </c>
       <c r="G230">
-        <v>0.37080000000000002</v>
+        <v>0.33372000000000007</v>
       </c>
       <c r="H230">
         <v>1439.6113320079523</v>
@@ -27489,7 +27489,7 @@
         <v>0.25619999999999998</v>
       </c>
       <c r="G231">
-        <v>0.37080000000000007</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H231">
         <v>1391.5</v>
@@ -27542,7 +27542,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="G232">
-        <v>0.37080000000000002</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H232">
         <v>1391.5</v>
@@ -27595,7 +27595,7 @@
         <v>0.192</v>
       </c>
       <c r="G233">
-        <v>0.36564999999999998</v>
+        <v>0.32908499999999996</v>
       </c>
       <c r="H233">
         <v>1391.5</v>
@@ -27648,7 +27648,7 @@
         <v>0.09</v>
       </c>
       <c r="G234">
-        <v>0.26264999999999999</v>
+        <v>0.23638500000000001</v>
       </c>
       <c r="H234">
         <v>1782.0000000000002</v>
@@ -27701,7 +27701,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="G235">
-        <v>0.27295000000000003</v>
+        <v>0.24565500000000004</v>
       </c>
       <c r="H235">
         <v>1518.0000000000002</v>
@@ -27754,7 +27754,7 @@
         <v>0.154</v>
       </c>
       <c r="G236">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H236">
         <v>1518.0000000000005</v>
@@ -27807,7 +27807,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G237">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H237">
         <v>1518.0000000000002</v>
@@ -27860,7 +27860,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G238">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H238">
         <v>1518.0000000000002</v>
@@ -27913,7 +27913,7 @@
         <v>0.10100000000000001</v>
       </c>
       <c r="G239">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H239">
         <v>1518.0000000000002</v>
@@ -27966,7 +27966,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="G240">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H240">
         <v>1518.0000000000002</v>
@@ -28019,7 +28019,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="G241">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H241">
         <v>1782.0000000000002</v>
@@ -28072,7 +28072,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="G242">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H242">
         <v>1782.0000000000002</v>
@@ -28125,7 +28125,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G243">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H243">
         <v>1782.0000000000005</v>
@@ -28178,7 +28178,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G244">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H244">
         <v>1782.0000000000002</v>
@@ -28231,7 +28231,7 @@
         <v>0.12840000000000001</v>
       </c>
       <c r="G245">
-        <v>0.31766355140186914</v>
+        <v>0.28589719626168225</v>
       </c>
       <c r="H245">
         <v>1559.9439252336451</v>
@@ -28284,7 +28284,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G246">
-        <v>0.31930000000000003</v>
+        <v>0.28737000000000001</v>
       </c>
       <c r="H246">
         <v>1782.0000000000002</v>
@@ -28337,7 +28337,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="G247">
-        <v>0.31930000000000003</v>
+        <v>0.28737000000000001</v>
       </c>
       <c r="H247">
         <v>1782.0000000000005</v>
@@ -28390,7 +28390,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="G248">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H248">
         <v>1518.0000000000002</v>
@@ -28443,7 +28443,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="G249">
-        <v>0.31930000000000003</v>
+        <v>0.28737000000000001</v>
       </c>
       <c r="H249">
         <v>1782.0000000000002</v>
@@ -28496,7 +28496,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G250">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H250">
         <v>1782.0000000000005</v>
@@ -28549,7 +28549,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G251">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H251">
         <v>1782.0000000000002</v>
@@ -28602,7 +28602,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G252">
-        <v>0.32960000000000006</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H252">
         <v>1782.0000000000002</v>
@@ -28655,7 +28655,7 @@
         <v>0.113</v>
       </c>
       <c r="G253">
-        <v>0.3296</v>
+        <v>0.29663999999999996</v>
       </c>
       <c r="H253">
         <v>1782.0000000000005</v>
@@ -28708,7 +28708,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="G254">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H254">
         <v>1782.0000000000002</v>
@@ -28761,7 +28761,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G255">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H255">
         <v>1782.0000000000002</v>
@@ -28793,7 +28793,7 @@
         <v>4.8899999999999999E-2</v>
       </c>
       <c r="G256">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H256">
         <v>1782</v>
@@ -28825,7 +28825,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="G257">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H257">
         <v>1782.0000000000005</v>
@@ -28857,7 +28857,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="G258">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H258">
         <v>1782.0000000000002</v>
@@ -28889,7 +28889,7 @@
         <v>0.113</v>
       </c>
       <c r="G259">
-        <v>0.34655398230088497</v>
+        <v>0.31189858407079646</v>
       </c>
       <c r="H259">
         <v>1611.4513274336286</v>
@@ -28921,7 +28921,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="G260">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H260">
         <v>1782.0000000000002</v>
@@ -28953,7 +28953,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G261">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H261">
         <v>1518.0000000000002</v>
@@ -28985,7 +28985,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G262">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H262">
         <v>1782.0000000000002</v>
@@ -29017,7 +29017,7 @@
         <v>2.9960000000000001E-2</v>
       </c>
       <c r="G263">
-        <v>0.33990000000000004</v>
+        <v>0.30590999999999996</v>
       </c>
       <c r="H263">
         <v>1782.0000000000002</v>
@@ -29049,7 +29049,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="G264">
-        <v>0.34505000000000002</v>
+        <v>0.31054500000000002</v>
       </c>
       <c r="H264">
         <v>1782.0000000000002</v>
@@ -29081,7 +29081,7 @@
         <v>0.24399999999999999</v>
       </c>
       <c r="G265">
-        <v>0.3518885245901639</v>
+        <v>0.31669967213114752</v>
       </c>
       <c r="H265">
         <v>1606.7213114754104</v>
@@ -29113,7 +29113,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="G266">
-        <v>0.34505000000000002</v>
+        <v>0.31054500000000002</v>
       </c>
       <c r="H266">
         <v>1782.0000000000002</v>
@@ -29145,7 +29145,7 @@
         <v>3.8700000000000005E-2</v>
       </c>
       <c r="G267">
-        <v>0.34505000000000002</v>
+        <v>0.31054500000000002</v>
       </c>
       <c r="H267">
         <v>1782</v>
@@ -29177,7 +29177,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="G268">
-        <v>0.35252808219178078</v>
+        <v>0.3172752739726028</v>
       </c>
       <c r="H268">
         <v>1590.3287671232881</v>
@@ -29209,7 +29209,7 @@
         <v>0.13789999999999999</v>
       </c>
       <c r="G269">
-        <v>0.34915804931109506</v>
+        <v>0.31424224437998549</v>
       </c>
       <c r="H269">
         <v>1676.7063089195069</v>
@@ -29241,7 +29241,7 @@
         <v>2.155E-2</v>
       </c>
       <c r="G270">
-        <v>0.34505000000000002</v>
+        <v>0.31054500000000002</v>
       </c>
       <c r="H270">
         <v>1782.0000000000002</v>
@@ -29273,7 +29273,7 @@
         <v>0.121</v>
       </c>
       <c r="G271">
-        <v>0.35535</v>
+        <v>0.31981500000000002</v>
       </c>
       <c r="H271">
         <v>1518.0000000000002</v>
@@ -29305,7 +29305,7 @@
         <v>0.44500000000000001</v>
       </c>
       <c r="G272">
-        <v>0.37595000000000001</v>
+        <v>0.33835500000000002</v>
       </c>
       <c r="H272">
         <v>1320</v>
@@ -29337,7 +29337,7 @@
         <v>0.622</v>
       </c>
       <c r="G273">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H273">
         <v>1320</v>
@@ -29369,7 +29369,7 @@
         <v>0.1108</v>
       </c>
       <c r="G274">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000007</v>
       </c>
       <c r="H274">
         <v>1518.0000000000002</v>
@@ -29401,7 +29401,7 @@
         <v>0.41499999999999998</v>
       </c>
       <c r="G275">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H275">
         <v>1320</v>
@@ -29433,7 +29433,7 @@
         <v>0.11</v>
       </c>
       <c r="G276">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H276">
         <v>1518.0000000000002</v>
@@ -29465,7 +29465,7 @@
         <v>0.11</v>
       </c>
       <c r="G277">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H277">
         <v>1518.0000000000002</v>
@@ -29497,7 +29497,7 @@
         <v>0.32</v>
       </c>
       <c r="G278">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H278">
         <v>1320</v>
@@ -29529,7 +29529,7 @@
         <v>0.32</v>
       </c>
       <c r="G279">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H279">
         <v>1320</v>
@@ -29561,7 +29561,7 @@
         <v>0.17699999999999999</v>
       </c>
       <c r="G280">
-        <v>0.309</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H280">
         <v>1518.0000000000002</v>
@@ -29593,7 +29593,7 @@
         <v>0.24099999999999999</v>
       </c>
       <c r="G281">
-        <v>0.35020000000000001</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H281">
         <v>1518.0000000000002</v>
@@ -29625,7 +29625,7 @@
         <v>0.45</v>
       </c>
       <c r="G282">
-        <v>0.33990000000000004</v>
+        <v>0.30591000000000002</v>
       </c>
       <c r="H282">
         <v>1320</v>
@@ -29657,7 +29657,7 @@
         <v>0.188</v>
       </c>
       <c r="G283">
-        <v>0.35535</v>
+        <v>0.31981500000000002</v>
       </c>
       <c r="H283">
         <v>1518.0000000000002</v>
@@ -29689,7 +29689,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G284">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H284">
         <v>1782.0000000000002</v>
@@ -30905,7 +30905,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G322">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H322">
         <v>1633.5000000000002</v>
@@ -30937,7 +30937,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="G323">
-        <v>0.49440000000000006</v>
+        <v>0.44496000000000002</v>
       </c>
       <c r="H323">
         <v>1391.5</v>
@@ -30969,7 +30969,7 @@
         <v>4.7E-2</v>
       </c>
       <c r="G324">
-        <v>0.47380000000000005</v>
+        <v>0.42642000000000008</v>
       </c>
       <c r="H324">
         <v>1633.5000000000002</v>
@@ -31001,7 +31001,7 @@
         <v>0.26500000000000001</v>
       </c>
       <c r="G325">
-        <v>0.37080000000000002</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H325">
         <v>1391.5</v>
@@ -31033,7 +31033,7 @@
         <v>0.16200000000000001</v>
       </c>
       <c r="G326">
-        <v>0.49440000000000001</v>
+        <v>0.44496000000000002</v>
       </c>
       <c r="H326">
         <v>1391.5</v>
@@ -31065,7 +31065,7 @@
         <v>0.126</v>
       </c>
       <c r="G327">
-        <v>0.55620000000000003</v>
+        <v>0.50058000000000002</v>
       </c>
       <c r="H327">
         <v>1391.5</v>
@@ -31097,7 +31097,7 @@
         <v>0.10100000000000001</v>
       </c>
       <c r="G328">
-        <v>0.22659999999999997</v>
+        <v>0.20394000000000001</v>
       </c>
       <c r="H328">
         <v>1138.5</v>
@@ -31129,7 +31129,7 @@
         <v>0.1</v>
       </c>
       <c r="G329">
-        <v>0.2369</v>
+        <v>0.21321000000000004</v>
       </c>
       <c r="H329">
         <v>1336.5</v>
@@ -31161,7 +31161,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G330">
-        <v>0.27810000000000001</v>
+        <v>0.25029000000000001</v>
       </c>
       <c r="H330">
         <v>1336.5</v>
@@ -31193,7 +31193,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G331">
-        <v>0.29869999999999997</v>
+        <v>0.26882999999999996</v>
       </c>
       <c r="H331">
         <v>1336.5</v>
@@ -31225,7 +31225,7 @@
         <v>0.13600000000000001</v>
       </c>
       <c r="G332">
-        <v>0.2472</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H332">
         <v>1138.5</v>
@@ -31257,7 +31257,7 @@
         <v>0.13</v>
       </c>
       <c r="G333">
-        <v>0.20600000000000002</v>
+        <v>0.18540000000000001</v>
       </c>
       <c r="H333">
         <v>1138.5</v>
@@ -31289,7 +31289,7 @@
         <v>8.8800000000000004E-2</v>
       </c>
       <c r="G334">
-        <v>0.31414999999999998</v>
+        <v>0.28273500000000001</v>
       </c>
       <c r="H334">
         <v>1265</v>
@@ -31321,7 +31321,7 @@
         <v>0.02</v>
       </c>
       <c r="G335">
-        <v>0.28840000000000005</v>
+        <v>0.25956000000000007</v>
       </c>
       <c r="H335">
         <v>1930.5000000000005</v>
@@ -31353,7 +31353,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
       <c r="G336">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H336">
         <v>1644.4999999999998</v>
@@ -31385,7 +31385,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G337">
-        <v>0.3296</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H337">
         <v>1930.5000000000002</v>
@@ -31417,7 +31417,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G338">
-        <v>0.34505000000000002</v>
+        <v>0.31054500000000002</v>
       </c>
       <c r="H338">
         <v>1644.4999999999998</v>
@@ -31449,7 +31449,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="G339">
-        <v>0.36564999999999998</v>
+        <v>0.32908499999999996</v>
       </c>
       <c r="H339">
         <v>1430.0000000000002</v>
@@ -31496,7 +31496,7 @@
         <v>33</v>
       </c>
       <c r="L340">
-        <v>0.14414942289270033</v>
+        <v>0.14414942289270036</v>
       </c>
     </row>
     <row r="341" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{474305DA-899B-4501-9C0B-456FDE90F366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5328332A-B96C-42A2-A53A-DF4FD2351126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EA8DCD04-FEAF-4876-9EE8-6BA5E9BCEF73}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E6FDAEFE-302B-43A6-B948-2BC49F2E2399}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2867,7 +2867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{951E6388-2381-4EE7-8A77-3B018DB399A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662AA5B5-3193-4AB5-9A92-23C731A15002}">
   <dimension ref="B9:T281"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2946,7 +2946,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.23684850000000002</v>
+        <v>0.24211180000000002</v>
       </c>
       <c r="F11">
         <v>2200</v>
@@ -3002,7 +3002,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.26767125000000003</v>
+        <v>0.27361950000000002</v>
       </c>
       <c r="F12">
         <v>1923</v>
@@ -3058,19 +3058,19 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>9.2996640000000019E-2</v>
+        <v>0.12664674000000001</v>
       </c>
       <c r="F13">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G13">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H13">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I13">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J13" t="s">
         <v>32</v>
@@ -3114,19 +3114,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>9.2996640000000019E-2</v>
+        <v>0.12664674000000001</v>
       </c>
       <c r="F14">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G14">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H14">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I14">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J14" t="s">
         <v>33</v>
@@ -3170,7 +3170,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.26767125000000003</v>
+        <v>0.27361950000000002</v>
       </c>
       <c r="F15">
         <v>1923</v>
@@ -3226,7 +3226,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.23008140000000002</v>
+        <v>0.23519432000000001</v>
       </c>
       <c r="F16">
         <v>2200</v>
@@ -3282,7 +3282,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.23008140000000002</v>
+        <v>0.23519432000000001</v>
       </c>
       <c r="F17">
         <v>2200</v>
@@ -3338,7 +3338,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>8.4542400000000018E-2</v>
+        <v>8.6421120000000032E-2</v>
       </c>
       <c r="F18">
         <v>3583</v>
@@ -3394,19 +3394,19 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>9.2996640000000019E-2</v>
+        <v>0.12664674000000001</v>
       </c>
       <c r="F19">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G19">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H19">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I19">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J19" t="s">
         <v>38</v>
@@ -3450,19 +3450,19 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>9.2996640000000019E-2</v>
+        <v>0.12664674000000001</v>
       </c>
       <c r="F20">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G20">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H20">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I20">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J20" t="s">
         <v>39</v>
@@ -3506,7 +3506,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>9.0178560000000019E-2</v>
+        <v>9.2182528000000014E-2</v>
       </c>
       <c r="F21">
         <v>3583</v>
@@ -3562,7 +3562,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.24361560000000004</v>
+        <v>0.24902928000000002</v>
       </c>
       <c r="F22">
         <v>2200</v>
@@ -3618,7 +3618,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>8.4542400000000018E-2</v>
+        <v>8.6421120000000032E-2</v>
       </c>
       <c r="F23">
         <v>3583</v>
@@ -3674,7 +3674,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>8.4542400000000018E-2</v>
+        <v>8.6421120000000032E-2</v>
       </c>
       <c r="F24">
         <v>3583</v>
@@ -3730,7 +3730,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.26767125000000008</v>
+        <v>0.27361950000000002</v>
       </c>
       <c r="F25">
         <v>1923</v>
@@ -3786,7 +3786,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.23684850000000002</v>
+        <v>0.24211180000000002</v>
       </c>
       <c r="F26">
         <v>2200</v>
@@ -3842,7 +3842,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.23684850000000002</v>
+        <v>0.24211180000000002</v>
       </c>
       <c r="F27">
         <v>2200</v>
@@ -3898,7 +3898,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.23684850000000002</v>
+        <v>0.24211180000000002</v>
       </c>
       <c r="F28">
         <v>2200</v>
@@ -3954,7 +3954,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.23684850000000002</v>
+        <v>0.24211180000000002</v>
       </c>
       <c r="F29">
         <v>2200</v>
@@ -4010,7 +4010,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>9.0178560000000019E-2</v>
+        <v>9.2182528000000014E-2</v>
       </c>
       <c r="F30">
         <v>3583</v>
@@ -4066,7 +4066,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.23008140000000002</v>
+        <v>0.23519432000000001</v>
       </c>
       <c r="F31">
         <v>2200</v>
@@ -4122,7 +4122,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.23008140000000002</v>
+        <v>0.23519432000000001</v>
       </c>
       <c r="F32">
         <v>2200</v>
@@ -4178,7 +4178,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.23684850000000002</v>
+        <v>0.24211180000000002</v>
       </c>
       <c r="F33">
         <v>2200</v>
@@ -4234,7 +4234,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.24361560000000002</v>
+        <v>0.24902928000000008</v>
       </c>
       <c r="F34">
         <v>2200</v>
@@ -4290,7 +4290,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.24361560000000002</v>
+        <v>0.24902928000000008</v>
       </c>
       <c r="F35">
         <v>2200</v>
@@ -4346,7 +4346,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>9.0178560000000019E-2</v>
+        <v>9.2182528000000014E-2</v>
       </c>
       <c r="F36">
         <v>3583</v>
@@ -4402,7 +4402,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>9.0178560000000019E-2</v>
+        <v>9.2182528000000014E-2</v>
       </c>
       <c r="F37">
         <v>3583</v>
@@ -4458,7 +4458,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.12764790000000001</v>
+        <v>0.13048451999999999</v>
       </c>
       <c r="F38">
         <v>3144</v>
@@ -4514,19 +4514,19 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>9.2996640000000033E-2</v>
+        <v>0.12664674000000001</v>
       </c>
       <c r="F39">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G39">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H39">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I39">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J39" t="s">
         <v>58</v>
@@ -4570,19 +4570,19 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>9.2996640000000033E-2</v>
+        <v>0.12664674000000001</v>
       </c>
       <c r="F40">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G40">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H40">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I40">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J40" t="s">
         <v>59</v>
@@ -4626,7 +4626,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>8.4542400000000018E-2</v>
+        <v>8.6421120000000032E-2</v>
       </c>
       <c r="F41">
         <v>3583</v>
@@ -4682,7 +4682,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>8.4542400000000018E-2</v>
+        <v>8.6421120000000032E-2</v>
       </c>
       <c r="F42">
         <v>3583</v>
@@ -4738,7 +4738,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>8.4542400000000018E-2</v>
+        <v>8.6421120000000032E-2</v>
       </c>
       <c r="F43">
         <v>3583</v>
@@ -4794,7 +4794,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.26002350000000002</v>
+        <v>0.26580180000000003</v>
       </c>
       <c r="F44">
         <v>1923</v>
@@ -4850,7 +4850,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>9.0178560000000019E-2</v>
+        <v>9.2182528000000014E-2</v>
       </c>
       <c r="F45">
         <v>3583</v>
@@ -4906,7 +4906,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.23008140000000002</v>
+        <v>0.23519432000000001</v>
       </c>
       <c r="F46">
         <v>2200</v>
@@ -4962,7 +4962,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.23008140000000002</v>
+        <v>0.23519432000000001</v>
       </c>
       <c r="F47">
         <v>2200</v>
@@ -5018,7 +5018,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.10145088000000003</v>
+        <v>0.10370534400000003</v>
       </c>
       <c r="F48">
         <v>3583</v>
@@ -5074,7 +5074,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>9.2996640000000019E-2</v>
+        <v>9.5063232000000025E-2</v>
       </c>
       <c r="F49">
         <v>3583</v>
@@ -5130,7 +5130,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>9.581472000000002E-2</v>
+        <v>9.7943936000000023E-2</v>
       </c>
       <c r="F50">
         <v>3583</v>
@@ -5186,7 +5186,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>9.581472000000002E-2</v>
+        <v>9.7943936000000023E-2</v>
       </c>
       <c r="F51">
         <v>3583</v>
@@ -5242,7 +5242,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>9.581472000000002E-2</v>
+        <v>9.7943936000000023E-2</v>
       </c>
       <c r="F52">
         <v>3583</v>
@@ -5298,7 +5298,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>9.581472000000002E-2</v>
+        <v>9.7943936000000023E-2</v>
       </c>
       <c r="F53">
         <v>3583</v>
@@ -5354,7 +5354,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>9.581472000000002E-2</v>
+        <v>9.7943936000000023E-2</v>
       </c>
       <c r="F54">
         <v>3583</v>
@@ -5410,7 +5410,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>9.581472000000002E-2</v>
+        <v>9.7943936000000023E-2</v>
       </c>
       <c r="F55">
         <v>3583</v>
@@ -5466,7 +5466,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>9.581472000000002E-2</v>
+        <v>9.7943936000000023E-2</v>
       </c>
       <c r="F56">
         <v>3583</v>
@@ -5522,7 +5522,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>9.581472000000002E-2</v>
+        <v>9.7943936000000023E-2</v>
       </c>
       <c r="F57">
         <v>3583</v>
@@ -5578,7 +5578,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.17859581999999999</v>
+        <v>0.18256461599999999</v>
       </c>
       <c r="F58">
         <v>2757</v>
@@ -5634,7 +5634,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.30549285000000004</v>
+        <v>0.31228158</v>
       </c>
       <c r="F59">
         <v>1726</v>
@@ -5690,7 +5690,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.26170136999999999</v>
+        <v>0.26751695600000003</v>
       </c>
       <c r="F60">
         <v>1967</v>
@@ -5746,7 +5746,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.26170136999999999</v>
+        <v>0.26751695600000003</v>
       </c>
       <c r="F61">
         <v>1967</v>
@@ -5802,7 +5802,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.30549285000000004</v>
+        <v>0.31228158000000006</v>
       </c>
       <c r="F62">
         <v>1726</v>
@@ -5858,7 +5858,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>0.30549285000000004</v>
+        <v>0.31228158000000006</v>
       </c>
       <c r="F63">
         <v>1726</v>
@@ -5914,7 +5914,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>0.27584738999999997</v>
+        <v>0.28197733199999997</v>
       </c>
       <c r="F64">
         <v>1967</v>
@@ -5970,7 +5970,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>0.30549284999999998</v>
+        <v>0.31228158</v>
       </c>
       <c r="F65">
         <v>1726</v>
@@ -6026,7 +6026,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>0.30549284999999998</v>
+        <v>0.31228158</v>
       </c>
       <c r="F66">
         <v>1726</v>
@@ -6082,7 +6082,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>0.27584738999999997</v>
+        <v>0.28197733199999997</v>
       </c>
       <c r="F67">
         <v>1967</v>
@@ -6138,7 +6138,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>0.26170136999999999</v>
+        <v>0.26751695599999997</v>
       </c>
       <c r="F68">
         <v>1967</v>
@@ -6194,7 +6194,7 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>0.30767593500000001</v>
+        <v>0.314513178</v>
       </c>
       <c r="F69">
         <v>1967</v>
@@ -6250,7 +6250,7 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>0.340742025</v>
+        <v>0.34831406999999998</v>
       </c>
       <c r="F70">
         <v>1726</v>
@@ -6306,7 +6306,7 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>0.340742025</v>
+        <v>0.34831406999999998</v>
       </c>
       <c r="F71">
         <v>1726</v>
@@ -6362,7 +6362,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.34074202500000006</v>
+        <v>0.34831406999999998</v>
       </c>
       <c r="F72">
         <v>1726</v>
@@ -6418,7 +6418,7 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>0.340742025</v>
+        <v>0.34831406999999998</v>
       </c>
       <c r="F73">
         <v>1726</v>
@@ -6474,7 +6474,7 @@
         <v>14</v>
       </c>
       <c r="E74">
-        <v>0.340742025</v>
+        <v>0.34831406999999998</v>
       </c>
       <c r="F74">
         <v>1726</v>
@@ -6530,7 +6530,7 @@
         <v>14</v>
       </c>
       <c r="E75">
-        <v>0.32899230000000002</v>
+        <v>0.33630324</v>
       </c>
       <c r="F75">
         <v>1726</v>
@@ -6586,7 +6586,7 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>0.34074202500000006</v>
+        <v>0.34831406999999998</v>
       </c>
       <c r="F76">
         <v>1726</v>
@@ -6642,7 +6642,7 @@
         <v>14</v>
       </c>
       <c r="E77">
-        <v>0.340742025</v>
+        <v>0.34831406999999998</v>
       </c>
       <c r="F77">
         <v>1726</v>
@@ -6698,7 +6698,7 @@
         <v>14</v>
       </c>
       <c r="E78">
-        <v>0.340742025</v>
+        <v>0.34831406999999998</v>
       </c>
       <c r="F78">
         <v>1726</v>
@@ -6754,7 +6754,7 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>0.40556249999999999</v>
+        <v>0.41457500000000003</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -6810,7 +6810,7 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>0.40556250000000005</v>
+        <v>0.41457500000000003</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -6866,7 +6866,7 @@
         <v>14</v>
       </c>
       <c r="E81">
-        <v>0.42584062500000008</v>
+        <v>0.43530375000000004</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -6922,7 +6922,7 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>0.40556249999999999</v>
+        <v>0.41457500000000003</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -6978,7 +6978,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0.40556250000000005</v>
+        <v>0.41457500000000003</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -7034,7 +7034,7 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <v>0.42178500000000013</v>
+        <v>0.4311580000000001</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -7090,7 +7090,7 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>0.44206312500000011</v>
+        <v>0.45188675000000006</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -7146,7 +7146,7 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>0.42584062500000008</v>
+        <v>0.43530375000000004</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -7202,7 +7202,7 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <v>0.42178500000000002</v>
+        <v>0.43115799999999999</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -7258,7 +7258,7 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000007</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -7314,7 +7314,7 @@
         <v>14</v>
       </c>
       <c r="E89">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000007</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -7370,7 +7370,7 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.44206312500000011</v>
+        <v>0.45188675000000006</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -7426,7 +7426,7 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000007</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -7482,7 +7482,7 @@
         <v>14</v>
       </c>
       <c r="E92">
-        <v>0.32445000000000002</v>
+        <v>0.33165999999999995</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -7538,7 +7538,7 @@
         <v>14</v>
       </c>
       <c r="E93">
-        <v>0.32445000000000002</v>
+        <v>0.33165999999999995</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -7594,7 +7594,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.45423000000000008</v>
+        <v>0.46432400000000007</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -7650,7 +7650,7 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -7706,7 +7706,7 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.44206312500000011</v>
+        <v>0.45188675000000006</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -7762,7 +7762,7 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0.40556249999999999</v>
+        <v>0.41457500000000003</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -7818,7 +7818,7 @@
         <v>14</v>
       </c>
       <c r="E98">
-        <v>0.45423000000000008</v>
+        <v>0.46432400000000007</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -7874,7 +7874,7 @@
         <v>14</v>
       </c>
       <c r="E99">
-        <v>0.40556249999999999</v>
+        <v>0.41457500000000003</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -7930,7 +7930,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.44206312500000011</v>
+        <v>0.45188675000000006</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -7986,7 +7986,7 @@
         <v>14</v>
       </c>
       <c r="E101">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -8042,7 +8042,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -8098,7 +8098,7 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.40556249999999999</v>
+        <v>0.41457500000000008</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -8154,7 +8154,7 @@
         <v>14</v>
       </c>
       <c r="E104">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -8210,7 +8210,7 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.44206312500000011</v>
+        <v>0.45188675000000006</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -8266,7 +8266,7 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>0.42584062500000008</v>
+        <v>0.43530375000000016</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -8322,7 +8322,7 @@
         <v>14</v>
       </c>
       <c r="E107">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000007</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -8378,7 +8378,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.42584062500000008</v>
+        <v>0.43530375000000004</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -8434,7 +8434,7 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>0.42178500000000008</v>
+        <v>0.4311580000000001</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -8490,7 +8490,7 @@
         <v>14</v>
       </c>
       <c r="E110">
-        <v>0.44206312500000011</v>
+        <v>0.45188675000000006</v>
       </c>
       <c r="F110">
         <v>1365</v>
@@ -8546,7 +8546,7 @@
         <v>14</v>
       </c>
       <c r="E111">
-        <v>0.30822750000000004</v>
+        <v>0.31507700000000005</v>
       </c>
       <c r="F111">
         <v>1365</v>
@@ -8602,7 +8602,7 @@
         <v>14</v>
       </c>
       <c r="E112">
-        <v>0.44206312500000011</v>
+        <v>0.45188675000000006</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -8658,7 +8658,7 @@
         <v>14</v>
       </c>
       <c r="E113">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -8714,7 +8714,7 @@
         <v>14</v>
       </c>
       <c r="E114">
-        <v>0.42584062500000008</v>
+        <v>0.43530375000000004</v>
       </c>
       <c r="F114">
         <v>1365</v>
@@ -8770,7 +8770,7 @@
         <v>14</v>
       </c>
       <c r="E115">
-        <v>0.45423000000000008</v>
+        <v>0.46432400000000007</v>
       </c>
       <c r="F115">
         <v>1365</v>
@@ -8826,7 +8826,7 @@
         <v>14</v>
       </c>
       <c r="E116">
-        <v>0.45423000000000008</v>
+        <v>0.46432400000000007</v>
       </c>
       <c r="F116">
         <v>1365</v>
@@ -8882,7 +8882,7 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>0.42178500000000008</v>
+        <v>0.4311580000000001</v>
       </c>
       <c r="F117">
         <v>1365</v>
@@ -8938,7 +8938,7 @@
         <v>14</v>
       </c>
       <c r="E118">
-        <v>0.44206312500000011</v>
+        <v>0.45188675000000006</v>
       </c>
       <c r="F118">
         <v>1365</v>
@@ -8994,7 +8994,7 @@
         <v>14</v>
       </c>
       <c r="E119">
-        <v>0.44206312500000011</v>
+        <v>0.45188675000000006</v>
       </c>
       <c r="F119">
         <v>1365</v>
@@ -9050,7 +9050,7 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>0.42178500000000008</v>
+        <v>0.43115799999999999</v>
       </c>
       <c r="F120">
         <v>1365</v>
@@ -9106,7 +9106,7 @@
         <v>14</v>
       </c>
       <c r="E121">
-        <v>0.45423000000000008</v>
+        <v>0.46432400000000007</v>
       </c>
       <c r="F121">
         <v>1365</v>
@@ -9162,7 +9162,7 @@
         <v>14</v>
       </c>
       <c r="E122">
-        <v>0.48667500000000002</v>
+        <v>0.49749000000000004</v>
       </c>
       <c r="F122">
         <v>1365</v>
@@ -9218,7 +9218,7 @@
         <v>14</v>
       </c>
       <c r="E123">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F123">
         <v>1365</v>
@@ -9274,7 +9274,7 @@
         <v>14</v>
       </c>
       <c r="E124">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F124">
         <v>1365</v>
@@ -9330,7 +9330,7 @@
         <v>14</v>
       </c>
       <c r="E125">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F125">
         <v>1365</v>
@@ -9386,7 +9386,7 @@
         <v>14</v>
       </c>
       <c r="E126">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F126">
         <v>1365</v>
@@ -9442,7 +9442,7 @@
         <v>14</v>
       </c>
       <c r="E127">
-        <v>0.32445000000000002</v>
+        <v>0.33165999999999995</v>
       </c>
       <c r="F127">
         <v>1365</v>
@@ -9498,7 +9498,7 @@
         <v>14</v>
       </c>
       <c r="E128">
-        <v>0.34878375</v>
+        <v>0.35653450000000009</v>
       </c>
       <c r="F128">
         <v>1365</v>
@@ -9554,7 +9554,7 @@
         <v>14</v>
       </c>
       <c r="E129">
-        <v>0.48667500000000002</v>
+        <v>0.49749000000000004</v>
       </c>
       <c r="F129">
         <v>1365</v>
@@ -9610,7 +9610,7 @@
         <v>14</v>
       </c>
       <c r="E130">
-        <v>0.32445000000000002</v>
+        <v>0.33165999999999995</v>
       </c>
       <c r="F130">
         <v>1365</v>
@@ -9666,7 +9666,7 @@
         <v>14</v>
       </c>
       <c r="E131">
-        <v>0.34878375</v>
+        <v>0.35653450000000009</v>
       </c>
       <c r="F131">
         <v>1365</v>
@@ -9722,7 +9722,7 @@
         <v>14</v>
       </c>
       <c r="E132">
-        <v>0.30822750000000004</v>
+        <v>0.31507700000000005</v>
       </c>
       <c r="F132">
         <v>1365</v>
@@ -9778,7 +9778,7 @@
         <v>14</v>
       </c>
       <c r="E133">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F133">
         <v>1365</v>
@@ -9834,7 +9834,7 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>0.48667500000000002</v>
+        <v>0.49749000000000004</v>
       </c>
       <c r="F134">
         <v>1365</v>
@@ -9890,7 +9890,7 @@
         <v>14</v>
       </c>
       <c r="E135">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F135">
         <v>1365</v>
@@ -9946,7 +9946,7 @@
         <v>14</v>
       </c>
       <c r="E136">
-        <v>0.30822750000000004</v>
+        <v>0.31507700000000005</v>
       </c>
       <c r="F136">
         <v>1365</v>
@@ -10002,7 +10002,7 @@
         <v>14</v>
       </c>
       <c r="E137">
-        <v>0.42178500000000008</v>
+        <v>0.4311580000000001</v>
       </c>
       <c r="F137">
         <v>1365</v>
@@ -10058,7 +10058,7 @@
         <v>14</v>
       </c>
       <c r="E138">
-        <v>0.48667500000000002</v>
+        <v>0.49749000000000004</v>
       </c>
       <c r="F138">
         <v>1365</v>
@@ -10114,7 +10114,7 @@
         <v>14</v>
       </c>
       <c r="E139">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F139">
         <v>1365</v>
@@ -10170,7 +10170,7 @@
         <v>14</v>
       </c>
       <c r="E140">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F140">
         <v>1365</v>
@@ -10226,7 +10226,7 @@
         <v>14</v>
       </c>
       <c r="E141">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F141">
         <v>1365</v>
@@ -10282,7 +10282,7 @@
         <v>14</v>
       </c>
       <c r="E142">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F142">
         <v>1365</v>
@@ -10338,7 +10338,7 @@
         <v>14</v>
       </c>
       <c r="E143">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F143">
         <v>1365</v>
@@ -10394,7 +10394,7 @@
         <v>14</v>
       </c>
       <c r="E144">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F144">
         <v>1365</v>
@@ -10450,7 +10450,7 @@
         <v>14</v>
       </c>
       <c r="E145">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F145">
         <v>1365</v>
@@ -10506,7 +10506,7 @@
         <v>14</v>
       </c>
       <c r="E146">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F146">
         <v>1365</v>
@@ -10562,7 +10562,7 @@
         <v>14</v>
       </c>
       <c r="E147">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F147">
         <v>1365</v>
@@ -10618,7 +10618,7 @@
         <v>14</v>
       </c>
       <c r="E148">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F148">
         <v>1365</v>
@@ -10674,7 +10674,7 @@
         <v>14</v>
       </c>
       <c r="E149">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F149">
         <v>1365</v>
@@ -10730,7 +10730,7 @@
         <v>14</v>
       </c>
       <c r="E150">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F150">
         <v>1365</v>
@@ -10786,7 +10786,7 @@
         <v>14</v>
       </c>
       <c r="E151">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F151">
         <v>1365</v>
@@ -10842,7 +10842,7 @@
         <v>14</v>
       </c>
       <c r="E152">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F152">
         <v>1365</v>
@@ -10898,7 +10898,7 @@
         <v>14</v>
       </c>
       <c r="E153">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F153">
         <v>1365</v>
@@ -10954,7 +10954,7 @@
         <v>14</v>
       </c>
       <c r="E154">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F154">
         <v>1365</v>
@@ -11010,7 +11010,7 @@
         <v>14</v>
       </c>
       <c r="E155">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F155">
         <v>1365</v>
@@ -11066,7 +11066,7 @@
         <v>14</v>
       </c>
       <c r="E156">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F156">
         <v>1365</v>
@@ -11122,7 +11122,7 @@
         <v>14</v>
       </c>
       <c r="E157">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F157">
         <v>1365</v>
@@ -11178,7 +11178,7 @@
         <v>14</v>
       </c>
       <c r="E158">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F158">
         <v>1365</v>
@@ -11234,7 +11234,7 @@
         <v>14</v>
       </c>
       <c r="E159">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F159">
         <v>1365</v>
@@ -11290,7 +11290,7 @@
         <v>14</v>
       </c>
       <c r="E160">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F160">
         <v>1365</v>
@@ -11346,7 +11346,7 @@
         <v>14</v>
       </c>
       <c r="E161">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F161">
         <v>1365</v>
@@ -11402,7 +11402,7 @@
         <v>14</v>
       </c>
       <c r="E162">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F162">
         <v>1365</v>
@@ -11458,7 +11458,7 @@
         <v>14</v>
       </c>
       <c r="E163">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F163">
         <v>1365</v>
@@ -11514,7 +11514,7 @@
         <v>14</v>
       </c>
       <c r="E164">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F164">
         <v>1365</v>
@@ -11570,7 +11570,7 @@
         <v>14</v>
       </c>
       <c r="E165">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F165">
         <v>1365</v>
@@ -11626,7 +11626,7 @@
         <v>14</v>
       </c>
       <c r="E166">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F166">
         <v>1365</v>
@@ -11682,7 +11682,7 @@
         <v>14</v>
       </c>
       <c r="E167">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F167">
         <v>1365</v>
@@ -11738,7 +11738,7 @@
         <v>14</v>
       </c>
       <c r="E168">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F168">
         <v>1365</v>
@@ -11794,7 +11794,7 @@
         <v>14</v>
       </c>
       <c r="E169">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F169">
         <v>1365</v>
@@ -11829,7 +11829,7 @@
         <v>14</v>
       </c>
       <c r="E170">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F170">
         <v>1365</v>
@@ -11864,7 +11864,7 @@
         <v>14</v>
       </c>
       <c r="E171">
-        <v>0.47045249999999994</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F171">
         <v>1365</v>
@@ -11899,7 +11899,7 @@
         <v>14</v>
       </c>
       <c r="E172">
-        <v>0.20278125000000002</v>
+        <v>0.20728750000000001</v>
       </c>
       <c r="F172">
         <v>1365</v>
@@ -11934,7 +11934,7 @@
         <v>14</v>
       </c>
       <c r="E173">
-        <v>0.19467000000000001</v>
+        <v>0.19899600000000003</v>
       </c>
       <c r="F173">
         <v>1365</v>
@@ -11969,7 +11969,7 @@
         <v>14</v>
       </c>
       <c r="E174">
-        <v>0.23522624999999997</v>
+        <v>0.24045349999999999</v>
       </c>
       <c r="F174">
         <v>1365</v>
@@ -12004,7 +12004,7 @@
         <v>14</v>
       </c>
       <c r="E175">
-        <v>0.23522624999999997</v>
+        <v>0.24045349999999999</v>
       </c>
       <c r="F175">
         <v>1365</v>
@@ -12039,7 +12039,7 @@
         <v>14</v>
       </c>
       <c r="E176">
-        <v>0.26767125000000003</v>
+        <v>0.27361950000000002</v>
       </c>
       <c r="F176">
         <v>1365</v>
@@ -12074,7 +12074,7 @@
         <v>14</v>
       </c>
       <c r="E177">
-        <v>0.26767125000000003</v>
+        <v>0.27361950000000002</v>
       </c>
       <c r="F177">
         <v>1365</v>
@@ -12109,7 +12109,7 @@
         <v>14</v>
       </c>
       <c r="E178">
-        <v>0.19467000000000001</v>
+        <v>0.19899600000000003</v>
       </c>
       <c r="F178">
         <v>1365</v>
@@ -12144,7 +12144,7 @@
         <v>14</v>
       </c>
       <c r="E179">
-        <v>0.25956000000000001</v>
+        <v>0.26532800000000001</v>
       </c>
       <c r="F179">
         <v>1365</v>
@@ -12179,7 +12179,7 @@
         <v>14</v>
       </c>
       <c r="E180">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F180">
         <v>1365</v>
@@ -12214,7 +12214,7 @@
         <v>14</v>
       </c>
       <c r="E181">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F181">
         <v>1365</v>
@@ -12249,7 +12249,7 @@
         <v>14</v>
       </c>
       <c r="E182">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F182">
         <v>1365</v>
@@ -12284,7 +12284,7 @@
         <v>14</v>
       </c>
       <c r="E183">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F183">
         <v>1365</v>
@@ -12319,7 +12319,7 @@
         <v>14</v>
       </c>
       <c r="E184">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F184">
         <v>1365</v>
@@ -12354,7 +12354,7 @@
         <v>14</v>
       </c>
       <c r="E185">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F185">
         <v>1365</v>
@@ -12389,7 +12389,7 @@
         <v>14</v>
       </c>
       <c r="E186">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F186">
         <v>1365</v>
@@ -12424,7 +12424,7 @@
         <v>14</v>
       </c>
       <c r="E187">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F187">
         <v>1365</v>
@@ -12459,7 +12459,7 @@
         <v>14</v>
       </c>
       <c r="E188">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F188">
         <v>1365</v>
@@ -12494,7 +12494,7 @@
         <v>14</v>
       </c>
       <c r="E189">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F189">
         <v>1365</v>
@@ -12529,7 +12529,7 @@
         <v>14</v>
       </c>
       <c r="E190">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F190">
         <v>1365</v>
@@ -12564,7 +12564,7 @@
         <v>14</v>
       </c>
       <c r="E191">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F191">
         <v>1365</v>
@@ -12599,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="E192">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F192">
         <v>1365</v>
@@ -12634,7 +12634,7 @@
         <v>14</v>
       </c>
       <c r="E193">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F193">
         <v>1365</v>
@@ -12669,7 +12669,7 @@
         <v>14</v>
       </c>
       <c r="E194">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F194">
         <v>1365</v>
@@ -12704,7 +12704,7 @@
         <v>14</v>
       </c>
       <c r="E195">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F195">
         <v>1365</v>
@@ -12739,7 +12739,7 @@
         <v>14</v>
       </c>
       <c r="E196">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F196">
         <v>1365</v>
@@ -12774,7 +12774,7 @@
         <v>14</v>
       </c>
       <c r="E197">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F197">
         <v>1365</v>
@@ -12809,7 +12809,7 @@
         <v>14</v>
       </c>
       <c r="E198">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F198">
         <v>1365</v>
@@ -12844,7 +12844,7 @@
         <v>14</v>
       </c>
       <c r="E199">
-        <v>0.25400152918781727</v>
+        <v>0.2596460076142133</v>
       </c>
       <c r="F199">
         <v>1365</v>
@@ -12879,7 +12879,7 @@
         <v>14</v>
       </c>
       <c r="E200">
-        <v>0.28794937499999995</v>
+        <v>0.29434824999999998</v>
       </c>
       <c r="F200">
         <v>1365</v>
@@ -12914,7 +12914,7 @@
         <v>14</v>
       </c>
       <c r="E201">
-        <v>0.29200500000000007</v>
+        <v>0.29849400000000009</v>
       </c>
       <c r="F201">
         <v>1365</v>
@@ -12949,7 +12949,7 @@
         <v>14</v>
       </c>
       <c r="E202">
-        <v>0.29200500000000007</v>
+        <v>0.29849400000000009</v>
       </c>
       <c r="F202">
         <v>1365</v>
@@ -12984,7 +12984,7 @@
         <v>14</v>
       </c>
       <c r="E203">
-        <v>0.29200500000000007</v>
+        <v>0.29849400000000009</v>
       </c>
       <c r="F203">
         <v>1365</v>
@@ -13019,7 +13019,7 @@
         <v>14</v>
       </c>
       <c r="E204">
-        <v>0.29200500000000007</v>
+        <v>0.29849400000000009</v>
       </c>
       <c r="F204">
         <v>1365</v>
@@ -13054,7 +13054,7 @@
         <v>14</v>
       </c>
       <c r="E205">
-        <v>0.29200500000000007</v>
+        <v>0.29849400000000009</v>
       </c>
       <c r="F205">
         <v>1365</v>
@@ -13089,7 +13089,7 @@
         <v>14</v>
       </c>
       <c r="E206">
-        <v>0.29200500000000007</v>
+        <v>0.29849400000000009</v>
       </c>
       <c r="F206">
         <v>1365</v>
@@ -13124,7 +13124,7 @@
         <v>14</v>
       </c>
       <c r="E207">
-        <v>0.29200500000000007</v>
+        <v>0.29849400000000009</v>
       </c>
       <c r="F207">
         <v>1365</v>
@@ -13159,7 +13159,7 @@
         <v>14</v>
       </c>
       <c r="E208">
-        <v>0.29200500000000007</v>
+        <v>0.29849400000000009</v>
       </c>
       <c r="F208">
         <v>1365</v>
@@ -13194,7 +13194,7 @@
         <v>14</v>
       </c>
       <c r="E209">
-        <v>0.29200500000000007</v>
+        <v>0.29849400000000009</v>
       </c>
       <c r="F209">
         <v>1365</v>
@@ -13229,7 +13229,7 @@
         <v>14</v>
       </c>
       <c r="E210">
-        <v>0.29200500000000007</v>
+        <v>0.29849400000000009</v>
       </c>
       <c r="F210">
         <v>1365</v>
@@ -13264,7 +13264,7 @@
         <v>14</v>
       </c>
       <c r="E211">
-        <v>0.29200500000000007</v>
+        <v>0.29849400000000009</v>
       </c>
       <c r="F211">
         <v>1365</v>
@@ -13299,7 +13299,7 @@
         <v>14</v>
       </c>
       <c r="E212">
-        <v>0.29200500000000007</v>
+        <v>0.29849400000000009</v>
       </c>
       <c r="F212">
         <v>1365</v>
@@ -13334,7 +13334,7 @@
         <v>14</v>
       </c>
       <c r="E213">
-        <v>0.27983812500000005</v>
+        <v>0.28605674999999997</v>
       </c>
       <c r="F213">
         <v>1365</v>
@@ -13369,7 +13369,7 @@
         <v>14</v>
       </c>
       <c r="E214">
-        <v>0.29606062500000002</v>
+        <v>0.30263974999999993</v>
       </c>
       <c r="F214">
         <v>1365</v>
@@ -13404,7 +13404,7 @@
         <v>14</v>
       </c>
       <c r="E215">
-        <v>0.26767125000000003</v>
+        <v>0.27361950000000002</v>
       </c>
       <c r="F215">
         <v>1365</v>
@@ -13439,7 +13439,7 @@
         <v>14</v>
       </c>
       <c r="E216">
-        <v>0.26767125000000008</v>
+        <v>0.27361950000000002</v>
       </c>
       <c r="F216">
         <v>1365</v>
@@ -13474,7 +13474,7 @@
         <v>14</v>
       </c>
       <c r="E217">
-        <v>0.26767125000000003</v>
+        <v>0.27361950000000007</v>
       </c>
       <c r="F217">
         <v>1365</v>
@@ -13509,7 +13509,7 @@
         <v>14</v>
       </c>
       <c r="E218">
-        <v>0.27578249999999999</v>
+        <v>0.28191100000000002</v>
       </c>
       <c r="F218">
         <v>1365</v>
@@ -13544,7 +13544,7 @@
         <v>14</v>
       </c>
       <c r="E219">
-        <v>0.27578249999999999</v>
+        <v>0.28191100000000002</v>
       </c>
       <c r="F219">
         <v>1365</v>
@@ -13579,7 +13579,7 @@
         <v>14</v>
       </c>
       <c r="E220">
-        <v>0.26767125000000003</v>
+        <v>0.27361950000000002</v>
       </c>
       <c r="F220">
         <v>1365</v>
@@ -13614,7 +13614,7 @@
         <v>14</v>
       </c>
       <c r="E221">
-        <v>0.26767125000000003</v>
+        <v>0.27361950000000002</v>
       </c>
       <c r="F221">
         <v>1365</v>
@@ -13649,7 +13649,7 @@
         <v>14</v>
       </c>
       <c r="E222">
-        <v>0.24333750000000001</v>
+        <v>0.24874500000000002</v>
       </c>
       <c r="F222">
         <v>1365</v>
@@ -13684,7 +13684,7 @@
         <v>14</v>
       </c>
       <c r="E223">
-        <v>0.27578249999999999</v>
+        <v>0.28191099999999997</v>
       </c>
       <c r="F223">
         <v>1365</v>
@@ -13719,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="E224">
-        <v>0.26767125000000003</v>
+        <v>0.27361950000000002</v>
       </c>
       <c r="F224">
         <v>1365</v>
@@ -13754,7 +13754,7 @@
         <v>14</v>
       </c>
       <c r="E225">
-        <v>0.27983812500000005</v>
+        <v>0.28605674999999997</v>
       </c>
       <c r="F225">
         <v>1365</v>
@@ -13789,7 +13789,7 @@
         <v>14</v>
       </c>
       <c r="E226">
-        <v>0.23522624999999997</v>
+        <v>0.24045349999999999</v>
       </c>
       <c r="F226">
         <v>1365</v>
@@ -13824,7 +13824,7 @@
         <v>14</v>
       </c>
       <c r="E227">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F227">
         <v>1365</v>
@@ -13859,7 +13859,7 @@
         <v>14</v>
       </c>
       <c r="E228">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F228">
         <v>1365</v>
@@ -13894,7 +13894,7 @@
         <v>14</v>
       </c>
       <c r="E229">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F229">
         <v>1365</v>
@@ -13929,7 +13929,7 @@
         <v>14</v>
       </c>
       <c r="E230">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F230">
         <v>1365</v>
@@ -13964,7 +13964,7 @@
         <v>14</v>
       </c>
       <c r="E231">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F231">
         <v>1365</v>
@@ -13999,7 +13999,7 @@
         <v>14</v>
       </c>
       <c r="E232">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F232">
         <v>1365</v>
@@ -14034,7 +14034,7 @@
         <v>14</v>
       </c>
       <c r="E233">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F233">
         <v>1365</v>
@@ -14069,7 +14069,7 @@
         <v>14</v>
       </c>
       <c r="E234">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F234">
         <v>1365</v>
@@ -14104,7 +14104,7 @@
         <v>14</v>
       </c>
       <c r="E235">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F235">
         <v>1365</v>
@@ -14139,7 +14139,7 @@
         <v>14</v>
       </c>
       <c r="E236">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F236">
         <v>1365</v>
@@ -14174,7 +14174,7 @@
         <v>14</v>
       </c>
       <c r="E237">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F237">
         <v>1365</v>
@@ -14209,7 +14209,7 @@
         <v>14</v>
       </c>
       <c r="E238">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F238">
         <v>1365</v>
@@ -14244,7 +14244,7 @@
         <v>14</v>
       </c>
       <c r="E239">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F239">
         <v>1365</v>
@@ -14279,7 +14279,7 @@
         <v>14</v>
       </c>
       <c r="E240">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F240">
         <v>1365</v>
@@ -14314,7 +14314,7 @@
         <v>14</v>
       </c>
       <c r="E241">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F241">
         <v>1365</v>
@@ -14349,7 +14349,7 @@
         <v>14</v>
       </c>
       <c r="E242">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F242">
         <v>1365</v>
@@ -14384,7 +14384,7 @@
         <v>14</v>
       </c>
       <c r="E243">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F243">
         <v>1365</v>
@@ -14419,7 +14419,7 @@
         <v>14</v>
       </c>
       <c r="E244">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F244">
         <v>1365</v>
@@ -14454,7 +14454,7 @@
         <v>14</v>
       </c>
       <c r="E245">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F245">
         <v>1365</v>
@@ -14489,7 +14489,7 @@
         <v>14</v>
       </c>
       <c r="E246">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F246">
         <v>1365</v>
@@ -14524,7 +14524,7 @@
         <v>14</v>
       </c>
       <c r="E247">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F247">
         <v>1365</v>
@@ -14559,7 +14559,7 @@
         <v>14</v>
       </c>
       <c r="E248">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F248">
         <v>1365</v>
@@ -14594,7 +14594,7 @@
         <v>14</v>
       </c>
       <c r="E249">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F249">
         <v>1365</v>
@@ -14629,7 +14629,7 @@
         <v>14</v>
       </c>
       <c r="E250">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F250">
         <v>1365</v>
@@ -14664,7 +14664,7 @@
         <v>14</v>
       </c>
       <c r="E251">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F251">
         <v>1365</v>
@@ -14699,7 +14699,7 @@
         <v>14</v>
       </c>
       <c r="E252">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F252">
         <v>1365</v>
@@ -14734,7 +14734,7 @@
         <v>14</v>
       </c>
       <c r="E253">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F253">
         <v>1365</v>
@@ -14769,7 +14769,7 @@
         <v>14</v>
       </c>
       <c r="E254">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F254">
         <v>1365</v>
@@ -14804,7 +14804,7 @@
         <v>14</v>
       </c>
       <c r="E255">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F255">
         <v>1365</v>
@@ -14839,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="E256">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F256">
         <v>1365</v>
@@ -14874,7 +14874,7 @@
         <v>14</v>
       </c>
       <c r="E257">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F257">
         <v>1365</v>
@@ -14909,7 +14909,7 @@
         <v>14</v>
       </c>
       <c r="E258">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F258">
         <v>1365</v>
@@ -14944,7 +14944,7 @@
         <v>14</v>
       </c>
       <c r="E259">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F259">
         <v>1365</v>
@@ -14979,7 +14979,7 @@
         <v>14</v>
       </c>
       <c r="E260">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F260">
         <v>1365</v>
@@ -15014,7 +15014,7 @@
         <v>14</v>
       </c>
       <c r="E261">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F261">
         <v>1365</v>
@@ -15049,7 +15049,7 @@
         <v>14</v>
       </c>
       <c r="E262">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F262">
         <v>1365</v>
@@ -15084,7 +15084,7 @@
         <v>14</v>
       </c>
       <c r="E263">
-        <v>0.27761586472602745</v>
+        <v>0.28378510616438363</v>
       </c>
       <c r="F263">
         <v>1365</v>
@@ -15119,7 +15119,7 @@
         <v>14</v>
       </c>
       <c r="E264">
-        <v>0.29200500000000001</v>
+        <v>0.29849400000000004</v>
       </c>
       <c r="F264">
         <v>1365</v>
@@ -15154,7 +15154,7 @@
         <v>14</v>
       </c>
       <c r="E265">
-        <v>0.38934000000000002</v>
+        <v>0.39799200000000007</v>
       </c>
       <c r="F265">
         <v>1365</v>
@@ -15189,7 +15189,7 @@
         <v>14</v>
       </c>
       <c r="E266">
-        <v>0.43800749999999999</v>
+        <v>0.44774100000000006</v>
       </c>
       <c r="F266">
         <v>1365</v>
@@ -15224,7 +15224,7 @@
         <v>14</v>
       </c>
       <c r="E267">
-        <v>0.38934000000000002</v>
+        <v>0.39799200000000007</v>
       </c>
       <c r="F267">
         <v>1365</v>
@@ -15259,7 +15259,7 @@
         <v>14</v>
       </c>
       <c r="E268">
-        <v>0.38934000000000002</v>
+        <v>0.39799200000000007</v>
       </c>
       <c r="F268">
         <v>1365</v>
@@ -15294,7 +15294,7 @@
         <v>14</v>
       </c>
       <c r="E269">
-        <v>0.38934000000000002</v>
+        <v>0.39799200000000007</v>
       </c>
       <c r="F269">
         <v>1365</v>
@@ -15329,7 +15329,7 @@
         <v>14</v>
       </c>
       <c r="E270">
-        <v>0.19467000000000001</v>
+        <v>0.19899600000000003</v>
       </c>
       <c r="F270">
         <v>1365</v>
@@ -15364,7 +15364,7 @@
         <v>14</v>
       </c>
       <c r="E271">
-        <v>0.16222500000000001</v>
+        <v>0.16583000000000003</v>
       </c>
       <c r="F271">
         <v>1365</v>
@@ -15399,7 +15399,7 @@
         <v>14</v>
       </c>
       <c r="E272">
-        <v>0.23522624999999997</v>
+        <v>0.24045349999999999</v>
       </c>
       <c r="F272">
         <v>1365</v>
@@ -15434,7 +15434,7 @@
         <v>14</v>
       </c>
       <c r="E273">
-        <v>0.23522624999999997</v>
+        <v>0.24045349999999999</v>
       </c>
       <c r="F273">
         <v>1365</v>
@@ -15469,7 +15469,7 @@
         <v>14</v>
       </c>
       <c r="E274">
-        <v>0.23522624999999997</v>
+        <v>0.24045349999999999</v>
       </c>
       <c r="F274">
         <v>1365</v>
@@ -15504,7 +15504,7 @@
         <v>14</v>
       </c>
       <c r="E275">
-        <v>0.23522624999999997</v>
+        <v>0.24045349999999999</v>
       </c>
       <c r="F275">
         <v>1365</v>
@@ -15539,7 +15539,7 @@
         <v>14</v>
       </c>
       <c r="E276">
-        <v>0.24739312499999999</v>
+        <v>0.25289075</v>
       </c>
       <c r="F276">
         <v>1365</v>
@@ -15574,7 +15574,7 @@
         <v>14</v>
       </c>
       <c r="E277">
-        <v>0.28794937499999995</v>
+        <v>0.29434824999999998</v>
       </c>
       <c r="F277">
         <v>1365</v>
@@ -15609,7 +15609,7 @@
         <v>14</v>
       </c>
       <c r="E278">
-        <v>0.27172687500000003</v>
+        <v>0.27776525000000007</v>
       </c>
       <c r="F278">
         <v>1365</v>
@@ -15644,7 +15644,7 @@
         <v>14</v>
       </c>
       <c r="E279">
-        <v>0.27172687500000003</v>
+        <v>0.27776525000000007</v>
       </c>
       <c r="F279">
         <v>1365</v>
@@ -15679,7 +15679,7 @@
         <v>14</v>
       </c>
       <c r="E280">
-        <v>0.27172687500000003</v>
+        <v>0.27776525000000007</v>
       </c>
       <c r="F280">
         <v>1365</v>
@@ -15714,7 +15714,7 @@
         <v>14</v>
       </c>
       <c r="E281">
-        <v>0.27172687500000003</v>
+        <v>0.27776525000000007</v>
       </c>
       <c r="F281">
         <v>1365</v>
@@ -15744,7 +15744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97889FDA-DA1A-4AF5-9FCA-9B16D13B4126}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0E58D5-4CF6-47A1-8C69-DA39EBB52EA6}">
   <dimension ref="B9:T438"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15829,7 +15829,7 @@
         <v>0.04</v>
       </c>
       <c r="G11">
-        <v>0.22711500000000001</v>
+        <v>0.23216200000000004</v>
       </c>
       <c r="H11">
         <v>5197.5</v>
@@ -15882,7 +15882,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G12">
-        <v>0.22711500000000004</v>
+        <v>0.23216200000000004</v>
       </c>
       <c r="H12">
         <v>5197.5</v>
@@ -15935,7 +15935,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="G13">
-        <v>0.25956000000000007</v>
+        <v>0.26532800000000006</v>
       </c>
       <c r="H13">
         <v>5197.5</v>
@@ -15988,7 +15988,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G14">
-        <v>0.25956000000000007</v>
+        <v>0.26532800000000006</v>
       </c>
       <c r="H14">
         <v>5197.5</v>
@@ -16041,7 +16041,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="G15">
-        <v>0.25956000000000007</v>
+        <v>0.26532800000000006</v>
       </c>
       <c r="H15">
         <v>5197.5</v>
@@ -16094,7 +16094,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="G16">
-        <v>0.25956000000000007</v>
+        <v>0.26532800000000006</v>
       </c>
       <c r="H16">
         <v>5197.5</v>
@@ -16147,7 +16147,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="G17">
-        <v>0.25956000000000007</v>
+        <v>0.26532800000000012</v>
       </c>
       <c r="H17">
         <v>5197.5</v>
@@ -16200,7 +16200,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G18">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H18">
         <v>5197.5</v>
@@ -16253,7 +16253,7 @@
         <v>0.04</v>
       </c>
       <c r="G19">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H19">
         <v>5197.5</v>
@@ -16306,7 +16306,7 @@
         <v>8.777000000000001</v>
       </c>
       <c r="G20">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000001</v>
       </c>
       <c r="H20">
         <v>3850</v>
@@ -16359,7 +16359,7 @@
         <v>0.05</v>
       </c>
       <c r="G21">
-        <v>0.16686000000000001</v>
+        <v>0.17056800000000003</v>
       </c>
       <c r="H21">
         <v>5197.5</v>
@@ -16412,7 +16412,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G22">
-        <v>0.24565500000000004</v>
+        <v>0.25111400000000006</v>
       </c>
       <c r="H22">
         <v>4427.5</v>
@@ -16465,7 +16465,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G23">
-        <v>0.24565500000000004</v>
+        <v>0.25111400000000006</v>
       </c>
       <c r="H23">
         <v>4427.5</v>
@@ -16518,7 +16518,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="G24">
-        <v>0.24565500000000004</v>
+        <v>0.25111400000000006</v>
       </c>
       <c r="H24">
         <v>4427.5</v>
@@ -16571,7 +16571,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G25">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H25">
         <v>4427.5</v>
@@ -16624,7 +16624,7 @@
         <v>0.05</v>
       </c>
       <c r="G26">
-        <v>0.21321000000000004</v>
+        <v>0.21794800000000003</v>
       </c>
       <c r="H26">
         <v>5197.5</v>
@@ -16677,7 +16677,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G27">
-        <v>0.21321000000000004</v>
+        <v>0.21794800000000003</v>
       </c>
       <c r="H27">
         <v>4427.5</v>
@@ -16730,7 +16730,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G28">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H28">
         <v>4427.5</v>
@@ -16783,7 +16783,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G29">
-        <v>0.24565500000000004</v>
+        <v>0.25111400000000006</v>
       </c>
       <c r="H29">
         <v>4427.5</v>
@@ -16836,7 +16836,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="G30">
-        <v>0.28737000000000001</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H30">
         <v>4427.5</v>
@@ -16889,7 +16889,7 @@
         <v>0.1</v>
       </c>
       <c r="G31">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H31">
         <v>4427.5</v>
@@ -16942,7 +16942,7 @@
         <v>4.82E-2</v>
       </c>
       <c r="G32">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H32">
         <v>2970.0000000000005</v>
@@ -16995,7 +16995,7 @@
         <v>4.82E-2</v>
       </c>
       <c r="G33">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H33">
         <v>2970.0000000000005</v>
@@ -17048,7 +17048,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="G34">
-        <v>0.30203901098901098</v>
+        <v>0.30875098901098907</v>
       </c>
       <c r="H34">
         <v>2713.7362637362639</v>
@@ -17101,7 +17101,7 @@
         <v>0.14399999999999999</v>
       </c>
       <c r="G35">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H35">
         <v>2530</v>
@@ -17154,7 +17154,7 @@
         <v>0.16</v>
       </c>
       <c r="G36">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H36">
         <v>2530</v>
@@ -17207,7 +17207,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G37">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H37">
         <v>2530</v>
@@ -17260,7 +17260,7 @@
         <v>0.107</v>
       </c>
       <c r="G38">
-        <v>0.31249429906542059</v>
+        <v>0.31943861682242991</v>
       </c>
       <c r="H38">
         <v>2657.4766355140187</v>
@@ -17313,7 +17313,7 @@
         <v>3.7399999999999996E-2</v>
       </c>
       <c r="G39">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H39">
         <v>2970.0000000000005</v>
@@ -17366,7 +17366,7 @@
         <v>8.0874999999999986</v>
       </c>
       <c r="G40">
-        <v>0.33372000000000002</v>
+        <v>0.34113600000000005</v>
       </c>
       <c r="H40">
         <v>2200</v>
@@ -17419,7 +17419,7 @@
         <v>0.433</v>
       </c>
       <c r="G41">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000001</v>
       </c>
       <c r="H41">
         <v>2200</v>
@@ -17472,7 +17472,7 @@
         <v>0.78</v>
       </c>
       <c r="G42">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000001</v>
       </c>
       <c r="H42">
         <v>2200</v>
@@ -17525,7 +17525,7 @@
         <v>0.3</v>
       </c>
       <c r="G43">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H43">
         <v>2530</v>
@@ -17578,7 +17578,7 @@
         <v>0.3</v>
       </c>
       <c r="G44">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H44">
         <v>2530</v>
@@ -17631,7 +17631,7 @@
         <v>0.78</v>
       </c>
       <c r="G45">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000001</v>
       </c>
       <c r="H45">
         <v>2200</v>
@@ -17684,7 +17684,7 @@
         <v>0.5</v>
       </c>
       <c r="G46">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H46">
         <v>2200</v>
@@ -17737,7 +17737,7 @@
         <v>0.5</v>
       </c>
       <c r="G47">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H47">
         <v>2200</v>
@@ -17790,7 +17790,7 @@
         <v>0.112</v>
       </c>
       <c r="G48">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H48">
         <v>2530</v>
@@ -17843,7 +17843,7 @@
         <v>0.15</v>
       </c>
       <c r="G49">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H49">
         <v>2530</v>
@@ -17896,7 +17896,7 @@
         <v>0.15</v>
       </c>
       <c r="G50">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H50">
         <v>2530</v>
@@ -17949,7 +17949,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G51">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H51">
         <v>2530</v>
@@ -18002,7 +18002,7 @@
         <v>0.48</v>
       </c>
       <c r="G52">
-        <v>0.33372000000000007</v>
+        <v>0.34113600000000005</v>
       </c>
       <c r="H52">
         <v>2200</v>
@@ -18055,7 +18055,7 @@
         <v>0.125</v>
       </c>
       <c r="G53">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H53">
         <v>2530</v>
@@ -18108,7 +18108,7 @@
         <v>0.125</v>
       </c>
       <c r="G54">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H54">
         <v>2530</v>
@@ -18161,7 +18161,7 @@
         <v>0.81599999999999995</v>
       </c>
       <c r="G55">
-        <v>0.32445000000000007</v>
+        <v>0.33166000000000001</v>
       </c>
       <c r="H55">
         <v>2200</v>
@@ -18214,7 +18214,7 @@
         <v>0.53500000000000003</v>
       </c>
       <c r="G56">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000001</v>
       </c>
       <c r="H56">
         <v>2200</v>
@@ -18267,7 +18267,7 @@
         <v>0.53500000000000003</v>
       </c>
       <c r="G57">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000001</v>
       </c>
       <c r="H57">
         <v>2200</v>
@@ -18320,7 +18320,7 @@
         <v>0.53500000000000003</v>
       </c>
       <c r="G58">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000001</v>
       </c>
       <c r="H58">
         <v>2200</v>
@@ -18373,7 +18373,7 @@
         <v>0.53500000000000003</v>
       </c>
       <c r="G59">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000001</v>
       </c>
       <c r="H59">
         <v>2200</v>
@@ -18426,7 +18426,7 @@
         <v>0.12</v>
       </c>
       <c r="G60">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H60">
         <v>2530</v>
@@ -18479,7 +18479,7 @@
         <v>0.63</v>
       </c>
       <c r="G61">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H61">
         <v>2200</v>
@@ -18532,7 +18532,7 @@
         <v>0.63600000000000001</v>
       </c>
       <c r="G62">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H62">
         <v>2200</v>
@@ -18585,7 +18585,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G63">
-        <v>0.32445000000000002</v>
+        <v>0.33166000000000001</v>
       </c>
       <c r="H63">
         <v>2200</v>
@@ -18638,7 +18638,7 @@
         <v>0.49</v>
       </c>
       <c r="G64">
-        <v>0.33372000000000002</v>
+        <v>0.34113600000000011</v>
       </c>
       <c r="H64">
         <v>2200</v>
@@ -18691,7 +18691,7 @@
         <v>0.49</v>
       </c>
       <c r="G65">
-        <v>0.33372000000000002</v>
+        <v>0.34113600000000011</v>
       </c>
       <c r="H65">
         <v>2200</v>
@@ -18744,7 +18744,7 @@
         <v>0.37</v>
       </c>
       <c r="G66">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H66">
         <v>2200</v>
@@ -18797,7 +18797,7 @@
         <v>0.37</v>
       </c>
       <c r="G67">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H67">
         <v>2200</v>
@@ -18850,7 +18850,7 @@
         <v>0.20499999999999999</v>
       </c>
       <c r="G68">
-        <v>0.31518000000000002</v>
+        <v>0.32218399999999997</v>
       </c>
       <c r="H68">
         <v>2530</v>
@@ -18903,7 +18903,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="G69">
-        <v>0.30591000000000007</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H69">
         <v>2530</v>
@@ -18956,7 +18956,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="G70">
-        <v>0.30591000000000007</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H70">
         <v>2530</v>
@@ -19009,7 +19009,7 @@
         <v>0.16</v>
       </c>
       <c r="G71">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H71">
         <v>2530</v>
@@ -19062,7 +19062,7 @@
         <v>0.151</v>
       </c>
       <c r="G72">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H72">
         <v>2530</v>
@@ -19115,7 +19115,7 @@
         <v>0.13869999999999999</v>
       </c>
       <c r="G73">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H73">
         <v>2530</v>
@@ -19168,7 +19168,7 @@
         <v>0.72399999999999998</v>
       </c>
       <c r="G74">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H74">
         <v>2200</v>
@@ -19221,7 +19221,7 @@
         <v>0.34</v>
       </c>
       <c r="G75">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H75">
         <v>2200</v>
@@ -19274,7 +19274,7 @@
         <v>0.63</v>
       </c>
       <c r="G76">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H76">
         <v>2200</v>
@@ -19327,7 +19327,7 @@
         <v>0.625</v>
       </c>
       <c r="G77">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H77">
         <v>2200</v>
@@ -19380,7 +19380,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G78">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H78">
         <v>2530</v>
@@ -19433,7 +19433,7 @@
         <v>0.35</v>
       </c>
       <c r="G79">
-        <v>0.36153000000000002</v>
+        <v>0.369564</v>
       </c>
       <c r="H79">
         <v>2420</v>
@@ -19486,7 +19486,7 @@
         <v>0.90700000000000003</v>
       </c>
       <c r="G80">
-        <v>0.36153000000000002</v>
+        <v>0.369564</v>
       </c>
       <c r="H80">
         <v>2420</v>
@@ -19539,7 +19539,7 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="G81">
-        <v>0.34299000000000002</v>
+        <v>0.35061200000000003</v>
       </c>
       <c r="H81">
         <v>2420</v>
@@ -19592,7 +19592,7 @@
         <v>0.5</v>
       </c>
       <c r="G82">
-        <v>0.34299000000000002</v>
+        <v>0.35061200000000003</v>
       </c>
       <c r="H82">
         <v>2420</v>
@@ -19645,7 +19645,7 @@
         <v>0.93300000000000005</v>
       </c>
       <c r="G83">
-        <v>0.36153000000000002</v>
+        <v>0.36956400000000006</v>
       </c>
       <c r="H83">
         <v>2420</v>
@@ -19698,7 +19698,7 @@
         <v>0.93300000000000005</v>
       </c>
       <c r="G84">
-        <v>0.36153000000000002</v>
+        <v>0.36956400000000006</v>
       </c>
       <c r="H84">
         <v>2420</v>
@@ -19751,7 +19751,7 @@
         <v>0.55300000000000005</v>
       </c>
       <c r="G85">
-        <v>0.36153000000000002</v>
+        <v>0.369564</v>
       </c>
       <c r="H85">
         <v>2420</v>
@@ -19804,7 +19804,7 @@
         <v>0.8</v>
       </c>
       <c r="G86">
-        <v>0.36152999999999996</v>
+        <v>0.369564</v>
       </c>
       <c r="H86">
         <v>2420</v>
@@ -19857,7 +19857,7 @@
         <v>0.8</v>
       </c>
       <c r="G87">
-        <v>0.36152999999999996</v>
+        <v>0.369564</v>
       </c>
       <c r="H87">
         <v>2420</v>
@@ -19910,7 +19910,7 @@
         <v>0.55300000000000005</v>
       </c>
       <c r="G88">
-        <v>0.36153000000000002</v>
+        <v>0.369564</v>
       </c>
       <c r="H88">
         <v>2420</v>
@@ -19963,7 +19963,7 @@
         <v>0.47399999999999998</v>
       </c>
       <c r="G89">
-        <v>0.34299000000000002</v>
+        <v>0.35061199999999998</v>
       </c>
       <c r="H89">
         <v>2420</v>
@@ -20016,7 +20016,7 @@
         <v>0.67500000000000004</v>
       </c>
       <c r="G90">
-        <v>0.40324500000000002</v>
+        <v>0.41220600000000002</v>
       </c>
       <c r="H90">
         <v>2640</v>
@@ -20069,7 +20069,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G91">
-        <v>0.40324500000000002</v>
+        <v>0.41220600000000002</v>
       </c>
       <c r="H91">
         <v>2640</v>
@@ -20122,7 +20122,7 @@
         <v>0.91200000000000003</v>
       </c>
       <c r="G92">
-        <v>0.40324500000000002</v>
+        <v>0.41220600000000002</v>
       </c>
       <c r="H92">
         <v>2640</v>
@@ -20175,7 +20175,7 @@
         <v>0.81</v>
       </c>
       <c r="G93">
-        <v>0.40324500000000008</v>
+        <v>0.41220600000000002</v>
       </c>
       <c r="H93">
         <v>2640</v>
@@ -20228,7 +20228,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G94">
-        <v>0.40324500000000002</v>
+        <v>0.41220600000000002</v>
       </c>
       <c r="H94">
         <v>2640</v>
@@ -20281,7 +20281,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G95">
-        <v>0.40324500000000002</v>
+        <v>0.41220600000000002</v>
       </c>
       <c r="H95">
         <v>2640</v>
@@ -20334,7 +20334,7 @@
         <v>1.012</v>
       </c>
       <c r="G96">
-        <v>0.38934000000000002</v>
+        <v>0.39799200000000001</v>
       </c>
       <c r="H96">
         <v>2640</v>
@@ -20387,7 +20387,7 @@
         <v>0.91</v>
       </c>
       <c r="G97">
-        <v>0.40324500000000008</v>
+        <v>0.41220600000000002</v>
       </c>
       <c r="H97">
         <v>2640</v>
@@ -20440,7 +20440,7 @@
         <v>0.79</v>
       </c>
       <c r="G98">
-        <v>0.40324500000000002</v>
+        <v>0.41220600000000002</v>
       </c>
       <c r="H98">
         <v>2640</v>
@@ -20493,7 +20493,7 @@
         <v>0.83</v>
       </c>
       <c r="G99">
-        <v>0.40324500000000002</v>
+        <v>0.41220600000000002</v>
       </c>
       <c r="H99">
         <v>2640</v>
@@ -20546,7 +20546,7 @@
         <v>2.6499999999999999E-2</v>
       </c>
       <c r="G100">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H100">
         <v>1485.0000000000002</v>
@@ -20599,7 +20599,7 @@
         <v>0.108</v>
       </c>
       <c r="G101">
-        <v>0.32719666666666669</v>
+        <v>0.33446770370370371</v>
       </c>
       <c r="H101">
         <v>1342.4074074074074</v>
@@ -20652,7 +20652,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G102">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H102">
         <v>1485.0000000000002</v>
@@ -20705,7 +20705,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="G103">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H103">
         <v>1485.0000000000002</v>
@@ -20758,7 +20758,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G104">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H104">
         <v>1485.0000000000002</v>
@@ -20811,7 +20811,7 @@
         <v>0.02</v>
       </c>
       <c r="G105">
-        <v>0.33372000000000002</v>
+        <v>0.34113600000000005</v>
       </c>
       <c r="H105">
         <v>1485.0000000000002</v>
@@ -20864,7 +20864,7 @@
         <v>0.17299999999999999</v>
       </c>
       <c r="G106">
-        <v>0.35226000000000007</v>
+        <v>0.36008800000000002</v>
       </c>
       <c r="H106">
         <v>1265</v>
@@ -20917,7 +20917,7 @@
         <v>0.08</v>
       </c>
       <c r="G107">
-        <v>0.35226000000000002</v>
+        <v>0.36008800000000002</v>
       </c>
       <c r="H107">
         <v>1265</v>
@@ -20970,7 +20970,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G108">
-        <v>0.33372000000000002</v>
+        <v>0.34113600000000005</v>
       </c>
       <c r="H108">
         <v>1485.0000000000002</v>
@@ -21023,7 +21023,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G109">
-        <v>0.33371999999999996</v>
+        <v>0.34113600000000005</v>
       </c>
       <c r="H109">
         <v>1485.0000000000002</v>
@@ -21076,7 +21076,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="G110">
-        <v>0.39861000000000002</v>
+        <v>0.40746800000000005</v>
       </c>
       <c r="H110">
         <v>1265</v>
@@ -21129,7 +21129,7 @@
         <v>0.23799999999999999</v>
       </c>
       <c r="G111">
-        <v>0.45493109243697472</v>
+        <v>0.46504067226890766</v>
       </c>
       <c r="H111">
         <v>1366.6806722689075</v>
@@ -21182,7 +21182,7 @@
         <v>0.26900000000000002</v>
       </c>
       <c r="G112">
-        <v>0.46350000000000002</v>
+        <v>0.47380000000000011</v>
       </c>
       <c r="H112">
         <v>1265</v>
@@ -21235,7 +21235,7 @@
         <v>0.16</v>
       </c>
       <c r="G113">
-        <v>0.46349999999999997</v>
+        <v>0.47380000000000005</v>
       </c>
       <c r="H113">
         <v>1265</v>
@@ -21288,7 +21288,7 @@
         <v>0.14199999999999999</v>
       </c>
       <c r="G114">
-        <v>0.46350000000000008</v>
+        <v>0.47380000000000011</v>
       </c>
       <c r="H114">
         <v>1265</v>
@@ -21341,7 +21341,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="G115">
-        <v>0.45612183673469386</v>
+        <v>0.46625787755102049</v>
       </c>
       <c r="H115">
         <v>1352.5510204081634</v>
@@ -21394,7 +21394,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="G116">
-        <v>0.46350000000000008</v>
+        <v>0.47380000000000005</v>
       </c>
       <c r="H116">
         <v>1265</v>
@@ -21447,7 +21447,7 @@
         <v>0.1</v>
       </c>
       <c r="G117">
-        <v>0.46350000000000002</v>
+        <v>0.4738</v>
       </c>
       <c r="H117">
         <v>1265</v>
@@ -21500,7 +21500,7 @@
         <v>0.62879999999999991</v>
       </c>
       <c r="G118">
-        <v>0.47951315839694664</v>
+        <v>0.49016900636132327</v>
       </c>
       <c r="H118">
         <v>1294.984096692112</v>
@@ -21553,7 +21553,7 @@
         <v>7.8E-2</v>
       </c>
       <c r="G119">
-        <v>0.48204000000000008</v>
+        <v>0.49275200000000002</v>
       </c>
       <c r="H119">
         <v>1265</v>
@@ -21606,7 +21606,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G120">
-        <v>0.48204000000000002</v>
+        <v>0.49275200000000013</v>
       </c>
       <c r="H120">
         <v>1265</v>
@@ -21659,7 +21659,7 @@
         <v>0.19600000000000001</v>
       </c>
       <c r="G121">
-        <v>0.47825632653061234</v>
+        <v>0.48888424489795923</v>
       </c>
       <c r="H121">
         <v>1309.8979591836735</v>
@@ -21712,7 +21712,7 @@
         <v>0.13100000000000001</v>
       </c>
       <c r="G122">
-        <v>0.51204366412213753</v>
+        <v>0.52342241221374053</v>
       </c>
       <c r="H122">
         <v>1348.969465648855</v>
@@ -21765,7 +21765,7 @@
         <v>0.126</v>
       </c>
       <c r="G123">
-        <v>0.50058000000000002</v>
+        <v>0.51170400000000005</v>
       </c>
       <c r="H123">
         <v>1485.0000000000002</v>
@@ -21818,7 +21818,7 @@
         <v>0.1661</v>
       </c>
       <c r="G124">
-        <v>0.51387388320288985</v>
+        <v>0.52529330282962083</v>
       </c>
       <c r="H124">
         <v>1327.2516556291391</v>
@@ -21871,7 +21871,7 @@
         <v>0.18659999999999999</v>
       </c>
       <c r="G125">
-        <v>0.50932340836012868</v>
+        <v>0.52064170632368711</v>
       </c>
       <c r="H125">
         <v>1381.2486602357988</v>
@@ -21924,7 +21924,7 @@
         <v>0.24580000000000002</v>
       </c>
       <c r="G126">
-        <v>0.51912000000000003</v>
+        <v>0.53065600000000002</v>
       </c>
       <c r="H126">
         <v>1265</v>
@@ -21977,7 +21977,7 @@
         <v>3.9E-2</v>
       </c>
       <c r="G127">
-        <v>0.50058000000000002</v>
+        <v>0.51170400000000005</v>
       </c>
       <c r="H127">
         <v>1485.0000000000002</v>
@@ -22030,7 +22030,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G128">
-        <v>0.51912000000000014</v>
+        <v>0.53065600000000013</v>
       </c>
       <c r="H128">
         <v>1265</v>
@@ -22083,7 +22083,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="G129">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H129">
         <v>1265</v>
@@ -22136,7 +22136,7 @@
         <v>0.50900000000000001</v>
       </c>
       <c r="G130">
-        <v>0.5376599999999998</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H130">
         <v>1265</v>
@@ -22189,7 +22189,7 @@
         <v>0.155</v>
       </c>
       <c r="G131">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H131">
         <v>1265</v>
@@ -22242,7 +22242,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G132">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H132">
         <v>1265</v>
@@ -22295,7 +22295,7 @@
         <v>0.44733999999999347</v>
       </c>
       <c r="G133">
-        <v>0.55620000000000003</v>
+        <v>0.56856000000000007</v>
       </c>
       <c r="H133">
         <v>1100</v>
@@ -22348,7 +22348,7 @@
         <v>0.11600000000000001</v>
       </c>
       <c r="G134">
-        <v>0.46350000000000002</v>
+        <v>0.47380000000000005</v>
       </c>
       <c r="H134">
         <v>1265</v>
@@ -22401,7 +22401,7 @@
         <v>0.112</v>
       </c>
       <c r="G135">
-        <v>0.46350000000000008</v>
+        <v>0.47380000000000005</v>
       </c>
       <c r="H135">
         <v>1265</v>
@@ -22454,7 +22454,7 @@
         <v>0.46100000000000002</v>
       </c>
       <c r="G136">
-        <v>0.48667500000000008</v>
+        <v>0.4974900000000001</v>
       </c>
       <c r="H136">
         <v>1100</v>
@@ -22507,7 +22507,7 @@
         <v>0.23100000000000001</v>
       </c>
       <c r="G137">
-        <v>0.46350000000000002</v>
+        <v>0.47380000000000005</v>
       </c>
       <c r="H137">
         <v>1265</v>
@@ -22560,7 +22560,7 @@
         <v>0.112</v>
       </c>
       <c r="G138">
-        <v>0.46350000000000008</v>
+        <v>0.47380000000000005</v>
       </c>
       <c r="H138">
         <v>1265</v>
@@ -22613,7 +22613,7 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="G139">
-        <v>0.48204000000000014</v>
+        <v>0.49275200000000008</v>
       </c>
       <c r="H139">
         <v>1265</v>
@@ -22666,7 +22666,7 @@
         <v>0.41699999999999998</v>
       </c>
       <c r="G140">
-        <v>0.50521500000000008</v>
+        <v>0.51644200000000007</v>
       </c>
       <c r="H140">
         <v>1100</v>
@@ -22719,7 +22719,7 @@
         <v>0.58599999999999997</v>
       </c>
       <c r="G141">
-        <v>0.48667500000000014</v>
+        <v>0.49749000000000004</v>
       </c>
       <c r="H141">
         <v>1100</v>
@@ -22772,7 +22772,7 @@
         <v>0.23400000000000001</v>
       </c>
       <c r="G142">
-        <v>0.48204000000000002</v>
+        <v>0.49275200000000002</v>
       </c>
       <c r="H142">
         <v>1265</v>
@@ -22825,7 +22825,7 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="G143">
-        <v>0.37079999999999996</v>
+        <v>0.37904000000000004</v>
       </c>
       <c r="H143">
         <v>1100</v>
@@ -22878,7 +22878,7 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="G144">
-        <v>0.37079999999999996</v>
+        <v>0.37904000000000004</v>
       </c>
       <c r="H144">
         <v>1100</v>
@@ -22931,7 +22931,7 @@
         <v>0.88700000000000001</v>
       </c>
       <c r="G145">
-        <v>0.50521500000000008</v>
+        <v>0.51644200000000007</v>
       </c>
       <c r="H145">
         <v>1100</v>
@@ -22984,7 +22984,7 @@
         <v>0.39500000000000002</v>
       </c>
       <c r="G146">
-        <v>0.37080000000000002</v>
+        <v>0.37904000000000004</v>
       </c>
       <c r="H146">
         <v>1100</v>
@@ -23037,7 +23037,7 @@
         <v>0.44</v>
       </c>
       <c r="G147">
-        <v>0.37080000000000002</v>
+        <v>0.37903999999999999</v>
       </c>
       <c r="H147">
         <v>1100</v>
@@ -23090,7 +23090,7 @@
         <v>0.35499999999999998</v>
       </c>
       <c r="G148">
-        <v>0.37080000000000002</v>
+        <v>0.37903999999999999</v>
       </c>
       <c r="H148">
         <v>1100</v>
@@ -23143,7 +23143,7 @@
         <v>0.23</v>
       </c>
       <c r="G149">
-        <v>0.51912000000000014</v>
+        <v>0.53065600000000013</v>
       </c>
       <c r="H149">
         <v>1265</v>
@@ -23196,7 +23196,7 @@
         <v>0.56100000000000005</v>
       </c>
       <c r="G150">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H150">
         <v>1100</v>
@@ -23249,7 +23249,7 @@
         <v>0.84599999999999997</v>
       </c>
       <c r="G151">
-        <v>0.50521500000000008</v>
+        <v>0.51644200000000007</v>
       </c>
       <c r="H151">
         <v>1100</v>
@@ -23302,7 +23302,7 @@
         <v>0.182</v>
       </c>
       <c r="G152">
-        <v>0.46350000000000002</v>
+        <v>0.47380000000000005</v>
       </c>
       <c r="H152">
         <v>1265</v>
@@ -23355,7 +23355,7 @@
         <v>0.1288</v>
       </c>
       <c r="G153">
-        <v>0.51912000000000014</v>
+        <v>0.53065600000000013</v>
       </c>
       <c r="H153">
         <v>1265</v>
@@ -23408,7 +23408,7 @@
         <v>0.16</v>
       </c>
       <c r="G154">
-        <v>0.46349999999999997</v>
+        <v>0.47380000000000005</v>
       </c>
       <c r="H154">
         <v>1265</v>
@@ -23461,7 +23461,7 @@
         <v>0.80200000000000005</v>
       </c>
       <c r="G155">
-        <v>0.50521500000000008</v>
+        <v>0.51644200000000007</v>
       </c>
       <c r="H155">
         <v>1100</v>
@@ -23514,7 +23514,7 @@
         <v>0.45</v>
       </c>
       <c r="G156">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H156">
         <v>1100</v>
@@ -23567,7 +23567,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="G157">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H157">
         <v>1100</v>
@@ -23620,7 +23620,7 @@
         <v>0.17199999999999999</v>
       </c>
       <c r="G158">
-        <v>0.46350000000000002</v>
+        <v>0.47380000000000011</v>
       </c>
       <c r="H158">
         <v>1265</v>
@@ -23673,7 +23673,7 @@
         <v>0.315</v>
       </c>
       <c r="G159">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H159">
         <v>1100</v>
@@ -23726,7 +23726,7 @@
         <v>0.503</v>
       </c>
       <c r="G160">
-        <v>0.50521500000000008</v>
+        <v>0.51644200000000007</v>
       </c>
       <c r="H160">
         <v>1100</v>
@@ -23779,7 +23779,7 @@
         <v>0.41499999999999998</v>
       </c>
       <c r="G161">
-        <v>0.48667500000000008</v>
+        <v>0.49749000000000015</v>
       </c>
       <c r="H161">
         <v>1100</v>
@@ -23832,7 +23832,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="G162">
-        <v>0.37080000000000002</v>
+        <v>0.37904000000000004</v>
       </c>
       <c r="H162">
         <v>1100</v>
@@ -23885,7 +23885,7 @@
         <v>0.434</v>
       </c>
       <c r="G163">
-        <v>0.48667500000000008</v>
+        <v>0.4974900000000001</v>
       </c>
       <c r="H163">
         <v>1100</v>
@@ -23938,7 +23938,7 @@
         <v>0.128</v>
       </c>
       <c r="G164">
-        <v>0.48204000000000008</v>
+        <v>0.49275200000000008</v>
       </c>
       <c r="H164">
         <v>1265</v>
@@ -23991,7 +23991,7 @@
         <v>0.42899999999999999</v>
       </c>
       <c r="G165">
-        <v>0.50521500000000008</v>
+        <v>0.51644200000000007</v>
       </c>
       <c r="H165">
         <v>1100</v>
@@ -24044,7 +24044,7 @@
         <v>0.214</v>
       </c>
       <c r="G166">
-        <v>0.35226000000000002</v>
+        <v>0.36008800000000002</v>
       </c>
       <c r="H166">
         <v>1265</v>
@@ -24097,7 +24097,7 @@
         <v>0.41299999999999998</v>
       </c>
       <c r="G167">
-        <v>0.50521500000000008</v>
+        <v>0.51644200000000007</v>
       </c>
       <c r="H167">
         <v>1100</v>
@@ -24150,7 +24150,7 @@
         <v>0.46</v>
       </c>
       <c r="G168">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H168">
         <v>1100</v>
@@ -24203,7 +24203,7 @@
         <v>0.36299999999999999</v>
       </c>
       <c r="G169">
-        <v>0.48667500000000008</v>
+        <v>0.4974900000000001</v>
       </c>
       <c r="H169">
         <v>1100</v>
@@ -24256,7 +24256,7 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="G170">
-        <v>0.51912000000000014</v>
+        <v>0.53065600000000013</v>
       </c>
       <c r="H170">
         <v>1265</v>
@@ -24309,7 +24309,7 @@
         <v>0.13400000000000001</v>
       </c>
       <c r="G171">
-        <v>0.51912000000000014</v>
+        <v>0.53065600000000013</v>
       </c>
       <c r="H171">
         <v>1265</v>
@@ -24362,7 +24362,7 @@
         <v>0.127</v>
       </c>
       <c r="G172">
-        <v>0.48204000000000008</v>
+        <v>0.49275200000000008</v>
       </c>
       <c r="H172">
         <v>1265</v>
@@ -24415,7 +24415,7 @@
         <v>0.41699999999999998</v>
       </c>
       <c r="G173">
-        <v>0.50521500000000008</v>
+        <v>0.51644200000000007</v>
       </c>
       <c r="H173">
         <v>1100</v>
@@ -24468,7 +24468,7 @@
         <v>0.42099999999999999</v>
       </c>
       <c r="G174">
-        <v>0.50521500000000008</v>
+        <v>0.51644200000000007</v>
       </c>
       <c r="H174">
         <v>1100</v>
@@ -24521,7 +24521,7 @@
         <v>0.112</v>
       </c>
       <c r="G175">
-        <v>0.48204000000000008</v>
+        <v>0.49275200000000002</v>
       </c>
       <c r="H175">
         <v>1265</v>
@@ -24574,7 +24574,7 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="G176">
-        <v>0.51912000000000014</v>
+        <v>0.53065600000000013</v>
       </c>
       <c r="H176">
         <v>1265</v>
@@ -24627,7 +24627,7 @@
         <v>0.72499999999999998</v>
       </c>
       <c r="G177">
-        <v>0.55620000000000003</v>
+        <v>0.56856000000000007</v>
       </c>
       <c r="H177">
         <v>1100</v>
@@ -24680,7 +24680,7 @@
         <v>0.13800000000000001</v>
       </c>
       <c r="G178">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H178">
         <v>1265</v>
@@ -24733,7 +24733,7 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="G179">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H179">
         <v>1265</v>
@@ -24786,7 +24786,7 @@
         <v>0.14399999999999999</v>
       </c>
       <c r="G180">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H180">
         <v>1265</v>
@@ -24839,7 +24839,7 @@
         <v>0.14399999999999999</v>
       </c>
       <c r="G181">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H181">
         <v>1265</v>
@@ -24892,7 +24892,7 @@
         <v>0.35499999999999998</v>
       </c>
       <c r="G182">
-        <v>0.37080000000000002</v>
+        <v>0.37903999999999999</v>
       </c>
       <c r="H182">
         <v>1100</v>
@@ -24945,7 +24945,7 @@
         <v>0.13</v>
       </c>
       <c r="G183">
-        <v>0.39861000000000002</v>
+        <v>0.40746800000000005</v>
       </c>
       <c r="H183">
         <v>1265</v>
@@ -24998,7 +24998,7 @@
         <v>0.44</v>
       </c>
       <c r="G184">
-        <v>0.55620000000000003</v>
+        <v>0.56856000000000007</v>
       </c>
       <c r="H184">
         <v>1100</v>
@@ -25051,7 +25051,7 @@
         <v>0.35499999999999998</v>
       </c>
       <c r="G185">
-        <v>0.37080000000000002</v>
+        <v>0.37903999999999999</v>
       </c>
       <c r="H185">
         <v>1100</v>
@@ -25104,7 +25104,7 @@
         <v>0.125</v>
       </c>
       <c r="G186">
-        <v>0.39861000000000002</v>
+        <v>0.40746800000000005</v>
       </c>
       <c r="H186">
         <v>1265</v>
@@ -25157,7 +25157,7 @@
         <v>0.254</v>
       </c>
       <c r="G187">
-        <v>0.35226000000000002</v>
+        <v>0.36008800000000002</v>
       </c>
       <c r="H187">
         <v>1265</v>
@@ -25210,7 +25210,7 @@
         <v>0.114</v>
       </c>
       <c r="G188">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H188">
         <v>1265</v>
@@ -25263,7 +25263,7 @@
         <v>0.75</v>
       </c>
       <c r="G189">
-        <v>0.55620000000000003</v>
+        <v>0.56856000000000007</v>
       </c>
       <c r="H189">
         <v>1100</v>
@@ -25316,7 +25316,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="G190">
-        <v>0.53765999999999992</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H190">
         <v>1265</v>
@@ -25369,7 +25369,7 @@
         <v>0.23799999999999999</v>
       </c>
       <c r="G191">
-        <v>0.35226000000000002</v>
+        <v>0.36008800000000002</v>
       </c>
       <c r="H191">
         <v>1265</v>
@@ -25422,7 +25422,7 @@
         <v>0.115</v>
       </c>
       <c r="G192">
-        <v>0.48204000000000008</v>
+        <v>0.49275200000000008</v>
       </c>
       <c r="H192">
         <v>1265</v>
@@ -25475,7 +25475,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G193">
-        <v>0.18539999999999998</v>
+        <v>0.18952000000000002</v>
       </c>
       <c r="H193">
         <v>1188</v>
@@ -25528,7 +25528,7 @@
         <v>0.05</v>
       </c>
       <c r="G194">
-        <v>0.20394000000000001</v>
+        <v>0.20847200000000002</v>
       </c>
       <c r="H194">
         <v>1188</v>
@@ -25581,7 +25581,7 @@
         <v>0.22500000000000001</v>
       </c>
       <c r="G195">
-        <v>0.21321000000000004</v>
+        <v>0.21794800000000003</v>
       </c>
       <c r="H195">
         <v>1012</v>
@@ -25634,7 +25634,7 @@
         <v>6.6700000000000009E-2</v>
       </c>
       <c r="G196">
-        <v>0.21321000000000004</v>
+        <v>0.21794800000000003</v>
       </c>
       <c r="H196">
         <v>1012.0000000000001</v>
@@ -25687,7 +25687,7 @@
         <v>0.29569999999999996</v>
       </c>
       <c r="G197">
-        <v>0.21321000000000007</v>
+        <v>0.217948</v>
       </c>
       <c r="H197">
         <v>1012.0000000000001</v>
@@ -25740,7 +25740,7 @@
         <v>0.152</v>
       </c>
       <c r="G198">
-        <v>0.22248000000000001</v>
+        <v>0.22742400000000002</v>
       </c>
       <c r="H198">
         <v>1188</v>
@@ -25793,7 +25793,7 @@
         <v>3.9E-2</v>
       </c>
       <c r="G199">
-        <v>0.22247999999999998</v>
+        <v>0.22742400000000002</v>
       </c>
       <c r="H199">
         <v>1188</v>
@@ -25846,7 +25846,7 @@
         <v>0.15</v>
       </c>
       <c r="G200">
-        <v>0.22248000000000001</v>
+        <v>0.22742400000000004</v>
       </c>
       <c r="H200">
         <v>1188</v>
@@ -25899,7 +25899,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G201">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H201">
         <v>1012</v>
@@ -25952,7 +25952,7 @@
         <v>3.0699999999999998E-2</v>
       </c>
       <c r="G202">
-        <v>0.25956000000000007</v>
+        <v>0.26532800000000006</v>
       </c>
       <c r="H202">
         <v>1188</v>
@@ -26005,7 +26005,7 @@
         <v>4.4499999999999998E-2</v>
       </c>
       <c r="G203">
-        <v>0.25956000000000007</v>
+        <v>0.26532800000000006</v>
       </c>
       <c r="H203">
         <v>1188</v>
@@ -26058,7 +26058,7 @@
         <v>2.9499999999999998E-2</v>
       </c>
       <c r="G204">
-        <v>0.25956000000000007</v>
+        <v>0.26532800000000006</v>
       </c>
       <c r="H204">
         <v>1188</v>
@@ -26111,7 +26111,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G205">
-        <v>0.25956000000000007</v>
+        <v>0.26532800000000006</v>
       </c>
       <c r="H205">
         <v>1188</v>
@@ -26164,7 +26164,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="G206">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H206">
         <v>1188</v>
@@ -26217,7 +26217,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G207">
-        <v>0.28737000000000001</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H207">
         <v>1012</v>
@@ -26270,7 +26270,7 @@
         <v>0.02</v>
       </c>
       <c r="G208">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H208">
         <v>1188</v>
@@ -26323,7 +26323,7 @@
         <v>0.02</v>
       </c>
       <c r="G209">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H209">
         <v>1188</v>
@@ -26376,7 +26376,7 @@
         <v>0.1</v>
       </c>
       <c r="G210">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H210">
         <v>1188</v>
@@ -26429,7 +26429,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G211">
-        <v>0.28737000000000001</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H211">
         <v>1188</v>
@@ -26482,7 +26482,7 @@
         <v>0.59099999999999997</v>
       </c>
       <c r="G212">
-        <v>0.29028746192893401</v>
+        <v>0.29673829441624378</v>
       </c>
       <c r="H212">
         <v>1132.6091370558377</v>
@@ -26535,7 +26535,7 @@
         <v>0.112</v>
       </c>
       <c r="G213">
-        <v>0.23175000000000004</v>
+        <v>0.23690000000000003</v>
       </c>
       <c r="H213">
         <v>1012</v>
@@ -26588,7 +26588,7 @@
         <v>0.32100000000000001</v>
       </c>
       <c r="G214">
-        <v>0.22248000000000001</v>
+        <v>0.22742400000000002</v>
       </c>
       <c r="H214">
         <v>880.00000000000023</v>
@@ -26641,7 +26641,7 @@
         <v>0.2</v>
       </c>
       <c r="G215">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H215">
         <v>1012</v>
@@ -26694,7 +26694,7 @@
         <v>0.2</v>
       </c>
       <c r="G216">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H216">
         <v>1012</v>
@@ -26747,7 +26747,7 @@
         <v>0.31900000000000001</v>
       </c>
       <c r="G217">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H217">
         <v>880.00000000000023</v>
@@ -26800,7 +26800,7 @@
         <v>0.32</v>
       </c>
       <c r="G218">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H218">
         <v>880.00000000000023</v>
@@ -26853,7 +26853,7 @@
         <v>0.45</v>
       </c>
       <c r="G219">
-        <v>0.22248000000000001</v>
+        <v>0.22742400000000002</v>
       </c>
       <c r="H219">
         <v>880.00000000000011</v>
@@ -26906,7 +26906,7 @@
         <v>0.3</v>
       </c>
       <c r="G220">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H220">
         <v>1012</v>
@@ -26959,7 +26959,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="G221">
-        <v>0.28737000000000001</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H221">
         <v>1633.5000000000002</v>
@@ -27012,7 +27012,7 @@
         <v>3.1199999999999999E-2</v>
       </c>
       <c r="G222">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H222">
         <v>1633.5000000000002</v>
@@ -27065,7 +27065,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="G223">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H223">
         <v>1633.5000000000005</v>
@@ -27118,7 +27118,7 @@
         <v>6.4200000000000007E-2</v>
       </c>
       <c r="G224">
-        <v>0.31981499999999996</v>
+        <v>0.32692199999999999</v>
       </c>
       <c r="H224">
         <v>1633.5</v>
@@ -27171,7 +27171,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G225">
-        <v>0.32908499999999996</v>
+        <v>0.33639799999999997</v>
       </c>
       <c r="H225">
         <v>1633.5000000000002</v>
@@ -27224,7 +27224,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G226">
-        <v>0.32908499999999996</v>
+        <v>0.33639799999999997</v>
       </c>
       <c r="H226">
         <v>1633.5000000000002</v>
@@ -27277,7 +27277,7 @@
         <v>3.0899999999999997E-2</v>
       </c>
       <c r="G227">
-        <v>0.32908499999999996</v>
+        <v>0.33639799999999997</v>
       </c>
       <c r="H227">
         <v>1633.5000000000002</v>
@@ -27330,7 +27330,7 @@
         <v>0.13150000000000001</v>
       </c>
       <c r="G228">
-        <v>0.32908499999999996</v>
+        <v>0.33639799999999992</v>
       </c>
       <c r="H228">
         <v>1449.4695817490494</v>
@@ -27383,7 +27383,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G229">
-        <v>0.33372000000000002</v>
+        <v>0.34113600000000011</v>
       </c>
       <c r="H229">
         <v>1467.921052631579</v>
@@ -27436,7 +27436,7 @@
         <v>0.2515</v>
       </c>
       <c r="G230">
-        <v>0.33372000000000007</v>
+        <v>0.34113599999999999</v>
       </c>
       <c r="H230">
         <v>1439.6113320079523</v>
@@ -27489,7 +27489,7 @@
         <v>0.25619999999999998</v>
       </c>
       <c r="G231">
-        <v>0.33372000000000002</v>
+        <v>0.34113600000000011</v>
       </c>
       <c r="H231">
         <v>1391.5</v>
@@ -27542,7 +27542,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="G232">
-        <v>0.33372000000000002</v>
+        <v>0.34113600000000005</v>
       </c>
       <c r="H232">
         <v>1391.5</v>
@@ -27595,7 +27595,7 @@
         <v>0.192</v>
       </c>
       <c r="G233">
-        <v>0.32908499999999996</v>
+        <v>0.33639799999999997</v>
       </c>
       <c r="H233">
         <v>1391.5</v>
@@ -27648,7 +27648,7 @@
         <v>0.09</v>
       </c>
       <c r="G234">
-        <v>0.23638500000000001</v>
+        <v>0.24163799999999999</v>
       </c>
       <c r="H234">
         <v>1782.0000000000002</v>
@@ -27701,7 +27701,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="G235">
-        <v>0.24565500000000004</v>
+        <v>0.25111400000000006</v>
       </c>
       <c r="H235">
         <v>1518.0000000000002</v>
@@ -27754,7 +27754,7 @@
         <v>0.154</v>
       </c>
       <c r="G236">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H236">
         <v>1518.0000000000005</v>
@@ -27807,7 +27807,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G237">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H237">
         <v>1518.0000000000002</v>
@@ -27860,7 +27860,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G238">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H238">
         <v>1518.0000000000002</v>
@@ -27913,7 +27913,7 @@
         <v>0.10100000000000001</v>
       </c>
       <c r="G239">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H239">
         <v>1518.0000000000002</v>
@@ -27966,7 +27966,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="G240">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H240">
         <v>1518.0000000000002</v>
@@ -28019,7 +28019,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="G241">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H241">
         <v>1782.0000000000002</v>
@@ -28072,7 +28072,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="G242">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H242">
         <v>1782.0000000000002</v>
@@ -28125,7 +28125,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G243">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H243">
         <v>1782.0000000000005</v>
@@ -28178,7 +28178,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G244">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H244">
         <v>1782.0000000000002</v>
@@ -28231,7 +28231,7 @@
         <v>0.12840000000000001</v>
       </c>
       <c r="G245">
-        <v>0.28589719626168225</v>
+        <v>0.29225046728971965</v>
       </c>
       <c r="H245">
         <v>1559.9439252336451</v>
@@ -28284,7 +28284,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G246">
-        <v>0.28737000000000001</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H246">
         <v>1782.0000000000002</v>
@@ -28337,7 +28337,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="G247">
-        <v>0.28737000000000001</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H247">
         <v>1782.0000000000005</v>
@@ -28390,7 +28390,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="G248">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H248">
         <v>1518.0000000000002</v>
@@ -28443,7 +28443,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="G249">
-        <v>0.28737000000000001</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H249">
         <v>1782.0000000000002</v>
@@ -28496,7 +28496,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G250">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H250">
         <v>1782.0000000000005</v>
@@ -28549,7 +28549,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G251">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H251">
         <v>1782.0000000000002</v>
@@ -28602,7 +28602,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G252">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H252">
         <v>1782.0000000000002</v>
@@ -28655,7 +28655,7 @@
         <v>0.113</v>
       </c>
       <c r="G253">
-        <v>0.29663999999999996</v>
+        <v>0.30323199999999995</v>
       </c>
       <c r="H253">
         <v>1782.0000000000005</v>
@@ -28708,7 +28708,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="G254">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H254">
         <v>1782.0000000000002</v>
@@ -28761,7 +28761,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G255">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H255">
         <v>1782.0000000000002</v>
@@ -28793,7 +28793,7 @@
         <v>4.8899999999999999E-2</v>
       </c>
       <c r="G256">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H256">
         <v>1782</v>
@@ -28825,7 +28825,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="G257">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H257">
         <v>1782.0000000000005</v>
@@ -28857,7 +28857,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="G258">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H258">
         <v>1782.0000000000002</v>
@@ -28889,7 +28889,7 @@
         <v>0.113</v>
       </c>
       <c r="G259">
-        <v>0.31189858407079646</v>
+        <v>0.3188296637168142</v>
       </c>
       <c r="H259">
         <v>1611.4513274336286</v>
@@ -28921,7 +28921,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="G260">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H260">
         <v>1782.0000000000002</v>
@@ -28953,7 +28953,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G261">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H261">
         <v>1518.0000000000002</v>
@@ -28985,7 +28985,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G262">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H262">
         <v>1782.0000000000002</v>
@@ -29017,7 +29017,7 @@
         <v>2.9960000000000001E-2</v>
       </c>
       <c r="G263">
-        <v>0.30590999999999996</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H263">
         <v>1782.0000000000002</v>
@@ -29049,7 +29049,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="G264">
-        <v>0.31054500000000002</v>
+        <v>0.31744600000000006</v>
       </c>
       <c r="H264">
         <v>1782.0000000000002</v>
@@ -29081,7 +29081,7 @@
         <v>0.24399999999999999</v>
       </c>
       <c r="G265">
-        <v>0.31669967213114752</v>
+        <v>0.32373744262295084</v>
       </c>
       <c r="H265">
         <v>1606.7213114754104</v>
@@ -29113,7 +29113,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="G266">
-        <v>0.31054500000000002</v>
+        <v>0.31744600000000001</v>
       </c>
       <c r="H266">
         <v>1782.0000000000002</v>
@@ -29145,7 +29145,7 @@
         <v>3.8700000000000005E-2</v>
       </c>
       <c r="G267">
-        <v>0.31054500000000002</v>
+        <v>0.31744600000000006</v>
       </c>
       <c r="H267">
         <v>1782</v>
@@ -29177,7 +29177,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="G268">
-        <v>0.3172752739726028</v>
+        <v>0.32432583561643841</v>
       </c>
       <c r="H268">
         <v>1590.3287671232881</v>
@@ -29209,7 +29209,7 @@
         <v>0.13789999999999999</v>
       </c>
       <c r="G269">
-        <v>0.31424224437998549</v>
+        <v>0.32122540536620742</v>
       </c>
       <c r="H269">
         <v>1676.7063089195069</v>
@@ -29241,7 +29241,7 @@
         <v>2.155E-2</v>
       </c>
       <c r="G270">
-        <v>0.31054500000000002</v>
+        <v>0.31744600000000006</v>
       </c>
       <c r="H270">
         <v>1782.0000000000002</v>
@@ -29273,7 +29273,7 @@
         <v>0.121</v>
       </c>
       <c r="G271">
-        <v>0.31981500000000002</v>
+        <v>0.32692199999999999</v>
       </c>
       <c r="H271">
         <v>1518.0000000000002</v>
@@ -29305,7 +29305,7 @@
         <v>0.44500000000000001</v>
       </c>
       <c r="G272">
-        <v>0.33835500000000002</v>
+        <v>0.34587399999999996</v>
       </c>
       <c r="H272">
         <v>1320</v>
@@ -29337,7 +29337,7 @@
         <v>0.622</v>
       </c>
       <c r="G273">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H273">
         <v>1320</v>
@@ -29369,7 +29369,7 @@
         <v>0.1108</v>
       </c>
       <c r="G274">
-        <v>0.30591000000000007</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H274">
         <v>1518.0000000000002</v>
@@ -29401,7 +29401,7 @@
         <v>0.41499999999999998</v>
       </c>
       <c r="G275">
-        <v>0.30591000000000002</v>
+        <v>0.3127080000000001</v>
       </c>
       <c r="H275">
         <v>1320</v>
@@ -29433,7 +29433,7 @@
         <v>0.11</v>
       </c>
       <c r="G276">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H276">
         <v>1518.0000000000002</v>
@@ -29465,7 +29465,7 @@
         <v>0.11</v>
       </c>
       <c r="G277">
-        <v>0.31518000000000002</v>
+        <v>0.32218400000000003</v>
       </c>
       <c r="H277">
         <v>1518.0000000000002</v>
@@ -29497,7 +29497,7 @@
         <v>0.32</v>
       </c>
       <c r="G278">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H278">
         <v>1320</v>
@@ -29529,7 +29529,7 @@
         <v>0.32</v>
       </c>
       <c r="G279">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H279">
         <v>1320</v>
@@ -29561,7 +29561,7 @@
         <v>0.17699999999999999</v>
       </c>
       <c r="G280">
-        <v>0.27810000000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H280">
         <v>1518.0000000000002</v>
@@ -29593,7 +29593,7 @@
         <v>0.24099999999999999</v>
       </c>
       <c r="G281">
-        <v>0.31518000000000002</v>
+        <v>0.32218399999999997</v>
       </c>
       <c r="H281">
         <v>1518.0000000000002</v>
@@ -29625,7 +29625,7 @@
         <v>0.45</v>
       </c>
       <c r="G282">
-        <v>0.30591000000000002</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H282">
         <v>1320</v>
@@ -29657,7 +29657,7 @@
         <v>0.188</v>
       </c>
       <c r="G283">
-        <v>0.31981500000000002</v>
+        <v>0.32692199999999999</v>
       </c>
       <c r="H283">
         <v>1518.0000000000002</v>
@@ -29689,7 +29689,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G284">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H284">
         <v>1782.0000000000002</v>
@@ -30905,7 +30905,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G322">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H322">
         <v>1633.5000000000002</v>
@@ -30937,7 +30937,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="G323">
-        <v>0.44496000000000002</v>
+        <v>0.45484800000000003</v>
       </c>
       <c r="H323">
         <v>1391.5</v>
@@ -30969,7 +30969,7 @@
         <v>4.7E-2</v>
       </c>
       <c r="G324">
-        <v>0.42642000000000008</v>
+        <v>0.43589600000000006</v>
       </c>
       <c r="H324">
         <v>1633.5000000000002</v>
@@ -31001,7 +31001,7 @@
         <v>0.26500000000000001</v>
       </c>
       <c r="G325">
-        <v>0.33372000000000002</v>
+        <v>0.34113600000000005</v>
       </c>
       <c r="H325">
         <v>1391.5</v>
@@ -31033,7 +31033,7 @@
         <v>0.16200000000000001</v>
       </c>
       <c r="G326">
-        <v>0.44496000000000002</v>
+        <v>0.45484800000000003</v>
       </c>
       <c r="H326">
         <v>1391.5</v>
@@ -31065,7 +31065,7 @@
         <v>0.126</v>
       </c>
       <c r="G327">
-        <v>0.50058000000000002</v>
+        <v>0.51170400000000005</v>
       </c>
       <c r="H327">
         <v>1391.5</v>
@@ -31097,7 +31097,7 @@
         <v>0.10100000000000001</v>
       </c>
       <c r="G328">
-        <v>0.20394000000000001</v>
+        <v>0.20847200000000002</v>
       </c>
       <c r="H328">
         <v>1138.5</v>
@@ -31129,7 +31129,7 @@
         <v>0.1</v>
       </c>
       <c r="G329">
-        <v>0.21321000000000004</v>
+        <v>0.21794800000000003</v>
       </c>
       <c r="H329">
         <v>1336.5</v>
@@ -31161,7 +31161,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G330">
-        <v>0.25029000000000001</v>
+        <v>0.25585200000000002</v>
       </c>
       <c r="H330">
         <v>1336.5</v>
@@ -31193,7 +31193,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G331">
-        <v>0.26882999999999996</v>
+        <v>0.27480399999999999</v>
       </c>
       <c r="H331">
         <v>1336.5</v>
@@ -31225,7 +31225,7 @@
         <v>0.13600000000000001</v>
       </c>
       <c r="G332">
-        <v>0.22248000000000001</v>
+        <v>0.22742400000000002</v>
       </c>
       <c r="H332">
         <v>1138.5</v>
@@ -31257,7 +31257,7 @@
         <v>0.13</v>
       </c>
       <c r="G333">
-        <v>0.18540000000000001</v>
+        <v>0.18952000000000002</v>
       </c>
       <c r="H333">
         <v>1138.5</v>
@@ -31289,7 +31289,7 @@
         <v>8.8800000000000004E-2</v>
       </c>
       <c r="G334">
-        <v>0.28273500000000001</v>
+        <v>0.289018</v>
       </c>
       <c r="H334">
         <v>1265</v>
@@ -31321,7 +31321,7 @@
         <v>0.02</v>
       </c>
       <c r="G335">
-        <v>0.25956000000000007</v>
+        <v>0.26532800000000006</v>
       </c>
       <c r="H335">
         <v>1930.5000000000005</v>
@@ -31353,7 +31353,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
       <c r="G336">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H336">
         <v>1644.4999999999998</v>
@@ -31385,7 +31385,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G337">
-        <v>0.29664000000000001</v>
+        <v>0.303232</v>
       </c>
       <c r="H337">
         <v>1930.5000000000002</v>
@@ -31417,7 +31417,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G338">
-        <v>0.31054500000000002</v>
+        <v>0.31744600000000012</v>
       </c>
       <c r="H338">
         <v>1644.4999999999998</v>
@@ -31449,7 +31449,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="G339">
-        <v>0.32908499999999996</v>
+        <v>0.33639799999999997</v>
       </c>
       <c r="H339">
         <v>1430.0000000000002</v>
@@ -31496,7 +31496,7 @@
         <v>33</v>
       </c>
       <c r="L340">
-        <v>0.14414942289270036</v>
+        <v>0.14414942289270033</v>
       </c>
     </row>
     <row r="341" spans="2:12" x14ac:dyDescent="0.45">
@@ -32534,7 +32534,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L370">
-        <v>0.54945115474541018</v>
+        <v>0.54945115474541029</v>
       </c>
     </row>
     <row r="371" spans="2:12" x14ac:dyDescent="0.45">
@@ -33339,7 +33339,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L405">
-        <v>0.36687700880096002</v>
+        <v>0.36687700880096008</v>
       </c>
     </row>
     <row r="406" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5328332A-B96C-42A2-A53A-DF4FD2351126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FFE7B3B-4701-4820-8909-60A152A7E882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E6FDAEFE-302B-43A6-B948-2BC49F2E2399}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4AD46E8B-B3F8-4F87-8ABE-0385DC9C83FD}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2867,7 +2867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662AA5B5-3193-4AB5-9A92-23C731A15002}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D52362-CA85-4A23-B274-218D9A856C98}">
   <dimension ref="B9:T281"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15744,7 +15744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0E58D5-4CF6-47A1-8C69-DA39EBB52EA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2CCC2B1-6131-4541-884E-DC63CA98158F}">
   <dimension ref="B9:T438"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31496,7 +31496,7 @@
         <v>33</v>
       </c>
       <c r="L340">
-        <v>0.14414942289270033</v>
+        <v>0.14414942289270036</v>
       </c>
     </row>
     <row r="341" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FFE7B3B-4701-4820-8909-60A152A7E882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E50587C-E2CE-4EFF-A876-29EF6C9839AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4AD46E8B-B3F8-4F87-8ABE-0385DC9C83FD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0CAAC6B5-DB01-425C-B204-028BE6BF6EB8}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2867,7 +2867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D52362-CA85-4A23-B274-218D9A856C98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29623FD-AB59-434B-BD66-DAC9519D7575}">
   <dimension ref="B9:T281"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15744,7 +15744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2CCC2B1-6131-4541-884E-DC63CA98158F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA2A38C4-C9CE-429D-8847-5177E7BD1318}">
   <dimension ref="B9:T438"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33339,7 +33339,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L405">
-        <v>0.36687700880096008</v>
+        <v>0.36687700880096002</v>
       </c>
     </row>
     <row r="406" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E50587C-E2CE-4EFF-A876-29EF6C9839AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6900FF00-5773-440F-AAB4-EE0E6558BF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0CAAC6B5-DB01-425C-B204-028BE6BF6EB8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{40A6519C-8213-40CD-8F77-FB3DA60155A1}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2867,7 +2867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29623FD-AB59-434B-BD66-DAC9519D7575}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{261FAF23-A3D2-4C44-8CBF-CCB7F437C7F0}">
   <dimension ref="B9:T281"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15744,7 +15744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA2A38C4-C9CE-429D-8847-5177E7BD1318}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C5152C-3C91-467E-8EF1-C97B19B3FE5F}">
   <dimension ref="B9:T438"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31496,7 +31496,7 @@
         <v>33</v>
       </c>
       <c r="L340">
-        <v>0.14414942289270036</v>
+        <v>0.14414942289270033</v>
       </c>
     </row>
     <row r="341" spans="2:12" x14ac:dyDescent="0.45">
@@ -33339,7 +33339,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L405">
-        <v>0.36687700880096002</v>
+        <v>0.36687700880096008</v>
       </c>
     </row>
     <row r="406" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F905DBE3-A1EB-4EBE-9BC7-EA053DE52838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F353DE70-D48A-4678-918B-E4B4131435BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B4B530CD-ECBE-4FBE-A8A4-14D2E77469B4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{94CCC158-1173-4E80-A1A5-4962F6D3FDE9}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3835,7 +3835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FD7347-B7A8-46CF-B3F6-376B3EF2B07D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C973F19E-FC2B-4725-9773-CD9C6F30090B}">
   <dimension ref="B9:T186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13732,7 +13732,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BED8CD64-B148-4AB2-9E56-F66ACEE1AEC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A11FC4AF-122E-42E4-AF0E-091CCB7B7CA0}">
   <dimension ref="B9:T160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21135,7 +21135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E560B354-A01A-4B5A-80A6-0094DA8C3973}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6DD4FC5-8629-49F1-B3FB-7F4C515F7EDE}">
   <dimension ref="B9:T1169"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30021,7 +30021,7 @@
         <v>181</v>
       </c>
       <c r="P177" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="Q177" t="s">
         <v>395</v>
@@ -30074,7 +30074,7 @@
         <v>181</v>
       </c>
       <c r="P178" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="Q178" t="s">
         <v>395</v>
@@ -34208,7 +34208,7 @@
         <v>274</v>
       </c>
       <c r="P256" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="Q256" t="s">
         <v>395</v>
@@ -34261,7 +34261,7 @@
         <v>274</v>
       </c>
       <c r="P257" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="Q257" t="s">
         <v>395</v>
@@ -37152,7 +37152,7 @@
         <v>351</v>
       </c>
       <c r="P312" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="Q312" t="s">
         <v>395</v>
@@ -37202,7 +37202,7 @@
         <v>351</v>
       </c>
       <c r="P313" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="Q313" t="s">
         <v>395</v>
@@ -37252,7 +37252,7 @@
         <v>352</v>
       </c>
       <c r="P314" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="Q314" t="s">
         <v>395</v>
@@ -37302,7 +37302,7 @@
         <v>352</v>
       </c>
       <c r="P315" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="Q315" t="s">
         <v>395</v>
@@ -37352,7 +37352,7 @@
         <v>354</v>
       </c>
       <c r="P316" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="Q316" t="s">
         <v>395</v>
@@ -37402,7 +37402,7 @@
         <v>354</v>
       </c>
       <c r="P317" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="Q317" t="s">
         <v>395</v>
@@ -37852,7 +37852,7 @@
         <v>365</v>
       </c>
       <c r="P326" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="Q326" t="s">
         <v>395</v>
@@ -37902,7 +37902,7 @@
         <v>365</v>
       </c>
       <c r="P327" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="Q327" t="s">
         <v>395</v>
@@ -39494,7 +39494,7 @@
         <v>33</v>
       </c>
       <c r="L370">
-        <v>0.14147154991776351</v>
+        <v>0.14147154991776353</v>
       </c>
     </row>
     <row r="371" spans="2:12" x14ac:dyDescent="0.45">
@@ -39520,7 +39520,7 @@
         <v>33</v>
       </c>
       <c r="L371">
-        <v>0.14147154991776351</v>
+        <v>0.14147154991776353</v>
       </c>
     </row>
     <row r="372" spans="2:12" x14ac:dyDescent="0.45">
@@ -39546,7 +39546,7 @@
         <v>33</v>
       </c>
       <c r="L372">
-        <v>0.14147154991776351</v>
+        <v>0.14147154991776353</v>
       </c>
     </row>
     <row r="373" spans="2:12" x14ac:dyDescent="0.45">
@@ -39581,7 +39581,7 @@
         <v>35</v>
       </c>
       <c r="L373">
-        <v>0.14147154991776351</v>
+        <v>0.14147154991776353</v>
       </c>
     </row>
     <row r="374" spans="2:12" x14ac:dyDescent="0.45">
@@ -39616,7 +39616,7 @@
         <v>32</v>
       </c>
       <c r="L374">
-        <v>0.14147154991776351</v>
+        <v>0.14147154991776353</v>
       </c>
     </row>
     <row r="375" spans="2:12" x14ac:dyDescent="0.45">
@@ -54910,7 +54910,7 @@
         <v>33</v>
       </c>
       <c r="L812">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="813" spans="2:12" x14ac:dyDescent="0.45">
@@ -54936,7 +54936,7 @@
         <v>33</v>
       </c>
       <c r="L813">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="814" spans="2:12" x14ac:dyDescent="0.45">
@@ -54962,7 +54962,7 @@
         <v>33</v>
       </c>
       <c r="L814">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="815" spans="2:12" x14ac:dyDescent="0.45">
@@ -54997,7 +54997,7 @@
         <v>57</v>
       </c>
       <c r="L815">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="816" spans="2:12" x14ac:dyDescent="0.45">
@@ -55032,7 +55032,7 @@
         <v>56</v>
       </c>
       <c r="L816">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="817" spans="2:12" x14ac:dyDescent="0.45">
@@ -55067,7 +55067,7 @@
         <v>55</v>
       </c>
       <c r="L817">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="818" spans="2:12" x14ac:dyDescent="0.45">
@@ -55102,7 +55102,7 @@
         <v>54</v>
       </c>
       <c r="L818">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="819" spans="2:12" x14ac:dyDescent="0.45">
@@ -55137,7 +55137,7 @@
         <v>53</v>
       </c>
       <c r="L819">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="820" spans="2:12" x14ac:dyDescent="0.45">
@@ -55172,7 +55172,7 @@
         <v>52</v>
       </c>
       <c r="L820">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="821" spans="2:12" x14ac:dyDescent="0.45">
@@ -55207,7 +55207,7 @@
         <v>51</v>
       </c>
       <c r="L821">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="822" spans="2:12" x14ac:dyDescent="0.45">
@@ -55242,7 +55242,7 @@
         <v>50</v>
       </c>
       <c r="L822">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="823" spans="2:12" x14ac:dyDescent="0.45">
@@ -55277,7 +55277,7 @@
         <v>47</v>
       </c>
       <c r="L823">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="824" spans="2:12" x14ac:dyDescent="0.45">
@@ -55312,7 +55312,7 @@
         <v>46</v>
       </c>
       <c r="L824">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="825" spans="2:12" x14ac:dyDescent="0.45">
@@ -55347,7 +55347,7 @@
         <v>45</v>
       </c>
       <c r="L825">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="826" spans="2:12" x14ac:dyDescent="0.45">
@@ -67396,7 +67396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{509B44D1-970E-4874-B20D-77EA175A0073}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{754F94B4-6694-4EAB-B5FB-58CFFB939ECF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F353DE70-D48A-4678-918B-E4B4131435BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DEA05CB-7953-4211-A6D4-783C00C58CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{94CCC158-1173-4E80-A1A5-4962F6D3FDE9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3A073C9E-E0A4-4A19-9AD5-6D5E7C093C15}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3835,7 +3835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C973F19E-FC2B-4725-9773-CD9C6F30090B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07103D40-12F9-49F9-A4D6-73A008FF2ED5}">
   <dimension ref="B9:T186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11168,7 +11168,7 @@
         <v>929</v>
       </c>
       <c r="P140" t="s">
-        <v>1104</v>
+        <v>1023</v>
       </c>
       <c r="Q140" t="s">
         <v>395</v>
@@ -11224,7 +11224,7 @@
         <v>929</v>
       </c>
       <c r="P141" t="s">
-        <v>1023</v>
+        <v>1104</v>
       </c>
       <c r="Q141" t="s">
         <v>395</v>
@@ -13732,7 +13732,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A11FC4AF-122E-42E4-AF0E-091CCB7B7CA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAB0470B-34D0-47F2-9E5E-4B50FDE18958}">
   <dimension ref="B9:T160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21135,7 +21135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6DD4FC5-8629-49F1-B3FB-7F4C515F7EDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29DA4982-20B0-478C-B767-D5D58D2481D6}">
   <dimension ref="B9:T1169"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25737,7 +25737,7 @@
         <v>101</v>
       </c>
       <c r="P96" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="Q96" t="s">
         <v>395</v>
@@ -25790,7 +25790,7 @@
         <v>101</v>
       </c>
       <c r="P97" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="Q97" t="s">
         <v>395</v>
@@ -30021,7 +30021,7 @@
         <v>181</v>
       </c>
       <c r="P177" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="Q177" t="s">
         <v>395</v>
@@ -30074,7 +30074,7 @@
         <v>181</v>
       </c>
       <c r="P178" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="Q178" t="s">
         <v>395</v>
@@ -37252,7 +37252,7 @@
         <v>352</v>
       </c>
       <c r="P314" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="Q314" t="s">
         <v>395</v>
@@ -37302,7 +37302,7 @@
         <v>352</v>
       </c>
       <c r="P315" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="Q315" t="s">
         <v>395</v>
@@ -37352,7 +37352,7 @@
         <v>354</v>
       </c>
       <c r="P316" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="Q316" t="s">
         <v>395</v>
@@ -37402,7 +37402,7 @@
         <v>354</v>
       </c>
       <c r="P317" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="Q317" t="s">
         <v>395</v>
@@ -37752,7 +37752,7 @@
         <v>363</v>
       </c>
       <c r="P324" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="Q324" t="s">
         <v>395</v>
@@ -37802,7 +37802,7 @@
         <v>363</v>
       </c>
       <c r="P325" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="Q325" t="s">
         <v>395</v>
@@ -37852,7 +37852,7 @@
         <v>365</v>
       </c>
       <c r="P326" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="Q326" t="s">
         <v>395</v>
@@ -37902,7 +37902,7 @@
         <v>365</v>
       </c>
       <c r="P327" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="Q327" t="s">
         <v>395</v>
@@ -67396,7 +67396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{754F94B4-6694-4EAB-B5FB-58CFFB939ECF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A7B368-A7F1-4D3C-970B-BE06EBD4B794}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
